--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -839,9 +839,29 @@
         <v>N/A</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TEST-RESTORE-002</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2024-01-01</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Test Complainant 2</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Test Respondent 2</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>Test Offense 2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O13"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -859,9 +859,150 @@
         <v>Test Offense 2</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2342323</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C11" t="str">
+        <v>josshh</v>
+      </c>
+      <c r="D11" t="str">
+        <v>ssds</v>
+      </c>
+      <c r="E11" t="str">
+        <v>loboc</v>
+      </c>
+      <c r="F11" t="str">
+        <v>theft</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="I11" t="str">
+        <v>james</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Reppublic Act 2104</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Tagbi</v>
+      </c>
+      <c r="L11" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="M11" t="str">
+        <v>pending</v>
+      </c>
+      <c r="N11" t="str">
+        <v>14k</v>
+      </c>
+      <c r="O11" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>7567564</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C12" t="str">
+        <v>isabel</v>
+      </c>
+      <c r="D12" t="str">
+        <v>asas</v>
+      </c>
+      <c r="E12" t="str">
+        <v>maribojoc</v>
+      </c>
+      <c r="F12" t="str">
+        <v xml:space="preserve">tax </v>
+      </c>
+      <c r="G12" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-01-30</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Atty. Superman</v>
+      </c>
+      <c r="J12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K12" t="str">
+        <v>tagbi</v>
+      </c>
+      <c r="L12" t="str">
+        <v>2026-01-29</v>
+      </c>
+      <c r="M12" t="str">
+        <v>terminated</v>
+      </c>
+      <c r="N12" t="str">
+        <v>12k</v>
+      </c>
+      <c r="O12" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>8678675</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C13" t="str">
+        <v>mark</v>
+      </c>
+      <c r="D13" t="str">
+        <v>wasdas</v>
+      </c>
+      <c r="E13" t="str">
+        <v>buol</v>
+      </c>
+      <c r="F13" t="str">
+        <v>raped</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Atty. Doroy</v>
+      </c>
+      <c r="J13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Capitol</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="M13" t="str">
+        <v>pending</v>
+      </c>
+      <c r="N13" t="str">
+        <v>15k</v>
+      </c>
+      <c r="O13" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O11"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -465,254 +465,227 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DKT-2024-001</v>
+        <v>3232</v>
       </c>
       <c r="B2" t="str">
-        <v>2024-01-10</v>
+        <v>2026-01-06</v>
       </c>
       <c r="C2" t="str">
-        <v>PNP Tagbilaran</v>
+        <v>keynn</v>
       </c>
       <c r="D2" t="str">
-        <v>John Doe</v>
+        <v>trekk</v>
       </c>
       <c r="E2" t="str">
-        <v>loon</v>
+        <v>San Isidro</v>
       </c>
       <c r="F2" t="str">
-        <v>Theft</v>
+        <v>robbery</v>
       </c>
       <c r="G2" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="H2" t="str">
-        <v>2024-03-15</v>
+        <v>2026-01-07</v>
       </c>
       <c r="I2" t="str">
-        <v>Prosecutor Martinez</v>
+        <v>Atty.batman</v>
       </c>
       <c r="J2" t="str">
-        <v>CRIM-2024-001</v>
+        <v>Reppublic Act 2104</v>
       </c>
       <c r="K2" t="str">
-        <v>Branch 1</v>
+        <v>Tagbi</v>
       </c>
       <c r="L2" t="str">
-        <v>2024-02-05</v>
+        <v>2026-01-08</v>
       </c>
       <c r="M2" t="str">
-        <v>Dismissed</v>
+        <v>Pending</v>
       </c>
       <c r="N2" t="str">
-        <v>Fine of P5000</v>
+        <v>14k</v>
       </c>
       <c r="O2" t="str">
-        <v>/uploads/index_cards/indexcard-1769145928098-113952033.png</v>
+        <v>/uploads/index_cards/indexcard-1769146086538-553986725.png</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DKT-2024-002</v>
+        <v>4121214</v>
       </c>
       <c r="B3" t="str">
-        <v>2024-02-16</v>
+        <v>2026-01-29</v>
       </c>
       <c r="C3" t="str">
-        <v>PNP Tagbilaran</v>
+        <v>shaaan</v>
       </c>
       <c r="D3" t="str">
-        <v>Jane Smith</v>
+        <v>kroel</v>
       </c>
       <c r="E3" t="str">
-        <v>loon</v>
+        <v>Dauis</v>
       </c>
       <c r="F3" t="str">
-        <v>Assault</v>
+        <v>raped</v>
       </c>
       <c r="G3" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="H3" t="str">
-        <v>2024-04-11</v>
+        <v>2026-01-13</v>
       </c>
       <c r="I3" t="str">
-        <v>Prosecutor Garcia</v>
+        <v>Atty. Doroy</v>
       </c>
       <c r="J3" t="str">
-        <v>CRIM-2024-002</v>
+        <v>N/A</v>
       </c>
       <c r="K3" t="str">
-        <v>Branch 2</v>
+        <v>Capitol</v>
       </c>
       <c r="L3" t="str">
-        <v>2024-03-11</v>
+        <v>2026-01-22</v>
       </c>
       <c r="M3" t="str">
-        <v>Convicted</v>
+        <v>pending</v>
       </c>
       <c r="N3" t="str">
-        <v>Pending</v>
+        <v>15k</v>
       </c>
       <c r="O3" t="str">
-        <v>/uploads/index_cards/indexcard-1769145953585-913133096.png</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3232</v>
+        <v>65243242</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-06</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C4" t="str">
-        <v>keynn</v>
+        <v>emann</v>
       </c>
       <c r="D4" t="str">
-        <v>trekk</v>
+        <v>clifff</v>
       </c>
       <c r="E4" t="str">
-        <v>San Isidro</v>
+        <v>maribojoc</v>
       </c>
       <c r="F4" t="str">
-        <v>robbery</v>
+        <v xml:space="preserve">tax </v>
       </c>
       <c r="G4" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-01-07</v>
+        <v>2026-01-25</v>
       </c>
       <c r="I4" t="str">
-        <v>Atty.batman</v>
+        <v>Atty. Superman</v>
       </c>
       <c r="J4" t="str">
-        <v>Reppublic Act 2104</v>
+        <v>N/A</v>
       </c>
       <c r="K4" t="str">
-        <v>Tagbi</v>
+        <v>tagbi</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-24</v>
       </c>
       <c r="M4" t="str">
-        <v>Pending</v>
+        <v>Convicted</v>
       </c>
       <c r="N4" t="str">
-        <v>14k</v>
+        <v>12k</v>
       </c>
       <c r="O4" t="str">
-        <v>/uploads/index_cards/indexcard-1769146086538-553986725.png</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>245232</v>
+        <v>76543232</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-05</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C5" t="str">
-        <v>koynnn</v>
+        <v>namiiiii</v>
       </c>
       <c r="D5" t="str">
-        <v>kart</v>
+        <v>chriss</v>
       </c>
       <c r="E5" t="str">
-        <v xml:space="preserve">Tiptip </v>
+        <v>buol</v>
       </c>
       <c r="F5" t="str">
-        <v>grave threat</v>
+        <v>raped</v>
       </c>
       <c r="G5" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-01-28</v>
+        <v>2026-01-13</v>
       </c>
       <c r="I5" t="str">
-        <v>Atty. Superman</v>
+        <v>Atty. Doroy</v>
       </c>
       <c r="J5" t="str">
         <v>N/A</v>
       </c>
       <c r="K5" t="str">
-        <v>tagbi</v>
+        <v>Capitol</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-22</v>
       </c>
       <c r="M5" t="str">
-        <v>Dismissed</v>
+        <v>pending</v>
       </c>
       <c r="N5" t="str">
-        <v>12k</v>
+        <v>15k</v>
       </c>
       <c r="O5" t="str">
-        <v>/uploads/index_cards/indexcard-1769146194762-537518850.png</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>4121214</v>
+        <v>TEST-RESTORE-002</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-29</v>
+        <v>2024-01-01</v>
       </c>
       <c r="C6" t="str">
-        <v>shaaan</v>
+        <v>Test Complainant 2</v>
       </c>
       <c r="D6" t="str">
-        <v>kroel</v>
+        <v>Test Respondent 2</v>
       </c>
       <c r="E6" t="str">
-        <v>Dauis</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>raped</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H6" t="str">
-        <v>2026-01-13</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Atty. Doroy</v>
-      </c>
-      <c r="J6" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Capitol</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="M6" t="str">
-        <v>pending</v>
-      </c>
-      <c r="N6" t="str">
-        <v>15k</v>
-      </c>
-      <c r="O6" t="str">
-        <v>N/A</v>
+        <v>Test Offense 2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>13242141</v>
+        <v>2342323</v>
       </c>
       <c r="B7" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C7" t="str">
-        <v>manny</v>
+        <v>josshh</v>
       </c>
       <c r="D7" t="str">
-        <v>clifford</v>
+        <v>ssds</v>
       </c>
       <c r="E7" t="str">
-        <v>San isidro</v>
+        <v>loboc</v>
       </c>
       <c r="F7" t="str">
         <v>theft</v>
@@ -721,7 +694,7 @@
         <v>Invalid Date</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-01-08</v>
+        <v>2026-01-07</v>
       </c>
       <c r="I7" t="str">
         <v>james</v>
@@ -733,7 +706,7 @@
         <v>Tagbi</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-01-09</v>
+        <v>2026-01-08</v>
       </c>
       <c r="M7" t="str">
         <v>pending</v>
@@ -747,16 +720,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>65243242</v>
+        <v>7567564</v>
       </c>
       <c r="B8" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C8" t="str">
-        <v>emann</v>
+        <v>isabel</v>
       </c>
       <c r="D8" t="str">
-        <v>clifff</v>
+        <v>asas</v>
       </c>
       <c r="E8" t="str">
         <v>maribojoc</v>
@@ -768,7 +741,7 @@
         <v>Invalid Date</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-30</v>
       </c>
       <c r="I8" t="str">
         <v>Atty. Superman</v>
@@ -780,10 +753,10 @@
         <v>tagbi</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-01-24</v>
+        <v>2026-01-29</v>
       </c>
       <c r="M8" t="str">
-        <v>Convicted</v>
+        <v>terminated</v>
       </c>
       <c r="N8" t="str">
         <v>12k</v>
@@ -794,46 +767,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>76543232</v>
+        <v>TEST-2026-001</v>
       </c>
       <c r="B9" t="str">
-        <v>Invalid Date</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C9" t="str">
-        <v>namiiiii</v>
+        <v>Test Complainant</v>
       </c>
       <c r="D9" t="str">
-        <v>chriss</v>
+        <v>Test Respondent</v>
       </c>
       <c r="E9" t="str">
-        <v>buol</v>
+        <v>Test Address</v>
       </c>
       <c r="F9" t="str">
-        <v>raped</v>
+        <v>Test Offense</v>
       </c>
       <c r="G9" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H9" t="str">
-        <v>2026-01-13</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Atty. Doroy</v>
+        <v>2026-02-18</v>
       </c>
       <c r="J9" t="str">
         <v>N/A</v>
       </c>
       <c r="K9" t="str">
-        <v>Capitol</v>
-      </c>
-      <c r="L9" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="M9" t="str">
-        <v>pending</v>
-      </c>
-      <c r="N9" t="str">
-        <v>15k</v>
+        <v>Test Branch</v>
       </c>
       <c r="O9" t="str">
         <v>N/A</v>
@@ -841,168 +799,83 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TEST-RESTORE-002</v>
+        <v>TEST-2026-002</v>
       </c>
       <c r="B10" t="str">
-        <v>2024-01-01</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C10" t="str">
-        <v>Test Complainant 2</v>
+        <v>Test Complainant</v>
       </c>
       <c r="D10" t="str">
-        <v>Test Respondent 2</v>
+        <v>Test Respondent</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>Test Address</v>
       </c>
       <c r="F10" t="str">
-        <v>Test Offense 2</v>
+        <v>Test Offense</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="J10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Test Branch</v>
+      </c>
+      <c r="O10" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2342323</v>
+        <v>VII-14-INQ-22C-134</v>
       </c>
       <c r="B11" t="str">
-        <v>Invalid Date</v>
+        <v>2026-02-26</v>
       </c>
       <c r="C11" t="str">
-        <v>josshh</v>
+        <v>asdasda</v>
       </c>
       <c r="D11" t="str">
-        <v>ssds</v>
+        <v>asdasd</v>
       </c>
       <c r="E11" t="str">
-        <v>loboc</v>
+        <v>asdasdas</v>
       </c>
       <c r="F11" t="str">
-        <v>theft</v>
+        <v>asdasdas</v>
       </c>
       <c r="G11" t="str">
-        <v>Invalid Date</v>
+        <v>2026-02-28</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-01-07</v>
+        <v>2026-02-25</v>
       </c>
       <c r="I11" t="str">
-        <v>james</v>
+        <v>Atty. Joshua</v>
       </c>
       <c r="J11" t="str">
-        <v>Reppublic Act 2104</v>
+        <v>N/A</v>
       </c>
       <c r="K11" t="str">
-        <v>Tagbi</v>
+        <v>asdasda</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-01-08</v>
-      </c>
-      <c r="M11" t="str">
-        <v>pending</v>
+        <v>2026-02-25</v>
       </c>
       <c r="N11" t="str">
-        <v>14k</v>
+        <v>2322</v>
       </c>
       <c r="O11" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>7567564</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="C12" t="str">
-        <v>isabel</v>
-      </c>
-      <c r="D12" t="str">
-        <v>asas</v>
-      </c>
-      <c r="E12" t="str">
-        <v>maribojoc</v>
-      </c>
-      <c r="F12" t="str">
-        <v xml:space="preserve">tax </v>
-      </c>
-      <c r="G12" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H12" t="str">
-        <v>2026-01-30</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Atty. Superman</v>
-      </c>
-      <c r="J12" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="K12" t="str">
-        <v>tagbi</v>
-      </c>
-      <c r="L12" t="str">
-        <v>2026-01-29</v>
-      </c>
-      <c r="M12" t="str">
-        <v>terminated</v>
-      </c>
-      <c r="N12" t="str">
-        <v>12k</v>
-      </c>
-      <c r="O12" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>8678675</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="C13" t="str">
-        <v>mark</v>
-      </c>
-      <c r="D13" t="str">
-        <v>wasdas</v>
-      </c>
-      <c r="E13" t="str">
-        <v>buol</v>
-      </c>
-      <c r="F13" t="str">
-        <v>raped</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H13" t="str">
-        <v>2026-01-13</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Atty. Doroy</v>
-      </c>
-      <c r="J13" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Capitol</v>
-      </c>
-      <c r="L13" t="str">
-        <v>2026-01-22</v>
-      </c>
-      <c r="M13" t="str">
-        <v>pending</v>
-      </c>
-      <c r="N13" t="str">
-        <v>15k</v>
-      </c>
-      <c r="O13" t="str">
-        <v>N/A</v>
+        <v>/uploads/index_cards/indexcard-1771488487177-586779391.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O102"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -465,301 +465,283 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3232</v>
+        <v>VII-14-INV-21K-522</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-06</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C2" t="str">
-        <v>keynn</v>
+        <v>EVANGELINE M. GABI</v>
       </c>
       <c r="D2" t="str">
-        <v>trekk</v>
+        <v>VII-14-INV 23F-299</v>
       </c>
       <c r="E2" t="str">
-        <v>San Isidro</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>robbery</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Invalid Date</v>
+        <v>ESTAFA IN REL. TO R.A. 10175 KNOWN AS CYBERCRIME PREVENTION ACT OF 2021</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-01-07</v>
+        <v>Invalid Date</v>
       </c>
       <c r="I2" t="str">
-        <v>Atty.batman</v>
+        <v>J. R. CESAR</v>
       </c>
       <c r="J2" t="str">
-        <v>Reppublic Act 2104</v>
+        <v>R-25552</v>
       </c>
       <c r="K2" t="str">
-        <v>Tagbi</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>2026-01-08</v>
+        <v>Invalid Date</v>
       </c>
       <c r="M2" t="str">
-        <v>Pending</v>
+        <v/>
       </c>
       <c r="N2" t="str">
-        <v>14k</v>
+        <v/>
       </c>
       <c r="O2" t="str">
-        <v>/uploads/index_cards/indexcard-1769146086538-553986725.png</v>
+        <v>INDEX CARDS\ABALOS, LUCELLE y TUDTUD_0001.pdf</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>4121214</v>
+        <v>2006-131-132</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-29</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C3" t="str">
-        <v>shaaan</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>kroel</v>
+        <v>ABAO, ELSA y SALON a.ka. "LINDA"</v>
       </c>
       <c r="E3" t="str">
-        <v>Dauis</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>raped</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-01-13</v>
+        <v>SWINDLING</v>
       </c>
       <c r="I3" t="str">
-        <v>Atty. Doroy</v>
+        <v>R.CHATTO</v>
       </c>
       <c r="J3" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>Capitol</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-01-22</v>
+        <v/>
       </c>
       <c r="M3" t="str">
-        <v>pending</v>
+        <v/>
       </c>
       <c r="N3" t="str">
-        <v>15k</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v>N/A</v>
+        <v>INDEX CARDS\ABAO, ELSA y SALON a.ka. LINDA_0001.pdf</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>65243242</v>
+        <v>VII-14-INV-21I-202 (e-inquest)</v>
       </c>
       <c r="B4" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C4" t="str">
-        <v>emann</v>
+        <v>TAGBILARAN CITY PNP</v>
       </c>
       <c r="D4" t="str">
-        <v>clifff</v>
+        <v>ABAY-ABAY, DEXTER  BRIAN y MAKINANO</v>
       </c>
       <c r="E4" t="str">
-        <v>maribojoc</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v xml:space="preserve">tax </v>
-      </c>
-      <c r="G4" t="str">
-        <v>Invalid Date</v>
+        <v>VIOL OF ART 151 OF THE RPC</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-01-25</v>
+        <v>Invalid Date</v>
       </c>
       <c r="I4" t="str">
-        <v>Atty. Superman</v>
+        <v>ML. ENERLAS</v>
       </c>
       <c r="J4" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>tagbi</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-01-24</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>Convicted</v>
+        <v>DISMISSED 10/25/2021</v>
       </c>
       <c r="N4" t="str">
-        <v>12k</v>
+        <v/>
       </c>
       <c r="O4" t="str">
-        <v>N/A</v>
+        <v>INDEX CARDS\ABAY-ABAY, DEXTER  BRIAN y MAKINANO_0001.pdf</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>76543232</v>
+        <v>2000-868</v>
       </c>
       <c r="B5" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C5" t="str">
-        <v>namiiiii</v>
+        <v>PALMERA, MELECIO</v>
       </c>
       <c r="D5" t="str">
-        <v>chriss</v>
+        <v>ABDUL, ISMAEL</v>
       </c>
       <c r="E5" t="str">
-        <v>buol</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>raped</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H5" t="str">
-        <v>2026-01-13</v>
+        <v>GRAVE THREAT</v>
       </c>
       <c r="I5" t="str">
-        <v>Atty. Doroy</v>
+        <v>ACHAS</v>
       </c>
       <c r="J5" t="str">
-        <v>N/A</v>
+        <v>M-14217</v>
       </c>
       <c r="K5" t="str">
-        <v>Capitol</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>2026-01-22</v>
+        <v>Invalid Date</v>
       </c>
       <c r="M5" t="str">
-        <v>pending</v>
+        <v/>
       </c>
       <c r="N5" t="str">
-        <v>15k</v>
+        <v/>
       </c>
       <c r="O5" t="str">
-        <v>N/A</v>
+        <v>INDEX CARDS\ABDUL, ISMAEL_0001.pdf</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TEST-RESTORE-002</v>
+        <v>VII-14-INQ 25G-191</v>
       </c>
       <c r="B6" t="str">
-        <v>2024-01-01</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C6" t="str">
-        <v>Test Complainant 2</v>
+        <v>PIU-BOHOL</v>
       </c>
       <c r="D6" t="str">
-        <v>Test Respondent 2</v>
+        <v>ABELLANA, LESTER PAUL a.k.a "POLPOL"</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Test Offense 2</v>
+        <v>VIOL.OF section 5,Art II of R.A 9165</v>
+      </c>
+      <c r="I6" t="str">
+        <v>J.TORREGOSA</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2342323</v>
+        <v>2006-46</v>
       </c>
       <c r="B7" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C7" t="str">
-        <v>josshh</v>
+        <v/>
       </c>
       <c r="D7" t="str">
-        <v>ssds</v>
+        <v>ABING, GRACE y CINEZA</v>
       </c>
       <c r="E7" t="str">
-        <v>loboc</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>theft</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="H7" t="str">
-        <v>2026-01-07</v>
+        <v>VIOL. OF SEC. 11, ART. II, R.A. 9165</v>
       </c>
       <c r="I7" t="str">
-        <v>james</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J7" t="str">
-        <v>Reppublic Act 2104</v>
+        <v>R-13102</v>
       </c>
       <c r="K7" t="str">
-        <v>Tagbi</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>2026-01-08</v>
+        <v>Invalid Date</v>
       </c>
       <c r="M7" t="str">
-        <v>pending</v>
+        <v/>
       </c>
       <c r="N7" t="str">
-        <v>14k</v>
+        <v/>
       </c>
       <c r="O7" t="str">
-        <v>N/A</v>
+        <v>INDEX CARDS\ABING, GRACE y CINEZA_0001.pdf</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7567564</v>
+        <v>VII-14-INQ-18K-232</v>
       </c>
       <c r="B8" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C8" t="str">
-        <v>isabel</v>
+        <v>PIB-BOHOL</v>
       </c>
       <c r="D8" t="str">
-        <v>asas</v>
+        <v>ABUCAY,MARK ANTHONY y QUIZAN</v>
       </c>
       <c r="E8" t="str">
-        <v>maribojoc</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v xml:space="preserve">tax </v>
-      </c>
-      <c r="G8" t="str">
-        <v>Invalid Date</v>
+        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-01-30</v>
+        <v>Invalid Date</v>
       </c>
       <c r="I8" t="str">
-        <v>Atty. Superman</v>
+        <v>ADOLFO M. DOROY</v>
       </c>
       <c r="J8" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>tagbi</v>
-      </c>
-      <c r="L8" t="str">
-        <v>2026-01-29</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>terminated</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N8" t="str">
-        <v>12k</v>
+        <v/>
       </c>
       <c r="O8" t="str">
         <v>N/A</v>
@@ -767,31 +749,40 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TEST-2026-001</v>
+        <v>VII-14-INQ-18K-233</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-19</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C9" t="str">
-        <v>Test Complainant</v>
+        <v>PIB-BOHOL</v>
       </c>
       <c r="D9" t="str">
-        <v>Test Respondent</v>
+        <v>ABUCAY,MARK ANTHONY y QUIZAN</v>
       </c>
       <c r="E9" t="str">
-        <v>Test Address</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>Test Offense</v>
-      </c>
-      <c r="G9" t="str">
-        <v>2026-02-18</v>
+        <v>VIOL OF SEC 11,ART II OF R.A 9165</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I9" t="str">
+        <v>ADOLFO M. DOROY</v>
       </c>
       <c r="J9" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>Test Branch</v>
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
       </c>
       <c r="O9" t="str">
         <v>N/A</v>
@@ -799,83 +790,3856 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TEST-2026-002</v>
+        <v>VII-14-INV-16L-0487</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-19</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C10" t="str">
-        <v>Test Complainant</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>Test Respondent</v>
+        <v>ABUYABOR, CYRIL y UNGGAY</v>
       </c>
       <c r="E10" t="str">
-        <v>Test Address</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>Test Offense</v>
-      </c>
-      <c r="G10" t="str">
-        <v>2026-02-18</v>
+        <v>ROBBERY WITH VIOLENCE</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I10" t="str">
+        <v>L. TUYOGON</v>
       </c>
       <c r="J10" t="str">
-        <v>N/A</v>
+        <v>R-19925</v>
       </c>
       <c r="K10" t="str">
-        <v>Test Branch</v>
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
       </c>
       <c r="O10" t="str">
-        <v>N/A</v>
+        <v>INDEX CARDS\ABUYABOR, CYRIL y UNGGAY_0001.pdf</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>VII-14-INQ-22C-134</v>
+        <v>2000-644-645</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-26</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C11" t="str">
-        <v>asdasda</v>
+        <v/>
       </c>
       <c r="D11" t="str">
-        <v>asdasd</v>
+        <v>ACASO, AGUSTINE JOSEPH</v>
       </c>
       <c r="E11" t="str">
-        <v>asdasdas</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>asdasdas</v>
-      </c>
-      <c r="G11" t="str">
-        <v>2026-02-28</v>
-      </c>
-      <c r="H11" t="str">
-        <v>2026-02-25</v>
+        <v>VIOL. OF BP. BLG. 22</v>
       </c>
       <c r="I11" t="str">
-        <v>Atty. Joshua</v>
+        <v>SARIGUMBA</v>
       </c>
       <c r="J11" t="str">
-        <v>N/A</v>
+        <v>M-14133,       M-14134</v>
       </c>
       <c r="K11" t="str">
-        <v>asdasda</v>
+        <v>BR. 2</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-02-25</v>
+        <v>Invalid Date</v>
+      </c>
+      <c r="M11" t="str">
+        <v>ARCHIVED 12/29/2000</v>
       </c>
       <c r="N11" t="str">
-        <v>2322</v>
+        <v/>
       </c>
       <c r="O11" t="str">
-        <v>/uploads/index_cards/indexcard-1771488487177-586779391.png</v>
+        <v>INDEX CARDS\ACASO, AGUSTINE JOSEPH_0001.pdf</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2000-885</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v>ACEBES, GLEE</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>MALICIOUS MISCHIEF</v>
+      </c>
+      <c r="I12" t="str">
+        <v>A. MONTES</v>
+      </c>
+      <c r="J12" t="str">
+        <v>M-14222</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>INDEX CARDS\ACEBES, GLEE_0001.pdf</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>VII-14-INV-11D-00166</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C13" t="str">
+        <v>GESITA, BILLY CYRUS y SALAZAR</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ACERON, PIO</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>THEFT</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2004-07-08</v>
+      </c>
+      <c r="I13" t="str">
+        <v>A.S. RARA</v>
+      </c>
+      <c r="J13" t="str">
+        <v>R-15257</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>2004-07-15</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>INDEX CARDS\ACERON, PIO_0001.pdf</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2006-333</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v>ACERON, PIO JOHN</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>LESS SERIOUS PHYSICAL INJURIES</v>
+      </c>
+      <c r="I14" t="str">
+        <v>(J. SALISE)              C. SUPREMO</v>
+      </c>
+      <c r="J14" t="str">
+        <v>R-13245</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Undergo Diversion Com. Program</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>INDEX CARDS\ACERON, PIO JOHN_0001.pdf</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2004-85</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>ACERON, RODEL</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>MALICIOUS MISCHIEF</v>
+      </c>
+      <c r="I15" t="str">
+        <v>J. SALISE</v>
+      </c>
+      <c r="J15" t="str">
+        <v>M-15804</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v>INDEX CARDS\ACERON, RODEL_0001.pdf</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2005-399-401</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v>ACHAS, WILMA</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>ESTAFA (UNDER PAR. 1 (B) 315)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>R. CHATTO</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>DROPPED 8/16/2005</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v>INDEX CARDS\ACHAS, WILMA_0001.pdf</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2003-630</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>ACMAZAN, CHITO y PAZ</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>GRAVE THREAT</v>
+      </c>
+      <c r="I17" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J17" t="str">
+        <v>M-15564</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v>INDEX CARDS\ACMAZAN, CHTIO y PAZ_0001.pdf</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2000-199</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>ACTOB, RYAN a.ka. "BRIAN"</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>MURDER</v>
+      </c>
+      <c r="I18" t="str">
+        <v>MIGRIÑO</v>
+      </c>
+      <c r="J18" t="str">
+        <v>R-10583</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v>INDEX CARDS\ACTOB, RYAN a.ka. BRIAN_0001.pdf</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2002-1058</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>ADANO, CATALINO O.</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>VIOL. OF R.A. 8282</v>
+      </c>
+      <c r="I19" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J19" t="str">
+        <v>M-15259</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v>INDEX CARDS\ADANO, CATALINO O._0001.pdf</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2007-301</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>ADAPTAR, BENITO y BULLECER</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>THEFT</v>
+      </c>
+      <c r="I20" t="str">
+        <v>N. CAFÉ-UY</v>
+      </c>
+      <c r="J20" t="str">
+        <v>M-16963</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v>INDEX CARDS\ADAPTAR, BENITO y BULLECER_0001.pdf</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2005-862</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>AGAS, ERNESTO F. (P/SUPT.)</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>VIOL. OF ART. 125 OF THE RPC</v>
+      </c>
+      <c r="I21" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2005-863</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>AGAS, ERNESTO F. (P/SUPT.)</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>VIOL. OF R.A. 7438</v>
+      </c>
+      <c r="I22" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2000-472</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>AGBAYANI, DOLORES / SHOPPER'S MART</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>VIOL. OF SPECIAL SECURITY ACT OF 1997</v>
+      </c>
+      <c r="I23" t="str">
+        <v>MIGRIÑO</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>REFERRED TO SSS, TAGB. CITY BRANCH 9/10/2000</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>INDEX CARDS\AGBAYANI, DOLORES  SHOPPER'S MART_0001.pdf</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>VII-14-INV-16I-0338-0341</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C24" t="str">
+        <v>MARASIGAN, JOSE</v>
+      </c>
+      <c r="D24" t="str">
+        <v>AGENAR, GEORGE &amp; AGENAR, MARY JUDITH</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>TRESPASS TO DWELLING, CARNAPPING, THEFT AND MALICIOUS MISCHIEF</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I24" t="str">
+        <v>ML. ENERLAS</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>INDEX CARDS\AGENAR, GEORGE &amp; AGENAR, MARY JUDITH_0001.pdf</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>VII-14-INQ-14H-0175</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>AGOSTA, MARVIN y ILOY</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>VIOL. OF R.A. 9187</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I25" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J25" t="str">
+        <v>R-16944</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>INDEX CARDS\AGOSTA, MARVIN y ILOY_0001.pdf</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>VII-14-INV-09H-00317</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v xml:space="preserve">AGUAVIVA, CRISTITO, JR. </v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>SLIGHT PHYSICAL INJURIES</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I26" t="str">
+        <v>N. CAFÉ-UY</v>
+      </c>
+      <c r="J26" t="str">
+        <v>M-17568</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>INDEX CARDS\AGUAVIVA, CRISTITO, JR._0001.pdf</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>VII-14-INV-13A-00031</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>AGULLES, HERMAN</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>QUALIFIED THEFT</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I27" t="str">
+        <v>F.R. MATUOD</v>
+      </c>
+      <c r="J27" t="str">
+        <v>R-16153</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>AHAT, RIO</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>VII-14-INV-21K-563</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C28" t="str">
+        <v>MEIJA, EVELYN P.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>AGUIPO, IRENE H.</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>ESTAFA PUNISHABLE UNDER ARTICLE 315, SUBSECTION 2 PAR. (A) OF RPC IN REL. TO R.A. 10175</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I28" t="str">
+        <v>A. SELMA</v>
+      </c>
+      <c r="J28" t="str">
+        <v>R-25708</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>VII-14-INV-21K-564</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C29" t="str">
+        <v>MEIJA, EVELYN P.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>AGUIPO, IRENE H.</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>VIOL. OF SEC. 28 IN REL. TO SEC. 73 OF R.A. 8799</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I29" t="str">
+        <v>A. SELMA</v>
+      </c>
+      <c r="J29" t="str">
+        <v>R-25709</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2005-868</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>AHAT, RIO</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>RESISTANCE &amp; DISOBEDIENCE OF PERSON IN AUTHORITY</v>
+      </c>
+      <c r="I30" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J30" t="str">
+        <v>R-13031</v>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M30" t="str">
+        <v>WITHDRAWN 1/20/2006 CASE FALLS W/ IN THE JURISDICTION OF FAMILY COURT</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>INDEX CARDS\AHAT, RIO_0001.pdf</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>VII-14-INQ-12D-062</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2004-10-09</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>AHAT, RIO y ANDALES</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>VIOL. OF SEC 2, ART. II OF R.A. 9165</v>
+      </c>
+      <c r="H31" t="str">
+        <v>2004-10-29</v>
+      </c>
+      <c r="I31" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J31" t="str">
+        <v>R-15685</v>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>INDEX CARDS\AHAT, RIO y ANDALES 062_0001.pdf</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>VII-14-INQ-12D-061</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2004-10-09</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>AHAT, RIO y ANDALES</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>VIOL. OF SEC 5, ART. II OF R.A. 9165</v>
+      </c>
+      <c r="H32" t="str">
+        <v>2004-10-29</v>
+      </c>
+      <c r="I32" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J32" t="str">
+        <v>R-15684</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>INDEX CARDS\AHAT, RIO y ANDALES 061_0001_0001.pdf</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>VII-14-INQ-14E-117</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>ALAGADI, MARCOS</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>VIOL. OF SEC. 11, ART. II OF R.A. 9165</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I33" t="str">
+        <v>F.R. MATUOD</v>
+      </c>
+      <c r="J33" t="str">
+        <v>R-16847</v>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>VII-14-INQ-14E-118</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>ALAGADI, MARCOS</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>VIOL. OF SEC. 12, ART. II OF R.A. 9165</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I34" t="str">
+        <v>F.R. MATUOD</v>
+      </c>
+      <c r="J34" t="str">
+        <v>R-16848</v>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2004-345-349</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>ALAGO, LILIBETH</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>VIOL. OF BP. BLG. 22</v>
+      </c>
+      <c r="I35" t="str">
+        <v>CRISTOBAL</v>
+      </c>
+      <c r="J35" t="str">
+        <v>M-15914-15918</v>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v>INDEX CARDS\ALAGO, LILIBETH_0001.pdf</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>VII-14-INQ-22D-078</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C36" t="str">
+        <v>PNP, TAGBILARAN CITY</v>
+      </c>
+      <c r="D36" t="str">
+        <v>ALANGADI, CASANODING y SULTAN</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>VIOL. OF SEC. 7, ART. II OF R.A. 9165</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I36" t="str">
+        <v>J. TORREGOSA</v>
+      </c>
+      <c r="J36" t="str">
+        <v>R-25796</v>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v>INDEX CARDS\ALANGADI, CASANODING y SULTAN 078_0001.pdf</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>VII-14-INQ-21K-245</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C37" t="str">
+        <v>PNP, TAGBILARAN CITY</v>
+      </c>
+      <c r="D37" t="str">
+        <v>ALAPAN, KENNETH y ALBARICO</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>VIOL. OF SEC. P.D. 1602 (PRESCRIBING STIFFER PENALTIES IN ILLEGAL GAMBLING)</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I37" t="str">
+        <v>F.R. MATUOD</v>
+      </c>
+      <c r="J37" t="str">
+        <v>M-20677</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v>INDEX CARDS\ALAPAN, KENNETH y ALBARICO_0001.pdf</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>VII-14-INV-12F-0286</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v>ALBARADO, SERVILLA y MAMBAJEN</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>VIOL. OF PD 1602</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I38" t="str">
+        <v>R. CHATTO</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M38" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v>INDEX CARDS\ALBARADO, SERVILLA y MAMBAJEN_0001.pdf</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>VII-14-INQ-16I-0391</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C39" t="str">
+        <v>OLAIVAR, N. (PSUPT.)</v>
+      </c>
+      <c r="D39" t="str">
+        <v>ALBERIO, CARLO y GALZIM</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>VIOL. OF SEC. 11, ART. II, R.A. 9165</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I39" t="str">
+        <v>C. GAMAS</v>
+      </c>
+      <c r="J39" t="str">
+        <v>R-19325</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v>INDEX CARDS\ALBERIO, CARLO y GALZIM_0001.pdf</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2005-778-781</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v>ALBIENDA, LILIAN y BUICO</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>ESTAFA</v>
+      </c>
+      <c r="I40" t="str">
+        <v>J. SALISE</v>
+      </c>
+      <c r="J40" t="str">
+        <v>R-13036,         R-13037</v>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M40" t="str">
+        <v>780-781 DISMISSED 1/17/2005</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v>INDEX CARDS\ALBIENDA, LILIAN y BUICO_0001.pdf</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2006-27</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v>ALBIOS, SEVERINO y CABANG</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>LESS SERIOUS PHYSICAL INJURIES</v>
+      </c>
+      <c r="I41" t="str">
+        <v>N. CAFÉ-UY</v>
+      </c>
+      <c r="J41" t="str">
+        <v>M-16465</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v>INDEX CARDS\ALBIOS, SEVERINO y CABANG_0001.pdf</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>VII-14-INV-11C-00118</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2004-06-19</v>
+      </c>
+      <c r="C42" t="str">
+        <v>GALICIA, ROSALINA / EDUARTE, MARCELA</v>
+      </c>
+      <c r="D42" t="str">
+        <v>ALDEPOLLA, IGNACIO</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>FALSIFICATION OF PUBLIC DOCUMENTS</v>
+      </c>
+      <c r="I42" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M42" t="str">
+        <v>DISMISSED 6/6/2011</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v>INDEX CARDS\ALDEPOLLA, IGNACIO_0001.pdf</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>VII-14-INV-13G-0269</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v xml:space="preserve">ABING, MOISES  </v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>GRAVE THREATS /GRAVE COERCION LIGHT THREATS</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I43" t="str">
+        <v>M.ANORA</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N43" t="str">
+        <v>B.R 2</v>
+      </c>
+      <c r="O43" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2006-572</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v>ABLAN, MA. ANABELLE y NOPAL</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>RECKLESS IMPRUDENCE RE TO SERIOUS PHYSICAL INJURIES</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I44" t="str">
+        <v>N. CRISTOBAL</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>DROPPED</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2002-659,660,661</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v>ABLANQUE, SOCRATES</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>ESTAFA &amp; OR VIOL OF BP 22</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I45" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>WITHDRAWN</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>VII-14-INQ--16C-090</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C46" t="str">
+        <v>NBI-ATYY ALBAO</v>
+      </c>
+      <c r="D46" t="str">
+        <v>ABOYADOR,MARK JOSEPH</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>VIOL OF SEC 11,ART II, R.A 9165</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I46" t="str">
+        <v>G. LIM</v>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>VII-14-INQ-16C-091</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C47" t="str">
+        <v>NBI-ATTY ALBAO</v>
+      </c>
+      <c r="D47" t="str">
+        <v>ABOYADOR,MARK JOSEPH</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>VIOL OF SEC 12,R.A II,9165</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I47" t="str">
+        <v>G. LIM</v>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>VII-14-INQ-16C 092</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C48" t="str">
+        <v>NBI-ATTY ALBAO</v>
+      </c>
+      <c r="D48" t="str">
+        <v>ABOYADOR,,ARK JOSEPH y TORREMOCHA</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>VIOL OF SEC 15,ART II R.A 9165</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I48" t="str">
+        <v>G. LIM</v>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2006-177</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C49" t="str">
+        <v/>
+      </c>
+      <c r="D49" t="str">
+        <v>ABRAU, BENJIE</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>THEFT</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I49" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>DIVERSION PROCEEDINGSAT KATARUNGANG BRGY. OF S.BULLONES,BOHOL BR. 1</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2003-178</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v>ABRAU, BENJIE</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>TRESPASS TO DWELLING</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I50" t="str">
+        <v>A.S RARA</v>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>DROPPED</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2006-583</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v>ABRAU,EMMANUEL y DELA CRUZ</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>VIOL OF R.A 9262 (VAWC)</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I51" t="str">
+        <v>N. CRISTOBAL</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>DROPPED</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2000-690,691</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v xml:space="preserve">ABALO, JANICE  B. </v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v xml:space="preserve">ALARSON W/ SCANDAL,RESISTANCE W/DISOBEDIENCE TO A PERSON IN AUTHORITY </v>
+      </c>
+      <c r="H52" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I52" t="str">
+        <v>MIGRINO</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2008-201</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v>ABDALA,JUANITO A.K.A JORDAN</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>VIOL OF ART 281 OF THE RPC</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I53" t="str">
+        <v>N. UY</v>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>WITHDRWAN</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2003- OF R.A 761</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v>ABDUL, ISMAEL</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>VIOL OF R.A 761</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I54" t="str">
+        <v>MONTES</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>DROPPED</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2008-120</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v>ABEJARON, PACIANA</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>FALSIFICATION OF PUBLIC DOCUMENT</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I55" t="str">
+        <v>N. CAFE</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2008-0120</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>ABEJARON, EULALIO</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>FALSIFICATION OF PUBLIC DOCUMENT</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I56" t="str">
+        <v>N. IU</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>VII-14-INV-23I-410</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C57" t="str">
+        <v>ANALYN CALAMBA BAUTISTA</v>
+      </c>
+      <c r="D57" t="str">
+        <v>ABEJARON,MARY JANE</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>ESTAFA underART 315 par 2,sub parag (a) of the revised penal code as amended by r.a 10951</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I57" t="str">
+        <v>JOSIE SEMPRON</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>VII-14-INV-23i -410</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C58" t="str">
+        <v>ANALYN CALAMBA BAUTISTA</v>
+      </c>
+      <c r="D58" t="str">
+        <v>ABEJARON, MARY JANE</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>VIOL OF COMMONWEALTH ACT NO 142</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I58" t="str">
+        <v>JOSIE SEMPRON</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2007 - 472</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>ABEJARON, RJ y OMLERO</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v xml:space="preserve">RESISTANCE &amp; DISOBEDIENCE TO AN AGENT IN AUTHORITY </v>
+      </c>
+      <c r="H59" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I59" t="str">
+        <v>R. CHATTO</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N59" t="str">
+        <v>1 MS &amp; 15 DAYS OF ARRESTO MAYOR &amp; TO PAYA FINE OF 200.00 W/ ALL  THE ACCESORY PENALTIES  &amp; TO PAY THE COST</v>
+      </c>
+      <c r="O59" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2007-473</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>ABEJARON, RJ y OMLERO</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>VIOL OF BP BLG. 22</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I60" t="str">
+        <v>R. CHATTO</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N60" t="str">
+        <v>IMPRISONMENT OF 1 MONTH &amp; TO PAY THE COST</v>
+      </c>
+      <c r="O60" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2007-474</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>ABEJARON,RJ y OMLERO</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>LESS SERIOUS PHYSICAL INJURIES</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I61" t="str">
+        <v>R. CHATTO</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N61" t="str">
+        <v>1 MOS &amp;  15 DAYS ARRESTO MAYOR &amp; TO PRIVATE COMPLAIN ANT THE AMOUNT OF 2000.00 AS CIVILM LIABILITY</v>
+      </c>
+      <c r="O61" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2006-789</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v>ABEJARON, RJ y OMLERO</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>VIOL OF B.P BLG. 6</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I62" t="str">
+        <v>A.S RARA</v>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N62" t="str">
+        <v>IMPRISONMENT OF 4 MONTHS &amp; TO PAY THE COST</v>
+      </c>
+      <c r="O62" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2006-638</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>ABEJARON, RJ y OMLERO</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>VIOL OF  B.P BLG 6</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I63" t="str">
+        <v>N, UY</v>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N63" t="str">
+        <v>IMPRISONMENT OF 2 MOS. AND TO PAY THE COST</v>
+      </c>
+      <c r="O63" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2005-170</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v>ABEJARON, ARGIE y OMLERO</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>ATTEMPTED ROBBERY</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2005-171</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v>ABEJARON, ARGIE y OMLERO</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>SLIGHT PHYSICAL INJURIES</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>VII-14-INV-16A-044</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C66" t="str">
+        <v>TRANSITO E. TUYOGON</v>
+      </c>
+      <c r="D66" t="str">
+        <v>ABEJO, SANDY</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>ESTAFA (ART.315 (1) ( B) OF RPC</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I66" t="str">
+        <v>F. MATUOD</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2005-566</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v>ABELLA, LEONARDO y YAP</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>VIOL OF SSS LAW</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I67" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>DROPPED</v>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>VII-14-INV-14A-018</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v xml:space="preserve">ABELLANA, BENJAMIN A. </v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>VIOL OF SEC 22(a) IN REL TO SEC.28 (E) OF R.A 1161,as amended by R.A 8282</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I68" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>VII-14-INV-09D-00108</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v>ABELLANA,CHARLENE MARIE</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>FRUSTRATED MURDER</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I69" t="str">
+        <v>A.S. RARA</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2008-329</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v>ABELLANA, DANILO</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>LIBEL</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I70" t="str">
+        <v>R. CHATTO</v>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>VII-14=-INV-14A-018</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v xml:space="preserve">ABELLANA,JEAN ARLENE C. </v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>VIOL OF R.A 1161 AS AMENDED BY R.A 8282</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I71" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>VII-14-INQ-15K-0168</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>ABELLANA,JOANNE CLAIRE</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>VIOL OF SEC11,ART II,OF R.A 9165</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I72" t="str">
+        <v>F. MATUOD</v>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N72" t="str">
+        <v>LIFE IMPRISONMENT ANA A FINE OF 400,00.00 PEOS</v>
+      </c>
+      <c r="O72" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>VII-14-INQ-13J-0188</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
+      </c>
+      <c r="D73" t="str">
+        <v>ABELLANA, LESTER PAUL @ POLPOL</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>VIOL OF R.A 10591 (ILLEGAL POSSESION OF HIGH POWERED FIREARM)</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I73" t="str">
+        <v>F. MATUOD</v>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>VII-14--INQ-13J-0189</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>ABELLANA,LESTER PAUL</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>VIOL OF SEC 2,ART II,R.A 9165</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I74" t="str">
+        <v>F. MATUOD</v>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>VII-14-INQ-13J-0190</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>ABELLANA,LESTER PAUL</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>VIOL OF SEC12,ART. II, R.A 9165</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I75" t="str">
+        <v>F. MATUOD</v>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>VII-14-INQ-13J-0187</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v>ABELLANA,LESTER PAUL</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>VIOL OF SEC 5,ART. II, R.A 9165</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I76" t="str">
+        <v>M. ANORA</v>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2004-718,719</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v>ABELLANA,MIGUEL</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>VIOL OF B.P 22</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I77" t="str">
+        <v>N. UY</v>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2004-721</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v>ABELLANA,MIGUEL</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>VIOL OF B.P 22</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I78" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2004-720</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>ABELLANA,MIGUEL</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>VIOL OF BP 22</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I79" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2004-173</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v>ABRAU, JOEL</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>ESTAFA</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I80" t="str">
+        <v>N. CRISTOBAL</v>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v>WITHDRAWN</v>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>VII-14-INV-010A-00042</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v>ABRAU,MARIETTA</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>VIOL OF BP BLG. 22</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I81" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>VII-14-INV-010A-00043</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v>ABRAU,MARIETTA</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>VIOL OF BP BLG. 22</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I82" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>VII-14-INV-010A-00044</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v>ABRAU, MARIETTA</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v>VIOL OF BP BLG 22</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I83" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>VII-14-INV-010A-00045</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v>ABRAU, MARIETTA</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>VIOL OF BP BLG. 22</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I84" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>VI--14-INV-010A-00046</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v>ABRAU,MARIETTA</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>VIOL OF BP BLG 22</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I85" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>VII-14-INV-010A-00047</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v>ABRAU, MARIETTA</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>VIOL OF BP BLG 22</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I86" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>VII-14-INV-010A-00048</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v>ABRAU, MARIETTA</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>VIOL OF BP BLG 22</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I87" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>VII-14-INV-010A-00049</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v>ABRAU, MARIETTA</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>VIOL OF BP BLG 22</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I88" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>VII-14-INV-010A-00050</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
+        <v>ABRAU, MARIETTA</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>VIOL OF BP BLG 22</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I89" t="str">
+        <v>C. SUPREMO</v>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v>ACQUITTED</v>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>VII-14-INV-091-00394</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v>ABRAU, RUEL y AGAHAP</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>VIOL OF SEC 5,(A) OF R.A 9262</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I90" t="str">
+        <v>N. CRISTOBAL</v>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>99-1028</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91" t="str">
+        <v>ABREGANA,CARMELITA</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>VIOL OF P.D 1866 AS AMENDED</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I91" t="str">
+        <v>A. RARA</v>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2004-718 , 719</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v>ABELLANA,MIGUEL</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>VIOL OF B.P 22</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I92" t="str">
+        <v>N. UY</v>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2004 - 721</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>VIOL OF B.P 22</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I93" t="str">
+        <v>N. UY</v>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2004 - 720</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v>ABELLANA,MIGUEL</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>VIOL OF B.P 22</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I94" t="str">
+        <v>N. UY</v>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>VII-14-INV-14B-089</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95" t="str">
+        <v>ABREGANA,JAMES y NATAD</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>VIOL R.A 7610 (CHILD ABUSE)</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I95" t="str">
+        <v>M. ANORA</v>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v>PROV.DISMISSED</v>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>VII-14INQ-16F-0170</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C96" t="str">
+        <v>MAREJIN AGUILAR</v>
+      </c>
+      <c r="D96" t="str">
+        <v>ABREGO,RODEL y ACHAPERO</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>THEFT</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I96" t="str">
+        <v>B. BAUTISTA</v>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>VII-14-INQ-15L-0191</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C97" t="str">
+        <v>GERALD MARMITO</v>
+      </c>
+      <c r="D97" t="str">
+        <v>ABREGO,RODEL y ACHAPERO</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>ROBBERY WITH FORCE UPON THINGS</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I97" t="str">
+        <v>S. BULLONES</v>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>VII-14-INQ-16D-0114</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C98" t="str">
+        <v>PSUPT. VALE</v>
+      </c>
+      <c r="D98" t="str">
+        <v>ABREGO, RODEL y ACHAPERO</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>VIOL OF B.P BLG 6</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I98" t="str">
+        <v>C. GAMAS</v>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N98" t="str">
+        <v>METED A FIN EOF 200.00 W/ SUBSIDIARY IMPRISONMENT IN CAE OF INSOLVENCY &amp; TO PAY THE COST OF SUIT</v>
+      </c>
+      <c r="O98" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>VII-14-INQ-141-0177</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v>ABREGO,RODEL y ACHAPERO</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>VIOL OF B.P BLG 22</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I99" t="str">
+        <v>F. MATUOD</v>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>VII-14-INQ-16F-0204</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C100" t="str">
+        <v>PSUPT. G. VALE</v>
+      </c>
+      <c r="D100" t="str">
+        <v>ABUCAY, JOEL y TAN</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>VIOL OF SEC 11,ART. R.A 9165</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I100" t="str">
+        <v>M. ANORA</v>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v>CONVICTED</v>
+      </c>
+      <c r="N100" t="str">
+        <v>1 YEAR TO PAY A FINE OF 10,000.00</v>
+      </c>
+      <c r="O100" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>VII-14-INQ-22H-152</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C101" t="str">
+        <v>RDE-UNIT 7</v>
+      </c>
+      <c r="D101" t="str">
+        <v>ABUCAY,NOE y CABALLO</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I101" t="str">
+        <v>GLENA LIM</v>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>VII-14-INQ-22H-153</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C102" t="str">
+        <v>RDE-UNIT 7</v>
+      </c>
+      <c r="D102" t="str">
+        <v>ABUCAY,NOE y CABALLO</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="I102" t="str">
+        <v>GLENA LIM</v>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v>DISMISSED</v>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:P103"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -413,7 +413,8 @@
     <col min="12" max="12" width="15.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="50.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,6 +461,9 @@
         <v>Penalty</v>
       </c>
       <c r="O1" t="str">
+        <v>Decision Date</v>
+      </c>
+      <c r="P1" t="str">
         <v>Index Cards</v>
       </c>
     </row>
@@ -503,7 +507,7 @@
       <c r="N2" t="str">
         <v/>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>INDEX CARDS\ABALOS, LUCELLE y TUDTUD_0001.pdf</v>
       </c>
     </row>
@@ -541,7 +545,7 @@
       <c r="N3" t="str">
         <v/>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>INDEX CARDS\ABAO, ELSA y SALON a.ka. LINDA_0001.pdf</v>
       </c>
     </row>
@@ -582,133 +586,118 @@
       <c r="N4" t="str">
         <v/>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>INDEX CARDS\ABAY-ABAY, DEXTER  BRIAN y MAKINANO_0001.pdf</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2000-868</v>
+        <v>VII-14-INQ 25G-191</v>
       </c>
       <c r="B5" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C5" t="str">
-        <v>PALMERA, MELECIO</v>
+        <v>PIU-BOHOL</v>
       </c>
       <c r="D5" t="str">
-        <v>ABDUL, ISMAEL</v>
+        <v>ABELLANA, LESTER PAUL a.k.a "POLPOL"</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>GRAVE THREAT</v>
+        <v>VIOL.OF section 5,Art II of R.A 9165</v>
       </c>
       <c r="I5" t="str">
-        <v>ACHAS</v>
+        <v>J.TORREGOSA</v>
       </c>
       <c r="J5" t="str">
-        <v>M-14217</v>
+        <v/>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
-      <c r="L5" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
         <v/>
       </c>
-      <c r="O5" t="str">
-        <v>INDEX CARDS\ABDUL, ISMAEL_0001.pdf</v>
+      <c r="P5" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VII-14-INQ 25G-191</v>
+        <v>2006-46</v>
       </c>
       <c r="B6" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C6" t="str">
-        <v>PIU-BOHOL</v>
+        <v/>
       </c>
       <c r="D6" t="str">
-        <v>ABELLANA, LESTER PAUL a.k.a "POLPOL"</v>
+        <v>ABING, GRACE y CINEZA</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>VIOL.OF section 5,Art II of R.A 9165</v>
+        <v>VIOL. OF SEC. 11, ART. II, R.A. 9165</v>
       </c>
       <c r="I6" t="str">
-        <v>J.TORREGOSA</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>R-13102</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
+      <c r="L6" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M6" t="str">
         <v/>
       </c>
       <c r="N6" t="str">
         <v/>
       </c>
-      <c r="O6" t="str">
-        <v>N/A</v>
+      <c r="P6" t="str">
+        <v>INDEX CARDS\ABING, GRACE y CINEZA_0001.pdf</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2006-46</v>
+        <v>VII-14-INQ-18K-232</v>
       </c>
       <c r="B7" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>PIB-BOHOL</v>
       </c>
       <c r="D7" t="str">
-        <v>ABING, GRACE y CINEZA</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
+        <v>ABUCAY,MARK ANTHONY y QUIZAN</v>
       </c>
       <c r="F7" t="str">
-        <v>VIOL. OF SEC. 11, ART. II, R.A. 9165</v>
+        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
       </c>
       <c r="I7" t="str">
-        <v>R. CHATTO</v>
-      </c>
-      <c r="J7" t="str">
-        <v>R-13102</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>Invalid Date</v>
+        <v>ADOLFO M. DOROY</v>
       </c>
       <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v>INDEX CARDS\ABING, GRACE y CINEZA_0001.pdf</v>
+        <v>ACQUITTED</v>
+      </c>
+      <c r="P7" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>VII-14-INQ-18K-232</v>
+        <v>VII-14-INQ-18K-233</v>
       </c>
       <c r="B8" t="str">
         <v>Invalid Date</v>
@@ -723,7 +712,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
+        <v>VIOL OF SEC 11,ART II OF R.A 9165</v>
       </c>
       <c r="H8" t="str">
         <v>Invalid Date</v>
@@ -743,54 +732,57 @@
       <c r="N8" t="str">
         <v/>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>VII-14-INQ-18K-233</v>
+        <v>VII-14-INV-16L-0487</v>
       </c>
       <c r="B9" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C9" t="str">
-        <v>PIB-BOHOL</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>ABUCAY,MARK ANTHONY y QUIZAN</v>
+        <v>ABUYABOR, CYRIL y UNGGAY</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>VIOL OF SEC 11,ART II OF R.A 9165</v>
+        <v>ROBBERY WITH VIOLENCE</v>
       </c>
       <c r="H9" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I9" t="str">
-        <v>ADOLFO M. DOROY</v>
+        <v>L. TUYOGON</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>R-19925</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
+      <c r="L9" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M9" t="str">
-        <v>ACQUITTED</v>
+        <v/>
       </c>
       <c r="N9" t="str">
         <v/>
       </c>
-      <c r="O9" t="str">
-        <v>N/A</v>
+      <c r="P9" t="str">
+        <v>INDEX CARDS\ABUYABOR, CYRIL y UNGGAY_0001.pdf</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>VII-14-INV-16L-0487</v>
+        <v>2000-644-645</v>
       </c>
       <c r="B10" t="str">
         <v>Invalid Date</v>
@@ -799,42 +791,39 @@
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>ABUYABOR, CYRIL y UNGGAY</v>
+        <v>ACASO, AGUSTINE JOSEPH</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>ROBBERY WITH VIOLENCE</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Invalid Date</v>
+        <v>VIOL. OF BP. BLG. 22</v>
       </c>
       <c r="I10" t="str">
-        <v>L. TUYOGON</v>
+        <v>SARIGUMBA</v>
       </c>
       <c r="J10" t="str">
-        <v>R-19925</v>
+        <v>M-14133,       M-14134</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>BR. 2</v>
       </c>
       <c r="L10" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>ARCHIVED 12/29/2000</v>
       </c>
       <c r="N10" t="str">
         <v/>
       </c>
-      <c r="O10" t="str">
-        <v>INDEX CARDS\ABUYABOR, CYRIL y UNGGAY_0001.pdf</v>
+      <c r="P10" t="str">
+        <v>INDEX CARDS\ACASO, AGUSTINE JOSEPH_0001.pdf</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2000-644-645</v>
+        <v>2000-885</v>
       </c>
       <c r="B11" t="str">
         <v>Invalid Date</v>
@@ -843,66 +832,69 @@
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>ACASO, AGUSTINE JOSEPH</v>
+        <v>ACEBES, GLEE</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>VIOL. OF BP. BLG. 22</v>
+        <v>MALICIOUS MISCHIEF</v>
       </c>
       <c r="I11" t="str">
-        <v>SARIGUMBA</v>
+        <v>A. MONTES</v>
       </c>
       <c r="J11" t="str">
-        <v>M-14133,       M-14134</v>
+        <v>M-14222</v>
       </c>
       <c r="K11" t="str">
-        <v>BR. 2</v>
+        <v/>
       </c>
       <c r="L11" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="M11" t="str">
-        <v>ARCHIVED 12/29/2000</v>
+        <v/>
       </c>
       <c r="N11" t="str">
         <v/>
       </c>
-      <c r="O11" t="str">
-        <v>INDEX CARDS\ACASO, AGUSTINE JOSEPH_0001.pdf</v>
+      <c r="P11" t="str">
+        <v>INDEX CARDS\ACEBES, GLEE_0001.pdf</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2000-885</v>
+        <v>VII-14-INV-11D-00166</v>
       </c>
       <c r="B12" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>GESITA, BILLY CYRUS y SALAZAR</v>
       </c>
       <c r="D12" t="str">
-        <v>ACEBES, GLEE</v>
+        <v>ACERON, PIO</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>MALICIOUS MISCHIEF</v>
+        <v>THEFT</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2004-07-08</v>
       </c>
       <c r="I12" t="str">
-        <v>A. MONTES</v>
+        <v>A.S. RARA</v>
       </c>
       <c r="J12" t="str">
-        <v>M-14222</v>
+        <v>R-15257</v>
       </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Invalid Date</v>
+        <v>2004-07-15</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -910,43 +902,40 @@
       <c r="N12" t="str">
         <v/>
       </c>
-      <c r="O12" t="str">
-        <v>INDEX CARDS\ACEBES, GLEE_0001.pdf</v>
+      <c r="P12" t="str">
+        <v>INDEX CARDS\ACERON, PIO_0001.pdf</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>VII-14-INV-11D-00166</v>
+        <v>2004-85</v>
       </c>
       <c r="B13" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C13" t="str">
-        <v>GESITA, BILLY CYRUS y SALAZAR</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>ACERON, PIO</v>
+        <v>ACERON, RODEL</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>THEFT</v>
-      </c>
-      <c r="H13" t="str">
-        <v>2004-07-08</v>
+        <v>MALICIOUS MISCHIEF</v>
       </c>
       <c r="I13" t="str">
-        <v>A.S. RARA</v>
+        <v>J. SALISE</v>
       </c>
       <c r="J13" t="str">
-        <v>R-15257</v>
+        <v>M-15804</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>2004-07-15</v>
+        <v>Invalid Date</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -954,13 +943,13 @@
       <c r="N13" t="str">
         <v/>
       </c>
-      <c r="O13" t="str">
-        <v>INDEX CARDS\ACERON, PIO_0001.pdf</v>
+      <c r="P13" t="str">
+        <v>INDEX CARDS\ACERON, RODEL_0001.pdf</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2006-333</v>
+        <v>2005-399-401</v>
       </c>
       <c r="B14" t="str">
         <v>Invalid Date</v>
@@ -969,39 +958,36 @@
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>ACERON, PIO JOHN</v>
+        <v>ACHAS, WILMA</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>LESS SERIOUS PHYSICAL INJURIES</v>
+        <v>ESTAFA (UNDER PAR. 1 (B) 315)</v>
       </c>
       <c r="I14" t="str">
-        <v>(J. SALISE)              C. SUPREMO</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J14" t="str">
-        <v>R-13245</v>
+        <v/>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
-      <c r="L14" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="M14" t="str">
-        <v>Undergo Diversion Com. Program</v>
+        <v>DROPPED 8/16/2005</v>
       </c>
       <c r="N14" t="str">
         <v/>
       </c>
-      <c r="O14" t="str">
-        <v>INDEX CARDS\ACERON, PIO JOHN_0001.pdf</v>
+      <c r="P14" t="str">
+        <v>INDEX CARDS\ACHAS, WILMA_0001.pdf</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2004-85</v>
+        <v>2003-630</v>
       </c>
       <c r="B15" t="str">
         <v>Invalid Date</v>
@@ -1010,19 +996,19 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>ACERON, RODEL</v>
+        <v>ACMAZAN, CHITO y PAZ</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>MALICIOUS MISCHIEF</v>
+        <v>GRAVE THREAT</v>
       </c>
       <c r="I15" t="str">
-        <v>J. SALISE</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J15" t="str">
-        <v>M-15804</v>
+        <v>M-15564</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -1036,13 +1022,13 @@
       <c r="N15" t="str">
         <v/>
       </c>
-      <c r="O15" t="str">
-        <v>INDEX CARDS\ACERON, RODEL_0001.pdf</v>
+      <c r="P15" t="str">
+        <v>INDEX CARDS\ACMAZAN, CHTIO y PAZ_0001.pdf</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2005-399-401</v>
+        <v>2000-199</v>
       </c>
       <c r="B16" t="str">
         <v>Invalid Date</v>
@@ -1051,36 +1037,39 @@
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>ACHAS, WILMA</v>
+        <v>ACTOB, RYAN a.ka. "BRIAN"</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>ESTAFA (UNDER PAR. 1 (B) 315)</v>
+        <v>MURDER</v>
       </c>
       <c r="I16" t="str">
-        <v>R. CHATTO</v>
+        <v>MIGRIÑO</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>R-10583</v>
       </c>
       <c r="K16" t="str">
         <v/>
       </c>
+      <c r="L16" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M16" t="str">
-        <v>DROPPED 8/16/2005</v>
+        <v/>
       </c>
       <c r="N16" t="str">
         <v/>
       </c>
-      <c r="O16" t="str">
-        <v>INDEX CARDS\ACHAS, WILMA_0001.pdf</v>
+      <c r="P16" t="str">
+        <v>INDEX CARDS\ACTOB, RYAN a.ka. BRIAN_0001.pdf</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2003-630</v>
+        <v>2002-1058</v>
       </c>
       <c r="B17" t="str">
         <v>Invalid Date</v>
@@ -1089,19 +1078,19 @@
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>ACMAZAN, CHITO y PAZ</v>
+        <v>ADANO, CATALINO O.</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>GRAVE THREAT</v>
+        <v>VIOL. OF R.A. 8282</v>
       </c>
       <c r="I17" t="str">
         <v>B. BAUTISTA</v>
       </c>
       <c r="J17" t="str">
-        <v>M-15564</v>
+        <v>M-15259</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1115,13 +1104,13 @@
       <c r="N17" t="str">
         <v/>
       </c>
-      <c r="O17" t="str">
-        <v>INDEX CARDS\ACMAZAN, CHTIO y PAZ_0001.pdf</v>
+      <c r="P17" t="str">
+        <v>INDEX CARDS\ADANO, CATALINO O._0001.pdf</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2000-199</v>
+        <v>2007-301</v>
       </c>
       <c r="B18" t="str">
         <v>Invalid Date</v>
@@ -1130,19 +1119,19 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>ACTOB, RYAN a.ka. "BRIAN"</v>
+        <v>ADAPTAR, BENITO y BULLECER</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>MURDER</v>
+        <v>THEFT</v>
       </c>
       <c r="I18" t="str">
-        <v>MIGRIÑO</v>
+        <v>N. CAFÉ-UY</v>
       </c>
       <c r="J18" t="str">
-        <v>R-10583</v>
+        <v>M-16963</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1156,13 +1145,13 @@
       <c r="N18" t="str">
         <v/>
       </c>
-      <c r="O18" t="str">
-        <v>INDEX CARDS\ACTOB, RYAN a.ka. BRIAN_0001.pdf</v>
+      <c r="P18" t="str">
+        <v>INDEX CARDS\ADAPTAR, BENITO y BULLECER_0001.pdf</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2002-1058</v>
+        <v>2005-862</v>
       </c>
       <c r="B19" t="str">
         <v>Invalid Date</v>
@@ -1171,39 +1160,36 @@
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>ADANO, CATALINO O.</v>
+        <v>AGAS, ERNESTO F. (P/SUPT.)</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>VIOL. OF R.A. 8282</v>
+        <v>VIOL. OF ART. 125 OF THE RPC</v>
       </c>
       <c r="I19" t="str">
-        <v>B. BAUTISTA</v>
+        <v>A. RARA</v>
       </c>
       <c r="J19" t="str">
-        <v>M-15259</v>
+        <v/>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="L19" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="M19" t="str">
-        <v/>
+        <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
       </c>
       <c r="N19" t="str">
         <v/>
       </c>
-      <c r="O19" t="str">
-        <v>INDEX CARDS\ADANO, CATALINO O._0001.pdf</v>
+      <c r="P19" t="str">
+        <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2007-301</v>
+        <v>2005-863</v>
       </c>
       <c r="B20" t="str">
         <v>Invalid Date</v>
@@ -1212,39 +1198,36 @@
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>ADAPTAR, BENITO y BULLECER</v>
+        <v>AGAS, ERNESTO F. (P/SUPT.)</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>THEFT</v>
+        <v>VIOL. OF R.A. 7438</v>
       </c>
       <c r="I20" t="str">
-        <v>N. CAFÉ-UY</v>
+        <v>A. RARA</v>
       </c>
       <c r="J20" t="str">
-        <v>M-16963</v>
+        <v/>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="L20" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="M20" t="str">
-        <v/>
+        <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
       </c>
       <c r="N20" t="str">
         <v/>
       </c>
-      <c r="O20" t="str">
-        <v>INDEX CARDS\ADAPTAR, BENITO y BULLECER_0001.pdf</v>
+      <c r="P20" t="str">
+        <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2005-862</v>
+        <v>2000-472</v>
       </c>
       <c r="B21" t="str">
         <v>Invalid Date</v>
@@ -1253,16 +1236,16 @@
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>AGAS, ERNESTO F. (P/SUPT.)</v>
+        <v>AGBAYANI, DOLORES / SHOPPER'S MART</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>VIOL. OF ART. 125 OF THE RPC</v>
+        <v>VIOL. OF SPECIAL SECURITY ACT OF 1997</v>
       </c>
       <c r="I21" t="str">
-        <v>A. RARA</v>
+        <v>MIGRIÑO</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1271,36 +1254,39 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
+        <v>REFERRED TO SSS, TAGB. CITY BRANCH 9/10/2000</v>
       </c>
       <c r="N21" t="str">
         <v/>
       </c>
-      <c r="O21" t="str">
-        <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
+      <c r="P21" t="str">
+        <v>INDEX CARDS\AGBAYANI, DOLORES  SHOPPER'S MART_0001.pdf</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2005-863</v>
+        <v>VII-14-INV-16I-0338-0341</v>
       </c>
       <c r="B22" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>MARASIGAN, JOSE</v>
       </c>
       <c r="D22" t="str">
-        <v>AGAS, ERNESTO F. (P/SUPT.)</v>
+        <v>AGENAR, GEORGE &amp; AGENAR, MARY JUDITH</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>VIOL. OF R.A. 7438</v>
+        <v>TRESPASS TO DWELLING, CARNAPPING, THEFT AND MALICIOUS MISCHIEF</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Invalid Date</v>
       </c>
       <c r="I22" t="str">
-        <v>A. RARA</v>
+        <v>ML. ENERLAS</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1308,19 +1294,22 @@
       <c r="K22" t="str">
         <v/>
       </c>
+      <c r="L22" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M22" t="str">
-        <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
+        <v/>
       </c>
       <c r="N22" t="str">
         <v/>
       </c>
-      <c r="O22" t="str">
-        <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
+      <c r="P22" t="str">
+        <v>INDEX CARDS\AGENAR, GEORGE &amp; AGENAR, MARY JUDITH_0001.pdf</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2000-472</v>
+        <v>VII-14-INQ-14H-0175</v>
       </c>
       <c r="B23" t="str">
         <v>Invalid Date</v>
@@ -1329,60 +1318,66 @@
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>AGBAYANI, DOLORES / SHOPPER'S MART</v>
+        <v>AGOSTA, MARVIN y ILOY</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>VIOL. OF SPECIAL SECURITY ACT OF 1997</v>
+        <v>VIOL. OF R.A. 9187</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Invalid Date</v>
       </c>
       <c r="I23" t="str">
-        <v>MIGRIÑO</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>R-16944</v>
       </c>
       <c r="K23" t="str">
         <v/>
       </c>
+      <c r="L23" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M23" t="str">
-        <v>REFERRED TO SSS, TAGB. CITY BRANCH 9/10/2000</v>
+        <v/>
       </c>
       <c r="N23" t="str">
         <v/>
       </c>
-      <c r="O23" t="str">
-        <v>INDEX CARDS\AGBAYANI, DOLORES  SHOPPER'S MART_0001.pdf</v>
+      <c r="P23" t="str">
+        <v>INDEX CARDS\AGOSTA, MARVIN y ILOY_0001.pdf</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>VII-14-INV-16I-0338-0341</v>
+        <v>VII-14-INV-09H-00317</v>
       </c>
       <c r="B24" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C24" t="str">
-        <v>MARASIGAN, JOSE</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>AGENAR, GEORGE &amp; AGENAR, MARY JUDITH</v>
+        <v xml:space="preserve">AGUAVIVA, CRISTITO, JR. </v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>TRESPASS TO DWELLING, CARNAPPING, THEFT AND MALICIOUS MISCHIEF</v>
+        <v>SLIGHT PHYSICAL INJURIES</v>
       </c>
       <c r="H24" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I24" t="str">
-        <v>ML. ENERLAS</v>
+        <v>N. CAFÉ-UY</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>M-17568</v>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -1396,13 +1391,13 @@
       <c r="N24" t="str">
         <v/>
       </c>
-      <c r="O24" t="str">
-        <v>INDEX CARDS\AGENAR, GEORGE &amp; AGENAR, MARY JUDITH_0001.pdf</v>
+      <c r="P24" t="str">
+        <v>INDEX CARDS\AGUAVIVA, CRISTITO, JR._0001.pdf</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>VII-14-INQ-14H-0175</v>
+        <v>VII-14-INV-13A-00031</v>
       </c>
       <c r="B25" t="str">
         <v>Invalid Date</v>
@@ -1411,22 +1406,22 @@
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>AGOSTA, MARVIN y ILOY</v>
+        <v>AGULLES, HERMAN</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>VIOL. OF R.A. 9187</v>
+        <v>QUALIFIED THEFT</v>
       </c>
       <c r="H25" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I25" t="str">
-        <v>B. BAUTISTA</v>
+        <v>F.R. MATUOD</v>
       </c>
       <c r="J25" t="str">
-        <v>R-16944</v>
+        <v>R-16153</v>
       </c>
       <c r="K25" t="str">
         <v/>
@@ -1440,37 +1435,37 @@
       <c r="N25" t="str">
         <v/>
       </c>
-      <c r="O25" t="str">
-        <v>INDEX CARDS\AGOSTA, MARVIN y ILOY_0001.pdf</v>
+      <c r="P25" t="str">
+        <v>AHAT, RIO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>VII-14-INV-09H-00317</v>
+        <v>VII-14-INV-21K-563</v>
       </c>
       <c r="B26" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>MEIJA, EVELYN P.</v>
       </c>
       <c r="D26" t="str">
-        <v xml:space="preserve">AGUAVIVA, CRISTITO, JR. </v>
+        <v>AGUIPO, IRENE H.</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>SLIGHT PHYSICAL INJURIES</v>
+        <v>ESTAFA PUNISHABLE UNDER ARTICLE 315, SUBSECTION 2 PAR. (A) OF RPC IN REL. TO R.A. 10175</v>
       </c>
       <c r="H26" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I26" t="str">
-        <v>N. CAFÉ-UY</v>
+        <v>A. SELMA</v>
       </c>
       <c r="J26" t="str">
-        <v>M-17568</v>
+        <v>R-25708</v>
       </c>
       <c r="K26" t="str">
         <v/>
@@ -1484,37 +1479,37 @@
       <c r="N26" t="str">
         <v/>
       </c>
-      <c r="O26" t="str">
-        <v>INDEX CARDS\AGUAVIVA, CRISTITO, JR._0001.pdf</v>
+      <c r="P26" t="str">
+        <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>VII-14-INV-13A-00031</v>
+        <v>VII-14-INV-21K-564</v>
       </c>
       <c r="B27" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>MEIJA, EVELYN P.</v>
       </c>
       <c r="D27" t="str">
-        <v>AGULLES, HERMAN</v>
+        <v>AGUIPO, IRENE H.</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>QUALIFIED THEFT</v>
+        <v>VIOL. OF SEC. 28 IN REL. TO SEC. 73 OF R.A. 8799</v>
       </c>
       <c r="H27" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I27" t="str">
-        <v>F.R. MATUOD</v>
+        <v>A. SELMA</v>
       </c>
       <c r="J27" t="str">
-        <v>R-16153</v>
+        <v>R-25709</v>
       </c>
       <c r="K27" t="str">
         <v/>
@@ -1528,37 +1523,34 @@
       <c r="N27" t="str">
         <v/>
       </c>
-      <c r="O27" t="str">
-        <v>AHAT, RIO</v>
+      <c r="P27" t="str">
+        <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>VII-14-INV-21K-563</v>
+        <v>2005-868</v>
       </c>
       <c r="B28" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C28" t="str">
-        <v>MEIJA, EVELYN P.</v>
+        <v/>
       </c>
       <c r="D28" t="str">
-        <v>AGUIPO, IRENE H.</v>
+        <v>AHAT, RIO</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>ESTAFA PUNISHABLE UNDER ARTICLE 315, SUBSECTION 2 PAR. (A) OF RPC IN REL. TO R.A. 10175</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Invalid Date</v>
+        <v>RESISTANCE &amp; DISOBEDIENCE OF PERSON IN AUTHORITY</v>
       </c>
       <c r="I28" t="str">
-        <v>A. SELMA</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J28" t="str">
-        <v>R-25708</v>
+        <v>R-13031</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -1567,42 +1559,42 @@
         <v>Invalid Date</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>WITHDRAWN 1/20/2006 CASE FALLS W/ IN THE JURISDICTION OF FAMILY COURT</v>
       </c>
       <c r="N28" t="str">
         <v/>
       </c>
-      <c r="O28" t="str">
-        <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
+      <c r="P28" t="str">
+        <v>INDEX CARDS\AHAT, RIO_0001.pdf</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>VII-14-INV-21K-564</v>
+        <v>VII-14-INQ-12D-062</v>
       </c>
       <c r="B29" t="str">
-        <v>Invalid Date</v>
+        <v>2004-10-09</v>
       </c>
       <c r="C29" t="str">
-        <v>MEIJA, EVELYN P.</v>
+        <v/>
       </c>
       <c r="D29" t="str">
-        <v>AGUIPO, IRENE H.</v>
+        <v>AHAT, RIO y ANDALES</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>VIOL. OF SEC. 28 IN REL. TO SEC. 73 OF R.A. 8799</v>
+        <v>VIOL. OF SEC 2, ART. II OF R.A. 9165</v>
       </c>
       <c r="H29" t="str">
-        <v>Invalid Date</v>
+        <v>2004-10-29</v>
       </c>
       <c r="I29" t="str">
-        <v>A. SELMA</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J29" t="str">
-        <v>R-25709</v>
+        <v>R-15685</v>
       </c>
       <c r="K29" t="str">
         <v/>
@@ -1616,34 +1608,37 @@
       <c r="N29" t="str">
         <v/>
       </c>
-      <c r="O29" t="str">
-        <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
+      <c r="P29" t="str">
+        <v>INDEX CARDS\AHAT, RIO y ANDALES 062_0001.pdf</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2005-868</v>
+        <v>VII-14-INQ-12D-061</v>
       </c>
       <c r="B30" t="str">
-        <v>Invalid Date</v>
+        <v>2004-10-09</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>AHAT, RIO</v>
+        <v>AHAT, RIO y ANDALES</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>RESISTANCE &amp; DISOBEDIENCE OF PERSON IN AUTHORITY</v>
+        <v>VIOL. OF SEC 5, ART. II OF R.A. 9165</v>
+      </c>
+      <c r="H30" t="str">
+        <v>2004-10-29</v>
       </c>
       <c r="I30" t="str">
         <v>B. BAUTISTA</v>
       </c>
       <c r="J30" t="str">
-        <v>R-13031</v>
+        <v>R-15684</v>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -1652,42 +1647,42 @@
         <v>Invalid Date</v>
       </c>
       <c r="M30" t="str">
-        <v>WITHDRAWN 1/20/2006 CASE FALLS W/ IN THE JURISDICTION OF FAMILY COURT</v>
+        <v/>
       </c>
       <c r="N30" t="str">
         <v/>
       </c>
-      <c r="O30" t="str">
-        <v>INDEX CARDS\AHAT, RIO_0001.pdf</v>
+      <c r="P30" t="str">
+        <v>INDEX CARDS\AHAT, RIO y ANDALES 061_0001_0001.pdf</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>VII-14-INQ-12D-062</v>
+        <v>VII-14-INQ-14E-117</v>
       </c>
       <c r="B31" t="str">
-        <v>2004-10-09</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>AHAT, RIO y ANDALES</v>
+        <v>ALAGADI, MARCOS</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>VIOL. OF SEC 2, ART. II OF R.A. 9165</v>
+        <v>VIOL. OF SEC. 11, ART. II OF R.A. 9165</v>
       </c>
       <c r="H31" t="str">
-        <v>2004-10-29</v>
+        <v>Invalid Date</v>
       </c>
       <c r="I31" t="str">
-        <v>B. BAUTISTA</v>
+        <v>F.R. MATUOD</v>
       </c>
       <c r="J31" t="str">
-        <v>R-15685</v>
+        <v>R-16847</v>
       </c>
       <c r="K31" t="str">
         <v/>
@@ -1701,37 +1696,37 @@
       <c r="N31" t="str">
         <v/>
       </c>
-      <c r="O31" t="str">
-        <v>INDEX CARDS\AHAT, RIO y ANDALES 062_0001.pdf</v>
+      <c r="P31" t="str">
+        <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>VII-14-INQ-12D-061</v>
+        <v>VII-14-INQ-14E-118</v>
       </c>
       <c r="B32" t="str">
-        <v>2004-10-09</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>AHAT, RIO y ANDALES</v>
+        <v>ALAGADI, MARCOS</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>VIOL. OF SEC 5, ART. II OF R.A. 9165</v>
+        <v>VIOL. OF SEC. 12, ART. II OF R.A. 9165</v>
       </c>
       <c r="H32" t="str">
-        <v>2004-10-29</v>
+        <v>Invalid Date</v>
       </c>
       <c r="I32" t="str">
-        <v>B. BAUTISTA</v>
+        <v>F.R. MATUOD</v>
       </c>
       <c r="J32" t="str">
-        <v>R-15684</v>
+        <v>R-16848</v>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -1745,13 +1740,13 @@
       <c r="N32" t="str">
         <v/>
       </c>
-      <c r="O32" t="str">
-        <v>INDEX CARDS\AHAT, RIO y ANDALES 061_0001_0001.pdf</v>
+      <c r="P32" t="str">
+        <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>VII-14-INQ-14E-117</v>
+        <v>2004-345-349</v>
       </c>
       <c r="B33" t="str">
         <v>Invalid Date</v>
@@ -1760,22 +1755,19 @@
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>ALAGADI, MARCOS</v>
+        <v>ALAGO, LILIBETH</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>VIOL. OF SEC. 11, ART. II OF R.A. 9165</v>
-      </c>
-      <c r="H33" t="str">
-        <v>Invalid Date</v>
+        <v>VIOL. OF BP. BLG. 22</v>
       </c>
       <c r="I33" t="str">
-        <v>F.R. MATUOD</v>
+        <v>CRISTOBAL</v>
       </c>
       <c r="J33" t="str">
-        <v>R-16847</v>
+        <v>M-15914-15918</v>
       </c>
       <c r="K33" t="str">
         <v/>
@@ -1789,37 +1781,37 @@
       <c r="N33" t="str">
         <v/>
       </c>
-      <c r="O33" t="str">
-        <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
+      <c r="P33" t="str">
+        <v>INDEX CARDS\ALAGO, LILIBETH_0001.pdf</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>VII-14-INQ-14E-118</v>
+        <v>VII-14-INQ-22D-078</v>
       </c>
       <c r="B34" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>PNP, TAGBILARAN CITY</v>
       </c>
       <c r="D34" t="str">
-        <v>ALAGADI, MARCOS</v>
+        <v>ALANGADI, CASANODING y SULTAN</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>VIOL. OF SEC. 12, ART. II OF R.A. 9165</v>
+        <v>VIOL. OF SEC. 7, ART. II OF R.A. 9165</v>
       </c>
       <c r="H34" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I34" t="str">
-        <v>F.R. MATUOD</v>
+        <v>J. TORREGOSA</v>
       </c>
       <c r="J34" t="str">
-        <v>R-16848</v>
+        <v>R-25796</v>
       </c>
       <c r="K34" t="str">
         <v/>
@@ -1833,34 +1825,37 @@
       <c r="N34" t="str">
         <v/>
       </c>
-      <c r="O34" t="str">
-        <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
+      <c r="P34" t="str">
+        <v>INDEX CARDS\ALANGADI, CASANODING y SULTAN 078_0001.pdf</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2004-345-349</v>
+        <v>VII-14-INQ-21K-245</v>
       </c>
       <c r="B35" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>PNP, TAGBILARAN CITY</v>
       </c>
       <c r="D35" t="str">
-        <v>ALAGO, LILIBETH</v>
+        <v>ALAPAN, KENNETH y ALBARICO</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>VIOL. OF BP. BLG. 22</v>
+        <v>VIOL. OF SEC. P.D. 1602 (PRESCRIBING STIFFER PENALTIES IN ILLEGAL GAMBLING)</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Invalid Date</v>
       </c>
       <c r="I35" t="str">
-        <v>CRISTOBAL</v>
+        <v>F.R. MATUOD</v>
       </c>
       <c r="J35" t="str">
-        <v>M-15914-15918</v>
+        <v>M-20677</v>
       </c>
       <c r="K35" t="str">
         <v/>
@@ -1874,37 +1869,37 @@
       <c r="N35" t="str">
         <v/>
       </c>
-      <c r="O35" t="str">
-        <v>INDEX CARDS\ALAGO, LILIBETH_0001.pdf</v>
+      <c r="P35" t="str">
+        <v>INDEX CARDS\ALAPAN, KENNETH y ALBARICO_0001.pdf</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>VII-14-INQ-22D-078</v>
+        <v>VII-14-INV-12F-0286</v>
       </c>
       <c r="B36" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C36" t="str">
-        <v>PNP, TAGBILARAN CITY</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>ALANGADI, CASANODING y SULTAN</v>
+        <v>ALBARADO, SERVILLA y MAMBAJEN</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>VIOL. OF SEC. 7, ART. II OF R.A. 9165</v>
+        <v>VIOL. OF PD 1602</v>
       </c>
       <c r="H36" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I36" t="str">
-        <v>J. TORREGOSA</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J36" t="str">
-        <v>R-25796</v>
+        <v/>
       </c>
       <c r="K36" t="str">
         <v/>
@@ -1913,42 +1908,42 @@
         <v>Invalid Date</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>DISMISSED</v>
       </c>
       <c r="N36" t="str">
         <v/>
       </c>
-      <c r="O36" t="str">
-        <v>INDEX CARDS\ALANGADI, CASANODING y SULTAN 078_0001.pdf</v>
+      <c r="P36" t="str">
+        <v>INDEX CARDS\ALBARADO, SERVILLA y MAMBAJEN_0001.pdf</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>VII-14-INQ-21K-245</v>
+        <v>VII-14-INQ-16I-0391</v>
       </c>
       <c r="B37" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C37" t="str">
-        <v>PNP, TAGBILARAN CITY</v>
+        <v>OLAIVAR, N. (PSUPT.)</v>
       </c>
       <c r="D37" t="str">
-        <v>ALAPAN, KENNETH y ALBARICO</v>
+        <v>ALBERIO, CARLO y GALZIM</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>VIOL. OF SEC. P.D. 1602 (PRESCRIBING STIFFER PENALTIES IN ILLEGAL GAMBLING)</v>
+        <v>VIOL. OF SEC. 11, ART. II, R.A. 9165</v>
       </c>
       <c r="H37" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I37" t="str">
-        <v>F.R. MATUOD</v>
+        <v>C. GAMAS</v>
       </c>
       <c r="J37" t="str">
-        <v>M-20677</v>
+        <v>R-19325</v>
       </c>
       <c r="K37" t="str">
         <v/>
@@ -1962,13 +1957,13 @@
       <c r="N37" t="str">
         <v/>
       </c>
-      <c r="O37" t="str">
-        <v>INDEX CARDS\ALAPAN, KENNETH y ALBARICO_0001.pdf</v>
+      <c r="P37" t="str">
+        <v>INDEX CARDS\ALBERIO, CARLO y GALZIM_0001.pdf</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>VII-14-INV-12F-0286</v>
+        <v>2005-778-781</v>
       </c>
       <c r="B38" t="str">
         <v>Invalid Date</v>
@@ -1977,22 +1972,19 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>ALBARADO, SERVILLA y MAMBAJEN</v>
+        <v>ALBIENDA, LILIAN y BUICO</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>VIOL. OF PD 1602</v>
-      </c>
-      <c r="H38" t="str">
-        <v>Invalid Date</v>
+        <v>ESTAFA</v>
       </c>
       <c r="I38" t="str">
-        <v>R. CHATTO</v>
+        <v>J. SALISE</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>R-13036,         R-13037</v>
       </c>
       <c r="K38" t="str">
         <v/>
@@ -2001,42 +1993,39 @@
         <v>Invalid Date</v>
       </c>
       <c r="M38" t="str">
-        <v>DISMISSED</v>
+        <v>780-781 DISMISSED 1/17/2005</v>
       </c>
       <c r="N38" t="str">
         <v/>
       </c>
-      <c r="O38" t="str">
-        <v>INDEX CARDS\ALBARADO, SERVILLA y MAMBAJEN_0001.pdf</v>
+      <c r="P38" t="str">
+        <v>INDEX CARDS\ALBIENDA, LILIAN y BUICO_0001.pdf</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>VII-14-INQ-16I-0391</v>
+        <v>2006-27</v>
       </c>
       <c r="B39" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C39" t="str">
-        <v>OLAIVAR, N. (PSUPT.)</v>
+        <v/>
       </c>
       <c r="D39" t="str">
-        <v>ALBERIO, CARLO y GALZIM</v>
+        <v>ALBIOS, SEVERINO y CABANG</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>VIOL. OF SEC. 11, ART. II, R.A. 9165</v>
-      </c>
-      <c r="H39" t="str">
-        <v>Invalid Date</v>
+        <v>LESS SERIOUS PHYSICAL INJURIES</v>
       </c>
       <c r="I39" t="str">
-        <v>C. GAMAS</v>
+        <v>N. CAFÉ-UY</v>
       </c>
       <c r="J39" t="str">
-        <v>R-19325</v>
+        <v>M-16465</v>
       </c>
       <c r="K39" t="str">
         <v/>
@@ -2050,34 +2039,34 @@
       <c r="N39" t="str">
         <v/>
       </c>
-      <c r="O39" t="str">
-        <v>INDEX CARDS\ALBERIO, CARLO y GALZIM_0001.pdf</v>
+      <c r="P39" t="str">
+        <v>INDEX CARDS\ALBIOS, SEVERINO y CABANG_0001.pdf</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2005-778-781</v>
+        <v>VII-14-INV-11C-00118</v>
       </c>
       <c r="B40" t="str">
-        <v>Invalid Date</v>
+        <v>2004-06-19</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>GALICIA, ROSALINA / EDUARTE, MARCELA</v>
       </c>
       <c r="D40" t="str">
-        <v>ALBIENDA, LILIAN y BUICO</v>
+        <v>ALDEPOLLA, IGNACIO</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>ESTAFA</v>
+        <v>FALSIFICATION OF PUBLIC DOCUMENTS</v>
       </c>
       <c r="I40" t="str">
-        <v>J. SALISE</v>
+        <v>A. RARA</v>
       </c>
       <c r="J40" t="str">
-        <v>R-13036,         R-13037</v>
+        <v/>
       </c>
       <c r="K40" t="str">
         <v/>
@@ -2086,18 +2075,18 @@
         <v>Invalid Date</v>
       </c>
       <c r="M40" t="str">
-        <v>780-781 DISMISSED 1/17/2005</v>
+        <v>DISMISSED 6/6/2011</v>
       </c>
       <c r="N40" t="str">
         <v/>
       </c>
-      <c r="O40" t="str">
-        <v>INDEX CARDS\ALBIENDA, LILIAN y BUICO_0001.pdf</v>
+      <c r="P40" t="str">
+        <v>INDEX CARDS\ALDEPOLLA, IGNACIO_0001.pdf</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2006-27</v>
+        <v>VII-14-INV-13G-0269</v>
       </c>
       <c r="B41" t="str">
         <v>Invalid Date</v>
@@ -2106,57 +2095,60 @@
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>ALBIOS, SEVERINO y CABANG</v>
+        <v xml:space="preserve">ABING, MOISES  </v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>LESS SERIOUS PHYSICAL INJURIES</v>
+        <v>GRAVE THREATS /GRAVE COERCION LIGHT THREATS</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Invalid Date</v>
       </c>
       <c r="I41" t="str">
-        <v>N. CAFÉ-UY</v>
+        <v>M.ANORA</v>
       </c>
       <c r="J41" t="str">
-        <v>M-16465</v>
+        <v/>
       </c>
       <c r="K41" t="str">
         <v/>
       </c>
-      <c r="L41" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="M41" t="str">
-        <v/>
+        <v>ACQUITTED</v>
       </c>
       <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <v>INDEX CARDS\ALBIOS, SEVERINO y CABANG_0001.pdf</v>
+        <v>B.R 2</v>
+      </c>
+      <c r="P41" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>VII-14-INV-11C-00118</v>
+        <v>2006-572</v>
       </c>
       <c r="B42" t="str">
-        <v>2004-06-19</v>
+        <v>Invalid Date</v>
       </c>
       <c r="C42" t="str">
-        <v>GALICIA, ROSALINA / EDUARTE, MARCELA</v>
+        <v/>
       </c>
       <c r="D42" t="str">
-        <v>ALDEPOLLA, IGNACIO</v>
+        <v>ABLAN, MA. ANABELLE y NOPAL</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>FALSIFICATION OF PUBLIC DOCUMENTS</v>
+        <v>RECKLESS IMPRUDENCE RE TO SERIOUS PHYSICAL INJURIES</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Invalid Date</v>
       </c>
       <c r="I42" t="str">
-        <v>A. RARA</v>
+        <v>N. CRISTOBAL</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2164,22 +2156,19 @@
       <c r="K42" t="str">
         <v/>
       </c>
-      <c r="L42" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="M42" t="str">
-        <v>DISMISSED 6/6/2011</v>
+        <v>DROPPED</v>
       </c>
       <c r="N42" t="str">
         <v/>
       </c>
-      <c r="O42" t="str">
-        <v>INDEX CARDS\ALDEPOLLA, IGNACIO_0001.pdf</v>
+      <c r="P42" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>VII-14-INV-13G-0269</v>
+        <v>2002-659,660,661</v>
       </c>
       <c r="B43" t="str">
         <v>Invalid Date</v>
@@ -2188,19 +2177,19 @@
         <v/>
       </c>
       <c r="D43" t="str">
-        <v xml:space="preserve">ABING, MOISES  </v>
+        <v>ABLANQUE, SOCRATES</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>GRAVE THREATS /GRAVE COERCION LIGHT THREATS</v>
+        <v>ESTAFA &amp; OR VIOL OF BP 22</v>
       </c>
       <c r="H43" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I43" t="str">
-        <v>M.ANORA</v>
+        <v>A. RARA</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -2209,39 +2198,39 @@
         <v/>
       </c>
       <c r="M43" t="str">
-        <v>ACQUITTED</v>
+        <v>WITHDRAWN</v>
       </c>
       <c r="N43" t="str">
-        <v>B.R 2</v>
-      </c>
-      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2006-572</v>
+        <v>VII-14-INQ--16C-090</v>
       </c>
       <c r="B44" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>NBI-ATYY ALBAO</v>
       </c>
       <c r="D44" t="str">
-        <v>ABLAN, MA. ANABELLE y NOPAL</v>
+        <v>ABOYADOR,MARK JOSEPH</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>RECKLESS IMPRUDENCE RE TO SERIOUS PHYSICAL INJURIES</v>
+        <v>VIOL OF SEC 11,ART II, R.A 9165</v>
       </c>
       <c r="H44" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I44" t="str">
-        <v>N. CRISTOBAL</v>
+        <v>G. LIM</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -2250,39 +2239,39 @@
         <v/>
       </c>
       <c r="M44" t="str">
-        <v>DROPPED</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N44" t="str">
         <v/>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2002-659,660,661</v>
+        <v>VII-14-INQ-16C-091</v>
       </c>
       <c r="B45" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>NBI-ATTY ALBAO</v>
       </c>
       <c r="D45" t="str">
-        <v>ABLANQUE, SOCRATES</v>
+        <v>ABOYADOR,MARK JOSEPH</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>ESTAFA &amp; OR VIOL OF BP 22</v>
+        <v>VIOL OF SEC 12,R.A II,9165</v>
       </c>
       <c r="H45" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I45" t="str">
-        <v>A. RARA</v>
+        <v>G. LIM</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2291,33 +2280,33 @@
         <v/>
       </c>
       <c r="M45" t="str">
-        <v>WITHDRAWN</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N45" t="str">
         <v/>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>VII-14-INQ--16C-090</v>
+        <v>VII-14-INQ-16C 092</v>
       </c>
       <c r="B46" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C46" t="str">
-        <v>NBI-ATYY ALBAO</v>
+        <v>NBI-ATTY ALBAO</v>
       </c>
       <c r="D46" t="str">
-        <v>ABOYADOR,MARK JOSEPH</v>
+        <v>ABOYADOR,,ARK JOSEPH y TORREMOCHA</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>VIOL OF SEC 11,ART II, R.A 9165</v>
+        <v>VIOL OF SEC 15,ART II R.A 9165</v>
       </c>
       <c r="H46" t="str">
         <v>Invalid Date</v>
@@ -2332,39 +2321,39 @@
         <v/>
       </c>
       <c r="M46" t="str">
-        <v>ACQUITTED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N46" t="str">
         <v/>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>VII-14-INQ-16C-091</v>
+        <v>2006-177</v>
       </c>
       <c r="B47" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C47" t="str">
-        <v>NBI-ATTY ALBAO</v>
+        <v/>
       </c>
       <c r="D47" t="str">
-        <v>ABOYADOR,MARK JOSEPH</v>
+        <v>ABRAU, BENJIE</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>VIOL OF SEC 12,R.A II,9165</v>
+        <v>THEFT</v>
       </c>
       <c r="H47" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I47" t="str">
-        <v>G. LIM</v>
+        <v>A. RARA</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -2373,39 +2362,39 @@
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>ACQUITTED</v>
+        <v>DIVERSION PROCEEDINGSAT KATARUNGANG BRGY. OF S.BULLONES,BOHOL BR. 1</v>
       </c>
       <c r="N47" t="str">
         <v/>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>VII-14-INQ-16C 092</v>
+        <v>2003-178</v>
       </c>
       <c r="B48" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C48" t="str">
-        <v>NBI-ATTY ALBAO</v>
+        <v/>
       </c>
       <c r="D48" t="str">
-        <v>ABOYADOR,,ARK JOSEPH y TORREMOCHA</v>
+        <v>ABRAU, BENJIE</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>VIOL OF SEC 15,ART II R.A 9165</v>
+        <v>TRESPASS TO DWELLING</v>
       </c>
       <c r="H48" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I48" t="str">
-        <v>G. LIM</v>
+        <v>A.S RARA</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -2414,18 +2403,18 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v>DISMISSED</v>
+        <v>DROPPED</v>
       </c>
       <c r="N48" t="str">
         <v/>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2006-177</v>
+        <v>2006-583</v>
       </c>
       <c r="B49" t="str">
         <v>Invalid Date</v>
@@ -2434,19 +2423,19 @@
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>ABRAU, BENJIE</v>
+        <v>ABRAU,EMMANUEL y DELA CRUZ</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>THEFT</v>
+        <v>VIOL OF R.A 9262 (VAWC)</v>
       </c>
       <c r="H49" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I49" t="str">
-        <v>A. RARA</v>
+        <v>N. CRISTOBAL</v>
       </c>
       <c r="J49" t="str">
         <v/>
@@ -2455,18 +2444,18 @@
         <v/>
       </c>
       <c r="M49" t="str">
-        <v>DIVERSION PROCEEDINGSAT KATARUNGANG BRGY. OF S.BULLONES,BOHOL BR. 1</v>
+        <v>DROPPED</v>
       </c>
       <c r="N49" t="str">
         <v/>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2003-178</v>
+        <v>2000-690,691</v>
       </c>
       <c r="B50" t="str">
         <v>Invalid Date</v>
@@ -2475,19 +2464,19 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>ABRAU, BENJIE</v>
+        <v xml:space="preserve">ABALO, JANICE  B. </v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>TRESPASS TO DWELLING</v>
+        <v xml:space="preserve">ALARSON W/ SCANDAL,RESISTANCE W/DISOBEDIENCE TO A PERSON IN AUTHORITY </v>
       </c>
       <c r="H50" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I50" t="str">
-        <v>A.S RARA</v>
+        <v>MIGRINO</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -2496,18 +2485,18 @@
         <v/>
       </c>
       <c r="M50" t="str">
-        <v>DROPPED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N50" t="str">
         <v/>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2006-583</v>
+        <v>2008-201</v>
       </c>
       <c r="B51" t="str">
         <v>Invalid Date</v>
@@ -2516,19 +2505,19 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>ABRAU,EMMANUEL y DELA CRUZ</v>
+        <v>ABDALA,JUANITO A.K.A JORDAN</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>VIOL OF R.A 9262 (VAWC)</v>
+        <v>VIOL OF ART 281 OF THE RPC</v>
       </c>
       <c r="H51" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I51" t="str">
-        <v>N. CRISTOBAL</v>
+        <v>N. UY</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2537,18 +2526,18 @@
         <v/>
       </c>
       <c r="M51" t="str">
-        <v>DROPPED</v>
+        <v>WITHDRWAN</v>
       </c>
       <c r="N51" t="str">
         <v/>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2000-690,691</v>
+        <v>2003- OF R.A 761</v>
       </c>
       <c r="B52" t="str">
         <v>Invalid Date</v>
@@ -2557,19 +2546,19 @@
         <v/>
       </c>
       <c r="D52" t="str">
-        <v xml:space="preserve">ABALO, JANICE  B. </v>
+        <v>ABDUL, ISMAEL</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v xml:space="preserve">ALARSON W/ SCANDAL,RESISTANCE W/DISOBEDIENCE TO A PERSON IN AUTHORITY </v>
+        <v>VIOL OF R.A 761</v>
       </c>
       <c r="H52" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I52" t="str">
-        <v>MIGRINO</v>
+        <v>MONTES</v>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2578,18 +2567,18 @@
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>DISMISSED</v>
+        <v>DROPPED</v>
       </c>
       <c r="N52" t="str">
         <v/>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2008-201</v>
+        <v>2008-120</v>
       </c>
       <c r="B53" t="str">
         <v>Invalid Date</v>
@@ -2598,19 +2587,19 @@
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>ABDALA,JUANITO A.K.A JORDAN</v>
+        <v>ABEJARON, PACIANA</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>VIOL OF ART 281 OF THE RPC</v>
+        <v>FALSIFICATION OF PUBLIC DOCUMENT</v>
       </c>
       <c r="H53" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I53" t="str">
-        <v>N. UY</v>
+        <v>N. CAFE</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -2619,18 +2608,18 @@
         <v/>
       </c>
       <c r="M53" t="str">
-        <v>WITHDRWAN</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N53" t="str">
         <v/>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2003- OF R.A 761</v>
+        <v>2008-0120</v>
       </c>
       <c r="B54" t="str">
         <v>Invalid Date</v>
@@ -2639,19 +2628,19 @@
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>ABDUL, ISMAEL</v>
+        <v>ABEJARON, EULALIO</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>VIOL OF R.A 761</v>
+        <v>FALSIFICATION OF PUBLIC DOCUMENT</v>
       </c>
       <c r="H54" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I54" t="str">
-        <v>MONTES</v>
+        <v>N. IU</v>
       </c>
       <c r="J54" t="str">
         <v/>
@@ -2660,39 +2649,39 @@
         <v/>
       </c>
       <c r="M54" t="str">
-        <v>DROPPED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N54" t="str">
         <v/>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2008-120</v>
+        <v>VII-14-INV-23I-410</v>
       </c>
       <c r="B55" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>ANALYN CALAMBA BAUTISTA</v>
       </c>
       <c r="D55" t="str">
-        <v>ABEJARON, PACIANA</v>
+        <v>ABEJARON,MARY JANE</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>FALSIFICATION OF PUBLIC DOCUMENT</v>
+        <v>ESTAFA underART 315 par 2,sub parag (a) of the revised penal code as amended by r.a 10951</v>
       </c>
       <c r="H55" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I55" t="str">
-        <v>N. CAFE</v>
+        <v>JOSIE SEMPRON</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -2706,34 +2695,34 @@
       <c r="N55" t="str">
         <v/>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2008-0120</v>
+        <v>VII-14-INV-23i -410</v>
       </c>
       <c r="B56" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>ANALYN CALAMBA BAUTISTA</v>
       </c>
       <c r="D56" t="str">
-        <v>ABEJARON, EULALIO</v>
+        <v>ABEJARON, MARY JANE</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>FALSIFICATION OF PUBLIC DOCUMENT</v>
+        <v>VIOL OF COMMONWEALTH ACT NO 142</v>
       </c>
       <c r="H56" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I56" t="str">
-        <v>N. IU</v>
+        <v>JOSIE SEMPRON</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2747,34 +2736,34 @@
       <c r="N56" t="str">
         <v/>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>VII-14-INV-23I-410</v>
+        <v>2007 - 472</v>
       </c>
       <c r="B57" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C57" t="str">
-        <v>ANALYN CALAMBA BAUTISTA</v>
+        <v/>
       </c>
       <c r="D57" t="str">
-        <v>ABEJARON,MARY JANE</v>
+        <v>ABEJARON, RJ y OMLERO</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>ESTAFA underART 315 par 2,sub parag (a) of the revised penal code as amended by r.a 10951</v>
+        <v xml:space="preserve">RESISTANCE &amp; DISOBEDIENCE TO AN AGENT IN AUTHORITY </v>
       </c>
       <c r="H57" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I57" t="str">
-        <v>JOSIE SEMPRON</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -2783,39 +2772,39 @@
         <v/>
       </c>
       <c r="M57" t="str">
-        <v>DISMISSED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57" t="str">
+        <v>1 MS &amp; 15 DAYS OF ARRESTO MAYOR &amp; TO PAYA FINE OF 200.00 W/ ALL  THE ACCESORY PENALTIES  &amp; TO PAY THE COST</v>
+      </c>
+      <c r="P57" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>VII-14-INV-23i -410</v>
+        <v>2007-473</v>
       </c>
       <c r="B58" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C58" t="str">
-        <v>ANALYN CALAMBA BAUTISTA</v>
+        <v/>
       </c>
       <c r="D58" t="str">
-        <v>ABEJARON, MARY JANE</v>
+        <v>ABEJARON, RJ y OMLERO</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>VIOL OF COMMONWEALTH ACT NO 142</v>
+        <v>VIOL OF BP BLG. 22</v>
       </c>
       <c r="H58" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I58" t="str">
-        <v>JOSIE SEMPRON</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -2824,18 +2813,18 @@
         <v/>
       </c>
       <c r="M58" t="str">
-        <v>DISMISSED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
+        <v>IMPRISONMENT OF 1 MONTH &amp; TO PAY THE COST</v>
+      </c>
+      <c r="P58" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2007 - 472</v>
+        <v>2007-474</v>
       </c>
       <c r="B59" t="str">
         <v>Invalid Date</v>
@@ -2844,13 +2833,13 @@
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>ABEJARON, RJ y OMLERO</v>
+        <v>ABEJARON,RJ y OMLERO</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v xml:space="preserve">RESISTANCE &amp; DISOBEDIENCE TO AN AGENT IN AUTHORITY </v>
+        <v>LESS SERIOUS PHYSICAL INJURIES</v>
       </c>
       <c r="H59" t="str">
         <v>Invalid Date</v>
@@ -2868,15 +2857,15 @@
         <v>CONVICTED</v>
       </c>
       <c r="N59" t="str">
-        <v>1 MS &amp; 15 DAYS OF ARRESTO MAYOR &amp; TO PAYA FINE OF 200.00 W/ ALL  THE ACCESORY PENALTIES  &amp; TO PAY THE COST</v>
-      </c>
-      <c r="O59" t="str">
+        <v>1 MOS &amp;  15 DAYS ARRESTO MAYOR &amp; TO PRIVATE COMPLAIN ANT THE AMOUNT OF 2000.00 AS CIVILM LIABILITY</v>
+      </c>
+      <c r="P59" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2007-473</v>
+        <v>2006-789</v>
       </c>
       <c r="B60" t="str">
         <v>Invalid Date</v>
@@ -2891,13 +2880,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>VIOL OF BP BLG. 22</v>
+        <v>VIOL OF B.P BLG. 6</v>
       </c>
       <c r="H60" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I60" t="str">
-        <v>R. CHATTO</v>
+        <v>A.S RARA</v>
       </c>
       <c r="J60" t="str">
         <v/>
@@ -2909,15 +2898,15 @@
         <v>CONVICTED</v>
       </c>
       <c r="N60" t="str">
-        <v>IMPRISONMENT OF 1 MONTH &amp; TO PAY THE COST</v>
-      </c>
-      <c r="O60" t="str">
+        <v>IMPRISONMENT OF 4 MONTHS &amp; TO PAY THE COST</v>
+      </c>
+      <c r="P60" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2007-474</v>
+        <v>2006-638</v>
       </c>
       <c r="B61" t="str">
         <v>Invalid Date</v>
@@ -2926,19 +2915,19 @@
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>ABEJARON,RJ y OMLERO</v>
+        <v>ABEJARON, RJ y OMLERO</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>LESS SERIOUS PHYSICAL INJURIES</v>
+        <v>VIOL OF  B.P BLG 6</v>
       </c>
       <c r="H61" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I61" t="str">
-        <v>R. CHATTO</v>
+        <v>N, UY</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -2950,15 +2939,15 @@
         <v>CONVICTED</v>
       </c>
       <c r="N61" t="str">
-        <v>1 MOS &amp;  15 DAYS ARRESTO MAYOR &amp; TO PRIVATE COMPLAIN ANT THE AMOUNT OF 2000.00 AS CIVILM LIABILITY</v>
-      </c>
-      <c r="O61" t="str">
+        <v>IMPRISONMENT OF 2 MOS. AND TO PAY THE COST</v>
+      </c>
+      <c r="P61" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2006-789</v>
+        <v>2005-170</v>
       </c>
       <c r="B62" t="str">
         <v>Invalid Date</v>
@@ -2967,19 +2956,19 @@
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>ABEJARON, RJ y OMLERO</v>
+        <v>ABEJARON, ARGIE y OMLERO</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>VIOL OF B.P BLG. 6</v>
+        <v>ATTEMPTED ROBBERY</v>
       </c>
       <c r="H62" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I62" t="str">
-        <v>A.S RARA</v>
+        <v/>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -2988,18 +2977,18 @@
         <v/>
       </c>
       <c r="M62" t="str">
-        <v>CONVICTED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N62" t="str">
-        <v>IMPRISONMENT OF 4 MONTHS &amp; TO PAY THE COST</v>
-      </c>
-      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2006-638</v>
+        <v>2005-171</v>
       </c>
       <c r="B63" t="str">
         <v>Invalid Date</v>
@@ -3008,19 +2997,19 @@
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>ABEJARON, RJ y OMLERO</v>
+        <v>ABEJARON, ARGIE y OMLERO</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>VIOL OF  B.P BLG 6</v>
+        <v>SLIGHT PHYSICAL INJURIES</v>
       </c>
       <c r="H63" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I63" t="str">
-        <v>N, UY</v>
+        <v/>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -3032,36 +3021,36 @@
         <v>CONVICTED</v>
       </c>
       <c r="N63" t="str">
-        <v>IMPRISONMENT OF 2 MOS. AND TO PAY THE COST</v>
-      </c>
-      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2005-170</v>
+        <v>VII-14-INV-16A-044</v>
       </c>
       <c r="B64" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>TRANSITO E. TUYOGON</v>
       </c>
       <c r="D64" t="str">
-        <v>ABEJARON, ARGIE y OMLERO</v>
+        <v>ABEJO, SANDY</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>ATTEMPTED ROBBERY</v>
+        <v>ESTAFA (ART.315 (1) ( B) OF RPC</v>
       </c>
       <c r="H64" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>F. MATUOD</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3075,13 +3064,13 @@
       <c r="N64" t="str">
         <v/>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2005-171</v>
+        <v>2005-566</v>
       </c>
       <c r="B65" t="str">
         <v>Invalid Date</v>
@@ -3090,19 +3079,19 @@
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>ABEJARON, ARGIE y OMLERO</v>
+        <v>ABELLA, LEONARDO y YAP</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>SLIGHT PHYSICAL INJURIES</v>
+        <v>VIOL OF SSS LAW</v>
       </c>
       <c r="H65" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J65" t="str">
         <v/>
@@ -3111,39 +3100,39 @@
         <v/>
       </c>
       <c r="M65" t="str">
-        <v>CONVICTED</v>
+        <v>DROPPED</v>
       </c>
       <c r="N65" t="str">
         <v/>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>VII-14-INV-16A-044</v>
+        <v>VII-14-INV-14A-018</v>
       </c>
       <c r="B66" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C66" t="str">
-        <v>TRANSITO E. TUYOGON</v>
+        <v/>
       </c>
       <c r="D66" t="str">
-        <v>ABEJO, SANDY</v>
+        <v xml:space="preserve">ABELLANA, BENJAMIN A. </v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>ESTAFA (ART.315 (1) ( B) OF RPC</v>
+        <v>VIOL OF SEC 22(a) IN REL TO SEC.28 (E) OF R.A 1161,as amended by R.A 8282</v>
       </c>
       <c r="H66" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I66" t="str">
-        <v>F. MATUOD</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -3157,13 +3146,13 @@
       <c r="N66" t="str">
         <v/>
       </c>
-      <c r="O66" t="str">
+      <c r="P66" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2005-566</v>
+        <v>VII-14-INV-09D-00108</v>
       </c>
       <c r="B67" t="str">
         <v>Invalid Date</v>
@@ -3172,19 +3161,19 @@
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>ABELLA, LEONARDO y YAP</v>
+        <v>ABELLANA,CHARLENE MARIE</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>VIOL OF SSS LAW</v>
+        <v>FRUSTRATED MURDER</v>
       </c>
       <c r="H67" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I67" t="str">
-        <v>B. BAUTISTA</v>
+        <v>A.S. RARA</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -3193,18 +3182,18 @@
         <v/>
       </c>
       <c r="M67" t="str">
-        <v>DROPPED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N67" t="str">
         <v/>
       </c>
-      <c r="O67" t="str">
+      <c r="P67" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>VII-14-INV-14A-018</v>
+        <v>2008-329</v>
       </c>
       <c r="B68" t="str">
         <v>Invalid Date</v>
@@ -3213,19 +3202,19 @@
         <v/>
       </c>
       <c r="D68" t="str">
-        <v xml:space="preserve">ABELLANA, BENJAMIN A. </v>
+        <v>ABELLANA, DANILO</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>VIOL OF SEC 22(a) IN REL TO SEC.28 (E) OF R.A 1161,as amended by R.A 8282</v>
+        <v>LIBEL</v>
       </c>
       <c r="H68" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I68" t="str">
-        <v>B. BAUTISTA</v>
+        <v>R. CHATTO</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -3239,13 +3228,13 @@
       <c r="N68" t="str">
         <v/>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>VII-14-INV-09D-00108</v>
+        <v>VII-14=-INV-14A-018</v>
       </c>
       <c r="B69" t="str">
         <v>Invalid Date</v>
@@ -3254,19 +3243,19 @@
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>ABELLANA,CHARLENE MARIE</v>
+        <v xml:space="preserve">ABELLANA,JEAN ARLENE C. </v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>FRUSTRATED MURDER</v>
+        <v>VIOL OF R.A 1161 AS AMENDED BY R.A 8282</v>
       </c>
       <c r="H69" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I69" t="str">
-        <v>A.S. RARA</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -3280,13 +3269,13 @@
       <c r="N69" t="str">
         <v/>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2008-329</v>
+        <v>VII-14-INQ-15K-0168</v>
       </c>
       <c r="B70" t="str">
         <v>Invalid Date</v>
@@ -3295,19 +3284,19 @@
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>ABELLANA, DANILO</v>
+        <v>ABELLANA,JOANNE CLAIRE</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>LIBEL</v>
+        <v>VIOL OF SEC11,ART II,OF R.A 9165</v>
       </c>
       <c r="H70" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I70" t="str">
-        <v>R. CHATTO</v>
+        <v>F. MATUOD</v>
       </c>
       <c r="J70" t="str">
         <v/>
@@ -3316,18 +3305,18 @@
         <v/>
       </c>
       <c r="M70" t="str">
-        <v>DISMISSED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
+        <v>LIFE IMPRISONMENT ANA A FINE OF 400,00.00 PEOS</v>
+      </c>
+      <c r="P70" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>VII-14=-INV-14A-018</v>
+        <v>VII-14-INQ-13J-0188</v>
       </c>
       <c r="B71" t="str">
         <v>Invalid Date</v>
@@ -3336,19 +3325,19 @@
         <v/>
       </c>
       <c r="D71" t="str">
-        <v xml:space="preserve">ABELLANA,JEAN ARLENE C. </v>
+        <v>ABELLANA, LESTER PAUL @ POLPOL</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>VIOL OF R.A 1161 AS AMENDED BY R.A 8282</v>
+        <v>VIOL OF R.A 10591 (ILLEGAL POSSESION OF HIGH POWERED FIREARM)</v>
       </c>
       <c r="H71" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I71" t="str">
-        <v>B. BAUTISTA</v>
+        <v>F. MATUOD</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -3357,18 +3346,18 @@
         <v/>
       </c>
       <c r="M71" t="str">
-        <v>DISMISSED</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N71" t="str">
         <v/>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>VII-14-INQ-15K-0168</v>
+        <v>VII-14--INQ-13J-0189</v>
       </c>
       <c r="B72" t="str">
         <v>Invalid Date</v>
@@ -3377,13 +3366,13 @@
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>ABELLANA,JOANNE CLAIRE</v>
+        <v>ABELLANA,LESTER PAUL</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>VIOL OF SEC11,ART II,OF R.A 9165</v>
+        <v>VIOL OF SEC 2,ART II,R.A 9165</v>
       </c>
       <c r="H72" t="str">
         <v>Invalid Date</v>
@@ -3398,18 +3387,18 @@
         <v/>
       </c>
       <c r="M72" t="str">
-        <v>CONVICTED</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N72" t="str">
-        <v>LIFE IMPRISONMENT ANA A FINE OF 400,00.00 PEOS</v>
-      </c>
-      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>VII-14-INQ-13J-0188</v>
+        <v>VII-14-INQ-13J-0190</v>
       </c>
       <c r="B73" t="str">
         <v>Invalid Date</v>
@@ -3418,13 +3407,13 @@
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>ABELLANA, LESTER PAUL @ POLPOL</v>
+        <v>ABELLANA,LESTER PAUL</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>VIOL OF R.A 10591 (ILLEGAL POSSESION OF HIGH POWERED FIREARM)</v>
+        <v>VIOL OF SEC12,ART. II, R.A 9165</v>
       </c>
       <c r="H73" t="str">
         <v>Invalid Date</v>
@@ -3444,13 +3433,13 @@
       <c r="N73" t="str">
         <v/>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>VII-14--INQ-13J-0189</v>
+        <v>VII-14-INQ-13J-0187</v>
       </c>
       <c r="B74" t="str">
         <v>Invalid Date</v>
@@ -3465,13 +3454,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>VIOL OF SEC 2,ART II,R.A 9165</v>
+        <v>VIOL OF SEC 5,ART. II, R.A 9165</v>
       </c>
       <c r="H74" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I74" t="str">
-        <v>F. MATUOD</v>
+        <v>M. ANORA</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -3480,18 +3469,18 @@
         <v/>
       </c>
       <c r="M74" t="str">
-        <v>ACQUITTED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N74" t="str">
         <v/>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>VII-14-INQ-13J-0190</v>
+        <v>2004-718,719</v>
       </c>
       <c r="B75" t="str">
         <v>Invalid Date</v>
@@ -3500,19 +3489,19 @@
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>ABELLANA,LESTER PAUL</v>
+        <v>ABELLANA,MIGUEL</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>VIOL OF SEC12,ART. II, R.A 9165</v>
+        <v>VIOL OF B.P 22</v>
       </c>
       <c r="H75" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I75" t="str">
-        <v>F. MATUOD</v>
+        <v>N. UY</v>
       </c>
       <c r="J75" t="str">
         <v/>
@@ -3521,18 +3510,18 @@
         <v/>
       </c>
       <c r="M75" t="str">
-        <v>ACQUITTED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N75" t="str">
         <v/>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>VII-14-INQ-13J-0187</v>
+        <v>2004-721</v>
       </c>
       <c r="B76" t="str">
         <v>Invalid Date</v>
@@ -3541,19 +3530,19 @@
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>ABELLANA,LESTER PAUL</v>
+        <v>ABELLANA,MIGUEL</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>VIOL OF SEC 5,ART. II, R.A 9165</v>
+        <v>VIOL OF B.P 22</v>
       </c>
       <c r="H76" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I76" t="str">
-        <v>M. ANORA</v>
+        <v>A. RARA</v>
       </c>
       <c r="J76" t="str">
         <v/>
@@ -3567,13 +3556,13 @@
       <c r="N76" t="str">
         <v/>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2004-718,719</v>
+        <v>2004-720</v>
       </c>
       <c r="B77" t="str">
         <v>Invalid Date</v>
@@ -3588,13 +3577,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>VIOL OF B.P 22</v>
+        <v>VIOL OF BP 22</v>
       </c>
       <c r="H77" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I77" t="str">
-        <v>N. UY</v>
+        <v>A. RARA</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -3608,13 +3597,13 @@
       <c r="N77" t="str">
         <v/>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2004-721</v>
+        <v>2004-173</v>
       </c>
       <c r="B78" t="str">
         <v>Invalid Date</v>
@@ -3623,19 +3612,19 @@
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>ABELLANA,MIGUEL</v>
+        <v>ABRAU, JOEL</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>VIOL OF B.P 22</v>
+        <v>ESTAFA</v>
       </c>
       <c r="H78" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I78" t="str">
-        <v>A. RARA</v>
+        <v>N. CRISTOBAL</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -3644,18 +3633,18 @@
         <v/>
       </c>
       <c r="M78" t="str">
-        <v>CONVICTED</v>
+        <v>WITHDRAWN</v>
       </c>
       <c r="N78" t="str">
         <v/>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2004-720</v>
+        <v>VII-14-INV-010A-00042</v>
       </c>
       <c r="B79" t="str">
         <v>Invalid Date</v>
@@ -3664,19 +3653,19 @@
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>ABELLANA,MIGUEL</v>
+        <v>ABRAU,MARIETTA</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>VIOL OF BP 22</v>
+        <v>VIOL OF BP BLG. 22</v>
       </c>
       <c r="H79" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I79" t="str">
-        <v>A. RARA</v>
+        <v>C. SUPREMO</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -3685,18 +3674,18 @@
         <v/>
       </c>
       <c r="M79" t="str">
-        <v>CONVICTED</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N79" t="str">
         <v/>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2004-173</v>
+        <v>VII-14-INV-010A-00043</v>
       </c>
       <c r="B80" t="str">
         <v>Invalid Date</v>
@@ -3705,19 +3694,19 @@
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>ABRAU, JOEL</v>
+        <v>ABRAU,MARIETTA</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>ESTAFA</v>
+        <v>VIOL OF BP BLG. 22</v>
       </c>
       <c r="H80" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I80" t="str">
-        <v>N. CRISTOBAL</v>
+        <v>C. SUPREMO</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -3726,18 +3715,18 @@
         <v/>
       </c>
       <c r="M80" t="str">
-        <v>WITHDRAWN</v>
+        <v>ACQUITTED</v>
       </c>
       <c r="N80" t="str">
         <v/>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>VII-14-INV-010A-00042</v>
+        <v>VII-14-INV-010A-00044</v>
       </c>
       <c r="B81" t="str">
         <v>Invalid Date</v>
@@ -3746,13 +3735,13 @@
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>ABRAU,MARIETTA</v>
+        <v>ABRAU, MARIETTA</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>VIOL OF BP BLG. 22</v>
+        <v>VIOL OF BP BLG 22</v>
       </c>
       <c r="H81" t="str">
         <v>Invalid Date</v>
@@ -3772,13 +3761,13 @@
       <c r="N81" t="str">
         <v/>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>VII-14-INV-010A-00043</v>
+        <v>VII-14-INV-010A-00045</v>
       </c>
       <c r="B82" t="str">
         <v>Invalid Date</v>
@@ -3787,7 +3776,7 @@
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>ABRAU,MARIETTA</v>
+        <v>ABRAU, MARIETTA</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3813,13 +3802,13 @@
       <c r="N82" t="str">
         <v/>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>VII-14-INV-010A-00044</v>
+        <v>VI--14-INV-010A-00046</v>
       </c>
       <c r="B83" t="str">
         <v>Invalid Date</v>
@@ -3828,7 +3817,7 @@
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>ABRAU, MARIETTA</v>
+        <v>ABRAU,MARIETTA</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3854,13 +3843,13 @@
       <c r="N83" t="str">
         <v/>
       </c>
-      <c r="O83" t="str">
+      <c r="P83" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>VII-14-INV-010A-00045</v>
+        <v>VII-14-INV-010A-00047</v>
       </c>
       <c r="B84" t="str">
         <v>Invalid Date</v>
@@ -3875,7 +3864,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>VIOL OF BP BLG. 22</v>
+        <v>VIOL OF BP BLG 22</v>
       </c>
       <c r="H84" t="str">
         <v>Invalid Date</v>
@@ -3895,13 +3884,13 @@
       <c r="N84" t="str">
         <v/>
       </c>
-      <c r="O84" t="str">
+      <c r="P84" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>VI--14-INV-010A-00046</v>
+        <v>VII-14-INV-010A-00048</v>
       </c>
       <c r="B85" t="str">
         <v>Invalid Date</v>
@@ -3910,7 +3899,7 @@
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>ABRAU,MARIETTA</v>
+        <v>ABRAU, MARIETTA</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3936,13 +3925,13 @@
       <c r="N85" t="str">
         <v/>
       </c>
-      <c r="O85" t="str">
+      <c r="P85" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>VII-14-INV-010A-00047</v>
+        <v>VII-14-INV-010A-00049</v>
       </c>
       <c r="B86" t="str">
         <v>Invalid Date</v>
@@ -3977,13 +3966,13 @@
       <c r="N86" t="str">
         <v/>
       </c>
-      <c r="O86" t="str">
+      <c r="P86" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>VII-14-INV-010A-00048</v>
+        <v>VII-14-INV-010A-00050</v>
       </c>
       <c r="B87" t="str">
         <v>Invalid Date</v>
@@ -4018,13 +4007,13 @@
       <c r="N87" t="str">
         <v/>
       </c>
-      <c r="O87" t="str">
+      <c r="P87" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>VII-14-INV-010A-00049</v>
+        <v>VII-14-INV-091-00394</v>
       </c>
       <c r="B88" t="str">
         <v>Invalid Date</v>
@@ -4033,19 +4022,19 @@
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>ABRAU, MARIETTA</v>
+        <v>ABRAU, RUEL y AGAHAP</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>VIOL OF BP BLG 22</v>
+        <v>VIOL OF SEC 5,(A) OF R.A 9262</v>
       </c>
       <c r="H88" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I88" t="str">
-        <v>C. SUPREMO</v>
+        <v>N. CRISTOBAL</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4054,18 +4043,18 @@
         <v/>
       </c>
       <c r="M88" t="str">
-        <v>ACQUITTED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N88" t="str">
         <v/>
       </c>
-      <c r="O88" t="str">
+      <c r="P88" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>VII-14-INV-010A-00050</v>
+        <v>99-1028</v>
       </c>
       <c r="B89" t="str">
         <v>Invalid Date</v>
@@ -4074,19 +4063,19 @@
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>ABRAU, MARIETTA</v>
+        <v>ABREGANA,CARMELITA</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>VIOL OF BP BLG 22</v>
+        <v>VIOL OF P.D 1866 AS AMENDED</v>
       </c>
       <c r="H89" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I89" t="str">
-        <v>C. SUPREMO</v>
+        <v>A. RARA</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -4095,18 +4084,18 @@
         <v/>
       </c>
       <c r="M89" t="str">
-        <v>ACQUITTED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N89" t="str">
         <v/>
       </c>
-      <c r="O89" t="str">
+      <c r="P89" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>VII-14-INV-091-00394</v>
+        <v>2004-718 , 719</v>
       </c>
       <c r="B90" t="str">
         <v>Invalid Date</v>
@@ -4115,19 +4104,19 @@
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>ABRAU, RUEL y AGAHAP</v>
+        <v>ABELLANA,MIGUEL</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>VIOL OF SEC 5,(A) OF R.A 9262</v>
+        <v>VIOL OF B.P 22</v>
       </c>
       <c r="H90" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I90" t="str">
-        <v>N. CRISTOBAL</v>
+        <v>N. UY</v>
       </c>
       <c r="J90" t="str">
         <v/>
@@ -4136,18 +4125,18 @@
         <v/>
       </c>
       <c r="M90" t="str">
-        <v>DISMISSED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N90" t="str">
         <v/>
       </c>
-      <c r="O90" t="str">
+      <c r="P90" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>99-1028</v>
+        <v>2004 - 721</v>
       </c>
       <c r="B91" t="str">
         <v>Invalid Date</v>
@@ -4156,19 +4145,19 @@
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>ABREGANA,CARMELITA</v>
+        <v/>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>VIOL OF P.D 1866 AS AMENDED</v>
+        <v>VIOL OF B.P 22</v>
       </c>
       <c r="H91" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I91" t="str">
-        <v>A. RARA</v>
+        <v>N. UY</v>
       </c>
       <c r="J91" t="str">
         <v/>
@@ -4182,13 +4171,13 @@
       <c r="N91" t="str">
         <v/>
       </c>
-      <c r="O91" t="str">
+      <c r="P91" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2004-718 , 719</v>
+        <v>2004 - 720</v>
       </c>
       <c r="B92" t="str">
         <v>Invalid Date</v>
@@ -4223,13 +4212,13 @@
       <c r="N92" t="str">
         <v/>
       </c>
-      <c r="O92" t="str">
+      <c r="P92" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2004 - 721</v>
+        <v>VII-14-INV-14B-089</v>
       </c>
       <c r="B93" t="str">
         <v>Invalid Date</v>
@@ -4238,19 +4227,19 @@
         <v/>
       </c>
       <c r="D93" t="str">
-        <v/>
+        <v>ABREGANA,JAMES y NATAD</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>VIOL OF B.P 22</v>
+        <v>VIOL R.A 7610 (CHILD ABUSE)</v>
       </c>
       <c r="H93" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I93" t="str">
-        <v>N. UY</v>
+        <v>M. ANORA</v>
       </c>
       <c r="J93" t="str">
         <v/>
@@ -4259,39 +4248,39 @@
         <v/>
       </c>
       <c r="M93" t="str">
-        <v>CONVICTED</v>
+        <v>PROV.DISMISSED</v>
       </c>
       <c r="N93" t="str">
         <v/>
       </c>
-      <c r="O93" t="str">
+      <c r="P93" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2004 - 720</v>
+        <v>VII-14INQ-16F-0170</v>
       </c>
       <c r="B94" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C94" t="str">
-        <v/>
+        <v>MAREJIN AGUILAR</v>
       </c>
       <c r="D94" t="str">
-        <v>ABELLANA,MIGUEL</v>
+        <v>ABREGO,RODEL y ACHAPERO</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>VIOL OF B.P 22</v>
+        <v>THEFT</v>
       </c>
       <c r="H94" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I94" t="str">
-        <v>N. UY</v>
+        <v>B. BAUTISTA</v>
       </c>
       <c r="J94" t="str">
         <v/>
@@ -4300,39 +4289,39 @@
         <v/>
       </c>
       <c r="M94" t="str">
-        <v>CONVICTED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N94" t="str">
         <v/>
       </c>
-      <c r="O94" t="str">
+      <c r="P94" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>VII-14-INV-14B-089</v>
+        <v>VII-14-INQ-15L-0191</v>
       </c>
       <c r="B95" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C95" t="str">
-        <v/>
+        <v>GERALD MARMITO</v>
       </c>
       <c r="D95" t="str">
-        <v>ABREGANA,JAMES y NATAD</v>
+        <v>ABREGO,RODEL y ACHAPERO</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>VIOL R.A 7610 (CHILD ABUSE)</v>
+        <v>ROBBERY WITH FORCE UPON THINGS</v>
       </c>
       <c r="H95" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I95" t="str">
-        <v>M. ANORA</v>
+        <v>S. BULLONES</v>
       </c>
       <c r="J95" t="str">
         <v/>
@@ -4341,39 +4330,39 @@
         <v/>
       </c>
       <c r="M95" t="str">
-        <v>PROV.DISMISSED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N95" t="str">
         <v/>
       </c>
-      <c r="O95" t="str">
+      <c r="P95" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>VII-14INQ-16F-0170</v>
+        <v>VII-14-INQ-16D-0114</v>
       </c>
       <c r="B96" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C96" t="str">
-        <v>MAREJIN AGUILAR</v>
+        <v>PSUPT. VALE</v>
       </c>
       <c r="D96" t="str">
-        <v>ABREGO,RODEL y ACHAPERO</v>
+        <v>ABREGO, RODEL y ACHAPERO</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>THEFT</v>
+        <v>VIOL OF B.P BLG 6</v>
       </c>
       <c r="H96" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I96" t="str">
-        <v>B. BAUTISTA</v>
+        <v>C. GAMAS</v>
       </c>
       <c r="J96" t="str">
         <v/>
@@ -4382,24 +4371,24 @@
         <v/>
       </c>
       <c r="M96" t="str">
-        <v>DISMISSED</v>
+        <v>CONVICTED</v>
       </c>
       <c r="N96" t="str">
-        <v/>
-      </c>
-      <c r="O96" t="str">
+        <v>METED A FIN EOF 200.00 W/ SUBSIDIARY IMPRISONMENT IN CAE OF INSOLVENCY &amp; TO PAY THE COST OF SUIT</v>
+      </c>
+      <c r="P96" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>VII-14-INQ-15L-0191</v>
+        <v>VII-14-INQ-141-0177</v>
       </c>
       <c r="B97" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C97" t="str">
-        <v>GERALD MARMITO</v>
+        <v/>
       </c>
       <c r="D97" t="str">
         <v>ABREGO,RODEL y ACHAPERO</v>
@@ -4408,13 +4397,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>ROBBERY WITH FORCE UPON THINGS</v>
+        <v>VIOL OF B.P BLG 22</v>
       </c>
       <c r="H97" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I97" t="str">
-        <v>S. BULLONES</v>
+        <v>F. MATUOD</v>
       </c>
       <c r="J97" t="str">
         <v/>
@@ -4423,39 +4412,39 @@
         <v/>
       </c>
       <c r="M97" t="str">
-        <v>DISMISSED</v>
+        <v/>
       </c>
       <c r="N97" t="str">
         <v/>
       </c>
-      <c r="O97" t="str">
+      <c r="P97" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>VII-14-INQ-16D-0114</v>
+        <v>VII-14-INQ-16F-0204</v>
       </c>
       <c r="B98" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C98" t="str">
-        <v>PSUPT. VALE</v>
+        <v>PSUPT. G. VALE</v>
       </c>
       <c r="D98" t="str">
-        <v>ABREGO, RODEL y ACHAPERO</v>
+        <v>ABUCAY, JOEL y TAN</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>VIOL OF B.P BLG 6</v>
+        <v>VIOL OF SEC 11,ART. R.A 9165</v>
       </c>
       <c r="H98" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I98" t="str">
-        <v>C. GAMAS</v>
+        <v>M. ANORA</v>
       </c>
       <c r="J98" t="str">
         <v/>
@@ -4467,36 +4456,36 @@
         <v>CONVICTED</v>
       </c>
       <c r="N98" t="str">
-        <v>METED A FIN EOF 200.00 W/ SUBSIDIARY IMPRISONMENT IN CAE OF INSOLVENCY &amp; TO PAY THE COST OF SUIT</v>
-      </c>
-      <c r="O98" t="str">
+        <v>1 YEAR TO PAY A FINE OF 10,000.00</v>
+      </c>
+      <c r="P98" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>VII-14-INQ-141-0177</v>
+        <v>VII-14-INQ-22H-152</v>
       </c>
       <c r="B99" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C99" t="str">
-        <v/>
+        <v>RDE-UNIT 7</v>
       </c>
       <c r="D99" t="str">
-        <v>ABREGO,RODEL y ACHAPERO</v>
+        <v>ABUCAY,NOE y CABALLO</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>VIOL OF B.P BLG 22</v>
+        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
       </c>
       <c r="H99" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I99" t="str">
-        <v>F. MATUOD</v>
+        <v>GLENA LIM</v>
       </c>
       <c r="J99" t="str">
         <v/>
@@ -4505,39 +4494,39 @@
         <v/>
       </c>
       <c r="M99" t="str">
-        <v/>
+        <v>DISMISSED</v>
       </c>
       <c r="N99" t="str">
         <v/>
       </c>
-      <c r="O99" t="str">
+      <c r="P99" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>VII-14-INQ-16F-0204</v>
+        <v>VII-14-INQ-22H-153</v>
       </c>
       <c r="B100" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C100" t="str">
-        <v>PSUPT. G. VALE</v>
+        <v>RDE-UNIT 7</v>
       </c>
       <c r="D100" t="str">
-        <v>ABUCAY, JOEL y TAN</v>
+        <v>ABUCAY,NOE y CABALLO</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>VIOL OF SEC 11,ART. R.A 9165</v>
+        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
       </c>
       <c r="H100" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="I100" t="str">
-        <v>M. ANORA</v>
+        <v>GLENA LIM</v>
       </c>
       <c r="J100" t="str">
         <v/>
@@ -4546,100 +4535,147 @@
         <v/>
       </c>
       <c r="M100" t="str">
-        <v>CONVICTED</v>
+        <v>DISMISSED</v>
       </c>
       <c r="N100" t="str">
-        <v>1 YEAR TO PAY A FINE OF 10,000.00</v>
-      </c>
-      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
         <v>N/A</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>VII-14-INQ-22H-152</v>
+        <v>2000-868</v>
       </c>
       <c r="B101" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C101" t="str">
-        <v>RDE-UNIT 7</v>
+        <v>PALMERA, MELECIO</v>
       </c>
       <c r="D101" t="str">
-        <v>ABUCAY,NOE y CABALLO</v>
+        <v>ABDUL, ISMAEL</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Invalid Date</v>
+        <v>GRAVE THREAT</v>
       </c>
       <c r="I101" t="str">
-        <v>GLENA LIM</v>
+        <v>ACHAS</v>
       </c>
       <c r="J101" t="str">
-        <v/>
+        <v>M-14217</v>
       </c>
       <c r="K101" t="str">
         <v/>
       </c>
+      <c r="L101" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M101" t="str">
-        <v>DISMISSED</v>
+        <v/>
       </c>
       <c r="N101" t="str">
         <v/>
       </c>
-      <c r="O101" t="str">
-        <v>N/A</v>
+      <c r="P101" t="str">
+        <v>INDEX CARDS\ABDUL, ISMAEL_0001.pdf</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>VII-14-INQ-22H-153</v>
+        <v>2006-333</v>
       </c>
       <c r="B102" t="str">
         <v>Invalid Date</v>
       </c>
       <c r="C102" t="str">
-        <v>RDE-UNIT 7</v>
+        <v/>
       </c>
       <c r="D102" t="str">
-        <v>ABUCAY,NOE y CABALLO</v>
+        <v>ACERON, PIO JOHN</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>VIOL OF SEC 5,ART II OF R.A 9165</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Invalid Date</v>
+        <v>LESS SERIOUS PHYSICAL INJURIES</v>
       </c>
       <c r="I102" t="str">
-        <v>GLENA LIM</v>
+        <v>(J. SALISE)              C. SUPREMO</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>R-13245</v>
       </c>
       <c r="K102" t="str">
         <v/>
       </c>
+      <c r="L102" t="str">
+        <v>Invalid Date</v>
+      </c>
       <c r="M102" t="str">
-        <v>DISMISSED</v>
+        <v>Undergo Diversion Com. Program</v>
       </c>
       <c r="N102" t="str">
         <v/>
       </c>
-      <c r="O102" t="str">
+      <c r="P102" t="str">
+        <v>INDEX CARDS\ACERON, PIO JOHN_0001.pdf</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2342323</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="C103" t="str">
+        <v>test apple</v>
+      </c>
+      <c r="D103" t="str">
+        <v>joshua</v>
+      </c>
+      <c r="E103" t="str">
+        <v>loboc</v>
+      </c>
+      <c r="F103" t="str">
+        <v>raped</v>
+      </c>
+      <c r="H103" t="str">
+        <v>2026-01-06</v>
+      </c>
+      <c r="I103" t="str">
+        <v>james</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Reppublic Act 2104</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Tagbi</v>
+      </c>
+      <c r="L103" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="M103" t="str">
+        <v>Hehhe</v>
+      </c>
+      <c r="N103" t="str">
+        <v>14k</v>
+      </c>
+      <c r="O103" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="P103" t="str">
         <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:Q105"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -411,10 +411,11 @@
     <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="50.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +456,18 @@
         <v>Date Filed in Court</v>
       </c>
       <c r="M1" t="str">
+        <v>Final Offense</v>
+      </c>
+      <c r="N1" t="str">
         <v>Remarks Decision</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Penalty</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Decision Date</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Index Cards</v>
       </c>
     </row>
@@ -501,13 +505,13 @@
       <c r="L2" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
       <c r="N2" t="str">
         <v/>
       </c>
-      <c r="P2" t="str">
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>INDEX CARDS\ABALOS, LUCELLE y TUDTUD_0001.pdf</v>
       </c>
     </row>
@@ -539,13 +543,13 @@
       <c r="K3" t="str">
         <v/>
       </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
       <c r="N3" t="str">
         <v/>
       </c>
-      <c r="P3" t="str">
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
         <v>INDEX CARDS\ABAO, ELSA y SALON a.ka. LINDA_0001.pdf</v>
       </c>
     </row>
@@ -580,13 +584,13 @@
       <c r="K4" t="str">
         <v/>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>DISMISSED 10/25/2021</v>
       </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
         <v>INDEX CARDS\ABAY-ABAY, DEXTER  BRIAN y MAKINANO_0001.pdf</v>
       </c>
     </row>
@@ -618,13 +622,13 @@
       <c r="K5" t="str">
         <v/>
       </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
       <c r="N5" t="str">
         <v/>
       </c>
-      <c r="P5" t="str">
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -659,13 +663,13 @@
       <c r="L6" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
       <c r="N6" t="str">
         <v/>
       </c>
-      <c r="P6" t="str">
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
         <v>INDEX CARDS\ABING, GRACE y CINEZA_0001.pdf</v>
       </c>
     </row>
@@ -688,10 +692,10 @@
       <c r="I7" t="str">
         <v>ADOLFO M. DOROY</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -726,13 +730,13 @@
       <c r="K8" t="str">
         <v/>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -770,13 +774,13 @@
       <c r="L9" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
       <c r="N9" t="str">
         <v/>
       </c>
-      <c r="P9" t="str">
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
         <v>INDEX CARDS\ABUYABOR, CYRIL y UNGGAY_0001.pdf</v>
       </c>
     </row>
@@ -811,13 +815,13 @@
       <c r="L10" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>ARCHIVED 12/29/2000</v>
       </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
         <v>INDEX CARDS\ACASO, AGUSTINE JOSEPH_0001.pdf</v>
       </c>
     </row>
@@ -852,13 +856,13 @@
       <c r="L11" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
       <c r="N11" t="str">
         <v/>
       </c>
-      <c r="P11" t="str">
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
         <v>INDEX CARDS\ACEBES, GLEE_0001.pdf</v>
       </c>
     </row>
@@ -873,16 +877,13 @@
         <v>GESITA, BILLY CYRUS y SALAZAR</v>
       </c>
       <c r="D12" t="str">
-        <v>ACERON, PIO</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
+        <v>["ACERON, PIO"]</v>
       </c>
       <c r="F12" t="str">
         <v>THEFT</v>
       </c>
       <c r="H12" t="str">
-        <v>2004-07-08</v>
+        <v>2004-07-06</v>
       </c>
       <c r="I12" t="str">
         <v>A.S. RARA</v>
@@ -890,19 +891,13 @@
       <c r="J12" t="str">
         <v>R-15257</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
       <c r="L12" t="str">
-        <v>2004-07-15</v>
-      </c>
-      <c r="M12" t="str">
-        <v/>
+        <v>2004-07-13</v>
       </c>
       <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="Q12" t="str">
         <v>INDEX CARDS\ACERON, PIO_0001.pdf</v>
       </c>
     </row>
@@ -937,13 +932,13 @@
       <c r="L13" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
       <c r="N13" t="str">
         <v/>
       </c>
-      <c r="P13" t="str">
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
         <v>INDEX CARDS\ACERON, RODEL_0001.pdf</v>
       </c>
     </row>
@@ -975,13 +970,13 @@
       <c r="K14" t="str">
         <v/>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>DROPPED 8/16/2005</v>
       </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
         <v>INDEX CARDS\ACHAS, WILMA_0001.pdf</v>
       </c>
     </row>
@@ -1016,13 +1011,13 @@
       <c r="L15" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
       <c r="N15" t="str">
         <v/>
       </c>
-      <c r="P15" t="str">
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
         <v>INDEX CARDS\ACMAZAN, CHTIO y PAZ_0001.pdf</v>
       </c>
     </row>
@@ -1057,13 +1052,13 @@
       <c r="L16" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
       <c r="N16" t="str">
         <v/>
       </c>
-      <c r="P16" t="str">
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v>INDEX CARDS\ACTOB, RYAN a.ka. BRIAN_0001.pdf</v>
       </c>
     </row>
@@ -1098,13 +1093,13 @@
       <c r="L17" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
       <c r="N17" t="str">
         <v/>
       </c>
-      <c r="P17" t="str">
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
         <v>INDEX CARDS\ADANO, CATALINO O._0001.pdf</v>
       </c>
     </row>
@@ -1139,13 +1134,13 @@
       <c r="L18" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
       <c r="N18" t="str">
         <v/>
       </c>
-      <c r="P18" t="str">
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
         <v>INDEX CARDS\ADAPTAR, BENITO y BULLECER_0001.pdf</v>
       </c>
     </row>
@@ -1177,13 +1172,13 @@
       <c r="K19" t="str">
         <v/>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
       </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
       </c>
     </row>
@@ -1215,13 +1210,13 @@
       <c r="K20" t="str">
         <v/>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>FORWARDED TO OMBUDSMAN - VISAYAS</v>
       </c>
-      <c r="N20" t="str">
-        <v/>
-      </c>
-      <c r="P20" t="str">
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
         <v>INDEX CARDS\AGAS, ERNESTO F. (P SUPT.)_0001.pdf</v>
       </c>
     </row>
@@ -1253,13 +1248,13 @@
       <c r="K21" t="str">
         <v/>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>REFERRED TO SSS, TAGB. CITY BRANCH 9/10/2000</v>
       </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
         <v>INDEX CARDS\AGBAYANI, DOLORES  SHOPPER'S MART_0001.pdf</v>
       </c>
     </row>
@@ -1297,13 +1292,13 @@
       <c r="L22" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
       <c r="N22" t="str">
         <v/>
       </c>
-      <c r="P22" t="str">
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
         <v>INDEX CARDS\AGENAR, GEORGE &amp; AGENAR, MARY JUDITH_0001.pdf</v>
       </c>
     </row>
@@ -1341,13 +1336,13 @@
       <c r="L23" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
       <c r="N23" t="str">
         <v/>
       </c>
-      <c r="P23" t="str">
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
         <v>INDEX CARDS\AGOSTA, MARVIN y ILOY_0001.pdf</v>
       </c>
     </row>
@@ -1385,13 +1380,13 @@
       <c r="L24" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
       <c r="N24" t="str">
         <v/>
       </c>
-      <c r="P24" t="str">
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
         <v>INDEX CARDS\AGUAVIVA, CRISTITO, JR._0001.pdf</v>
       </c>
     </row>
@@ -1429,13 +1424,13 @@
       <c r="L25" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
       <c r="N25" t="str">
         <v/>
       </c>
-      <c r="P25" t="str">
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
         <v>AHAT, RIO</v>
       </c>
     </row>
@@ -1473,13 +1468,13 @@
       <c r="L26" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
       <c r="N26" t="str">
         <v/>
       </c>
-      <c r="P26" t="str">
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
         <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
       </c>
     </row>
@@ -1517,13 +1512,13 @@
       <c r="L27" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
       <c r="N27" t="str">
         <v/>
       </c>
-      <c r="P27" t="str">
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
         <v>INDEX CARDS\AGUIPO, IRENE H._0001.pdf</v>
       </c>
     </row>
@@ -1558,13 +1553,13 @@
       <c r="L28" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>WITHDRAWN 1/20/2006 CASE FALLS W/ IN THE JURISDICTION OF FAMILY COURT</v>
       </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="P28" t="str">
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v>INDEX CARDS\AHAT, RIO_0001.pdf</v>
       </c>
     </row>
@@ -1602,13 +1597,13 @@
       <c r="L29" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
       <c r="N29" t="str">
         <v/>
       </c>
-      <c r="P29" t="str">
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
         <v>INDEX CARDS\AHAT, RIO y ANDALES 062_0001.pdf</v>
       </c>
     </row>
@@ -1646,13 +1641,13 @@
       <c r="L30" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
       <c r="N30" t="str">
         <v/>
       </c>
-      <c r="P30" t="str">
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
         <v>INDEX CARDS\AHAT, RIO y ANDALES 061_0001_0001.pdf</v>
       </c>
     </row>
@@ -1690,13 +1685,13 @@
       <c r="L31" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
       <c r="N31" t="str">
         <v/>
       </c>
-      <c r="P31" t="str">
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
         <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
       </c>
     </row>
@@ -1734,13 +1729,13 @@
       <c r="L32" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
       <c r="N32" t="str">
         <v/>
       </c>
-      <c r="P32" t="str">
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
         <v>INDEX CARDS\ALAGADI, MARCOS_0001.pdf</v>
       </c>
     </row>
@@ -1775,13 +1770,13 @@
       <c r="L33" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
       <c r="N33" t="str">
         <v/>
       </c>
-      <c r="P33" t="str">
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
         <v>INDEX CARDS\ALAGO, LILIBETH_0001.pdf</v>
       </c>
     </row>
@@ -1819,13 +1814,13 @@
       <c r="L34" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
       <c r="N34" t="str">
         <v/>
       </c>
-      <c r="P34" t="str">
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
         <v>INDEX CARDS\ALANGADI, CASANODING y SULTAN 078_0001.pdf</v>
       </c>
     </row>
@@ -1863,13 +1858,13 @@
       <c r="L35" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
       <c r="N35" t="str">
         <v/>
       </c>
-      <c r="P35" t="str">
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
         <v>INDEX CARDS\ALAPAN, KENNETH y ALBARICO_0001.pdf</v>
       </c>
     </row>
@@ -1907,13 +1902,13 @@
       <c r="L36" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="P36" t="str">
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
         <v>INDEX CARDS\ALBARADO, SERVILLA y MAMBAJEN_0001.pdf</v>
       </c>
     </row>
@@ -1951,13 +1946,13 @@
       <c r="L37" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
       <c r="N37" t="str">
         <v/>
       </c>
-      <c r="P37" t="str">
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
         <v>INDEX CARDS\ALBERIO, CARLO y GALZIM_0001.pdf</v>
       </c>
     </row>
@@ -1992,13 +1987,13 @@
       <c r="L38" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
         <v>780-781 DISMISSED 1/17/2005</v>
       </c>
-      <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="P38" t="str">
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
         <v>INDEX CARDS\ALBIENDA, LILIAN y BUICO_0001.pdf</v>
       </c>
     </row>
@@ -2033,13 +2028,13 @@
       <c r="L39" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
       <c r="N39" t="str">
         <v/>
       </c>
-      <c r="P39" t="str">
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
         <v>INDEX CARDS\ALBIOS, SEVERINO y CABANG_0001.pdf</v>
       </c>
     </row>
@@ -2074,13 +2069,13 @@
       <c r="L40" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
         <v>DISMISSED 6/6/2011</v>
       </c>
-      <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="P40" t="str">
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
         <v>INDEX CARDS\ALDEPOLLA, IGNACIO_0001.pdf</v>
       </c>
     </row>
@@ -2115,13 +2110,13 @@
       <c r="K41" t="str">
         <v/>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <v>B.R 2</v>
       </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2156,13 +2151,13 @@
       <c r="K42" t="str">
         <v/>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
         <v>DROPPED</v>
       </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="P42" t="str">
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2197,13 +2192,13 @@
       <c r="K43" t="str">
         <v/>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
         <v>WITHDRAWN</v>
       </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="P43" t="str">
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2238,13 +2233,13 @@
       <c r="K44" t="str">
         <v/>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="P44" t="str">
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2279,13 +2274,13 @@
       <c r="K45" t="str">
         <v/>
       </c>
-      <c r="M45" t="str">
+      <c r="N45" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="P45" t="str">
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2320,13 +2315,13 @@
       <c r="K46" t="str">
         <v/>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="P46" t="str">
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2361,13 +2356,13 @@
       <c r="K47" t="str">
         <v/>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
         <v>DIVERSION PROCEEDINGSAT KATARUNGANG BRGY. OF S.BULLONES,BOHOL BR. 1</v>
       </c>
-      <c r="N47" t="str">
-        <v/>
-      </c>
-      <c r="P47" t="str">
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2402,13 +2397,13 @@
       <c r="K48" t="str">
         <v/>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
         <v>DROPPED</v>
       </c>
-      <c r="N48" t="str">
-        <v/>
-      </c>
-      <c r="P48" t="str">
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2443,13 +2438,13 @@
       <c r="K49" t="str">
         <v/>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
         <v>DROPPED</v>
       </c>
-      <c r="N49" t="str">
-        <v/>
-      </c>
-      <c r="P49" t="str">
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2484,13 +2479,13 @@
       <c r="K50" t="str">
         <v/>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="P50" t="str">
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2525,13 +2520,13 @@
       <c r="K51" t="str">
         <v/>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v>WITHDRWAN</v>
       </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-      <c r="P51" t="str">
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2566,13 +2561,13 @@
       <c r="K52" t="str">
         <v/>
       </c>
-      <c r="M52" t="str">
+      <c r="N52" t="str">
         <v>DROPPED</v>
       </c>
-      <c r="N52" t="str">
-        <v/>
-      </c>
-      <c r="P52" t="str">
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2607,13 +2602,13 @@
       <c r="K53" t="str">
         <v/>
       </c>
-      <c r="M53" t="str">
+      <c r="N53" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N53" t="str">
-        <v/>
-      </c>
-      <c r="P53" t="str">
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2648,13 +2643,13 @@
       <c r="K54" t="str">
         <v/>
       </c>
-      <c r="M54" t="str">
+      <c r="N54" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N54" t="str">
-        <v/>
-      </c>
-      <c r="P54" t="str">
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2689,13 +2684,13 @@
       <c r="K55" t="str">
         <v/>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N55" t="str">
-        <v/>
-      </c>
-      <c r="P55" t="str">
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2730,13 +2725,13 @@
       <c r="K56" t="str">
         <v/>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N56" t="str">
-        <v/>
-      </c>
-      <c r="P56" t="str">
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2771,13 +2766,13 @@
       <c r="K57" t="str">
         <v/>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <v>1 MS &amp; 15 DAYS OF ARRESTO MAYOR &amp; TO PAYA FINE OF 200.00 W/ ALL  THE ACCESORY PENALTIES  &amp; TO PAY THE COST</v>
       </c>
-      <c r="P57" t="str">
+      <c r="Q57" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2812,13 +2807,13 @@
       <c r="K58" t="str">
         <v/>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>IMPRISONMENT OF 1 MONTH &amp; TO PAY THE COST</v>
       </c>
-      <c r="P58" t="str">
+      <c r="Q58" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2853,13 +2848,13 @@
       <c r="K59" t="str">
         <v/>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <v>1 MOS &amp;  15 DAYS ARRESTO MAYOR &amp; TO PRIVATE COMPLAIN ANT THE AMOUNT OF 2000.00 AS CIVILM LIABILITY</v>
       </c>
-      <c r="P59" t="str">
+      <c r="Q59" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2894,13 +2889,13 @@
       <c r="K60" t="str">
         <v/>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <v>IMPRISONMENT OF 4 MONTHS &amp; TO PAY THE COST</v>
       </c>
-      <c r="P60" t="str">
+      <c r="Q60" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2935,13 +2930,13 @@
       <c r="K61" t="str">
         <v/>
       </c>
-      <c r="M61" t="str">
+      <c r="N61" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <v>IMPRISONMENT OF 2 MOS. AND TO PAY THE COST</v>
       </c>
-      <c r="P61" t="str">
+      <c r="Q61" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -2976,13 +2971,13 @@
       <c r="K62" t="str">
         <v/>
       </c>
-      <c r="M62" t="str">
+      <c r="N62" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N62" t="str">
-        <v/>
-      </c>
-      <c r="P62" t="str">
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3017,13 +3012,13 @@
       <c r="K63" t="str">
         <v/>
       </c>
-      <c r="M63" t="str">
+      <c r="N63" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="P63" t="str">
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3058,13 +3053,13 @@
       <c r="K64" t="str">
         <v/>
       </c>
-      <c r="M64" t="str">
+      <c r="N64" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="P64" t="str">
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3099,13 +3094,13 @@
       <c r="K65" t="str">
         <v/>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>DROPPED</v>
       </c>
-      <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="P65" t="str">
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3140,13 +3135,13 @@
       <c r="K66" t="str">
         <v/>
       </c>
-      <c r="M66" t="str">
+      <c r="N66" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="P66" t="str">
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3181,13 +3176,13 @@
       <c r="K67" t="str">
         <v/>
       </c>
-      <c r="M67" t="str">
+      <c r="N67" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="P67" t="str">
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3222,13 +3217,13 @@
       <c r="K68" t="str">
         <v/>
       </c>
-      <c r="M68" t="str">
+      <c r="N68" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="P68" t="str">
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3263,13 +3258,13 @@
       <c r="K69" t="str">
         <v/>
       </c>
-      <c r="M69" t="str">
+      <c r="N69" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N69" t="str">
-        <v/>
-      </c>
-      <c r="P69" t="str">
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3304,13 +3299,13 @@
       <c r="K70" t="str">
         <v/>
       </c>
-      <c r="M70" t="str">
+      <c r="N70" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>LIFE IMPRISONMENT ANA A FINE OF 400,00.00 PEOS</v>
       </c>
-      <c r="P70" t="str">
+      <c r="Q70" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3345,13 +3340,13 @@
       <c r="K71" t="str">
         <v/>
       </c>
-      <c r="M71" t="str">
+      <c r="N71" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N71" t="str">
-        <v/>
-      </c>
-      <c r="P71" t="str">
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3386,13 +3381,13 @@
       <c r="K72" t="str">
         <v/>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="P72" t="str">
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3427,13 +3422,13 @@
       <c r="K73" t="str">
         <v/>
       </c>
-      <c r="M73" t="str">
+      <c r="N73" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="P73" t="str">
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3468,13 +3463,13 @@
       <c r="K74" t="str">
         <v/>
       </c>
-      <c r="M74" t="str">
+      <c r="N74" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="P74" t="str">
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3509,13 +3504,13 @@
       <c r="K75" t="str">
         <v/>
       </c>
-      <c r="M75" t="str">
+      <c r="N75" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="P75" t="str">
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3550,13 +3545,13 @@
       <c r="K76" t="str">
         <v/>
       </c>
-      <c r="M76" t="str">
+      <c r="N76" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N76" t="str">
-        <v/>
-      </c>
-      <c r="P76" t="str">
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3591,13 +3586,13 @@
       <c r="K77" t="str">
         <v/>
       </c>
-      <c r="M77" t="str">
+      <c r="N77" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="P77" t="str">
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3632,13 +3627,13 @@
       <c r="K78" t="str">
         <v/>
       </c>
-      <c r="M78" t="str">
+      <c r="N78" t="str">
         <v>WITHDRAWN</v>
       </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="P78" t="str">
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3673,13 +3668,13 @@
       <c r="K79" t="str">
         <v/>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="P79" t="str">
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3714,13 +3709,13 @@
       <c r="K80" t="str">
         <v/>
       </c>
-      <c r="M80" t="str">
+      <c r="N80" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="P80" t="str">
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3755,13 +3750,13 @@
       <c r="K81" t="str">
         <v/>
       </c>
-      <c r="M81" t="str">
+      <c r="N81" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="P81" t="str">
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3796,13 +3791,13 @@
       <c r="K82" t="str">
         <v/>
       </c>
-      <c r="M82" t="str">
+      <c r="N82" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="P82" t="str">
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3837,13 +3832,13 @@
       <c r="K83" t="str">
         <v/>
       </c>
-      <c r="M83" t="str">
+      <c r="N83" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="P83" t="str">
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3878,13 +3873,13 @@
       <c r="K84" t="str">
         <v/>
       </c>
-      <c r="M84" t="str">
+      <c r="N84" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N84" t="str">
-        <v/>
-      </c>
-      <c r="P84" t="str">
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3919,13 +3914,13 @@
       <c r="K85" t="str">
         <v/>
       </c>
-      <c r="M85" t="str">
+      <c r="N85" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="P85" t="str">
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -3960,13 +3955,13 @@
       <c r="K86" t="str">
         <v/>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="P86" t="str">
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4001,13 +3996,13 @@
       <c r="K87" t="str">
         <v/>
       </c>
-      <c r="M87" t="str">
+      <c r="N87" t="str">
         <v>ACQUITTED</v>
       </c>
-      <c r="N87" t="str">
-        <v/>
-      </c>
-      <c r="P87" t="str">
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4042,13 +4037,13 @@
       <c r="K88" t="str">
         <v/>
       </c>
-      <c r="M88" t="str">
+      <c r="N88" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N88" t="str">
-        <v/>
-      </c>
-      <c r="P88" t="str">
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4083,13 +4078,13 @@
       <c r="K89" t="str">
         <v/>
       </c>
-      <c r="M89" t="str">
+      <c r="N89" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N89" t="str">
-        <v/>
-      </c>
-      <c r="P89" t="str">
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4124,13 +4119,13 @@
       <c r="K90" t="str">
         <v/>
       </c>
-      <c r="M90" t="str">
+      <c r="N90" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N90" t="str">
-        <v/>
-      </c>
-      <c r="P90" t="str">
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4165,13 +4160,13 @@
       <c r="K91" t="str">
         <v/>
       </c>
-      <c r="M91" t="str">
+      <c r="N91" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="P91" t="str">
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4206,13 +4201,13 @@
       <c r="K92" t="str">
         <v/>
       </c>
-      <c r="M92" t="str">
+      <c r="N92" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N92" t="str">
-        <v/>
-      </c>
-      <c r="P92" t="str">
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4247,13 +4242,13 @@
       <c r="K93" t="str">
         <v/>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
         <v>PROV.DISMISSED</v>
       </c>
-      <c r="N93" t="str">
-        <v/>
-      </c>
-      <c r="P93" t="str">
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4288,13 +4283,13 @@
       <c r="K94" t="str">
         <v/>
       </c>
-      <c r="M94" t="str">
+      <c r="N94" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="P94" t="str">
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4329,13 +4324,13 @@
       <c r="K95" t="str">
         <v/>
       </c>
-      <c r="M95" t="str">
+      <c r="N95" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N95" t="str">
-        <v/>
-      </c>
-      <c r="P95" t="str">
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4370,13 +4365,13 @@
       <c r="K96" t="str">
         <v/>
       </c>
-      <c r="M96" t="str">
+      <c r="N96" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N96" t="str">
+      <c r="O96" t="str">
         <v>METED A FIN EOF 200.00 W/ SUBSIDIARY IMPRISONMENT IN CAE OF INSOLVENCY &amp; TO PAY THE COST OF SUIT</v>
       </c>
-      <c r="P96" t="str">
+      <c r="Q96" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4411,13 +4406,13 @@
       <c r="K97" t="str">
         <v/>
       </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
       <c r="N97" t="str">
         <v/>
       </c>
-      <c r="P97" t="str">
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4452,13 +4447,13 @@
       <c r="K98" t="str">
         <v/>
       </c>
-      <c r="M98" t="str">
+      <c r="N98" t="str">
         <v>CONVICTED</v>
       </c>
-      <c r="N98" t="str">
+      <c r="O98" t="str">
         <v>1 YEAR TO PAY A FINE OF 10,000.00</v>
       </c>
-      <c r="P98" t="str">
+      <c r="Q98" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4493,13 +4488,13 @@
       <c r="K99" t="str">
         <v/>
       </c>
-      <c r="M99" t="str">
+      <c r="N99" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N99" t="str">
-        <v/>
-      </c>
-      <c r="P99" t="str">
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4534,13 +4529,13 @@
       <c r="K100" t="str">
         <v/>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
         <v>DISMISSED</v>
       </c>
-      <c r="N100" t="str">
-        <v/>
-      </c>
-      <c r="P100" t="str">
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
         <v>N/A</v>
       </c>
     </row>
@@ -4575,13 +4570,13 @@
       <c r="L101" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M101" t="str">
-        <v/>
-      </c>
       <c r="N101" t="str">
         <v/>
       </c>
-      <c r="P101" t="str">
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
         <v>INDEX CARDS\ABDUL, ISMAEL_0001.pdf</v>
       </c>
     </row>
@@ -4616,66 +4611,136 @@
       <c r="L102" t="str">
         <v>Invalid Date</v>
       </c>
-      <c r="M102" t="str">
+      <c r="N102" t="str">
         <v>Undergo Diversion Com. Program</v>
       </c>
-      <c r="N102" t="str">
-        <v/>
-      </c>
-      <c r="P102" t="str">
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
         <v>INDEX CARDS\ACERON, PIO JOHN_0001.pdf</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2342323</v>
+        <v>test232</v>
       </c>
       <c r="B103" t="str">
-        <v>Invalid Date</v>
+        <v>2026-03-24</v>
       </c>
       <c r="C103" t="str">
-        <v>test apple</v>
+        <v>popo</v>
       </c>
       <c r="D103" t="str">
-        <v>joshua</v>
+        <v>["clemen","sofia","daryl","joshua"]</v>
       </c>
       <c r="E103" t="str">
-        <v>loboc</v>
+        <v>san isidro bohol</v>
       </c>
       <c r="F103" t="str">
-        <v>raped</v>
+        <v>robbery</v>
       </c>
       <c r="H103" t="str">
-        <v>2026-01-06</v>
+        <v>2026-03-25</v>
       </c>
       <c r="I103" t="str">
-        <v>james</v>
+        <v>atty doroy</v>
       </c>
       <c r="J103" t="str">
-        <v>Reppublic Act 2104</v>
+        <v>5675665</v>
       </c>
       <c r="K103" t="str">
-        <v>Tagbi</v>
-      </c>
-      <c r="L103" t="str">
-        <v>2026-01-07</v>
+        <v>2</v>
       </c>
       <c r="M103" t="str">
-        <v>Hehhe</v>
+        <v>guilty</v>
       </c>
       <c r="N103" t="str">
-        <v>14k</v>
-      </c>
-      <c r="O103" t="str">
-        <v>2026-03-11</v>
+        <v>Filed in court</v>
       </c>
       <c r="P103" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>VII-14-INQ-22C-13424</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="C104" t="str">
+        <v>daryl</v>
+      </c>
+      <c r="D104" t="str">
+        <v>["testt"]</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Anda Bohol</v>
+      </c>
+      <c r="F104" t="str">
+        <v>asd</v>
+      </c>
+      <c r="I104" t="str">
+        <v>asdas</v>
+      </c>
+      <c r="J104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="N104" t="str">
+        <v>Dismissed</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>VII-14-INQ-22C-134241</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C105" t="str">
+        <v>darylss</v>
+      </c>
+      <c r="D105" t="str">
+        <v>["testt","asda","asd"]</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Anda Bohol</v>
+      </c>
+      <c r="F105" t="str">
+        <v>asd</v>
+      </c>
+      <c r="I105" t="str">
+        <v>asdas</v>
+      </c>
+      <c r="J105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K105" t="str">
+        <v>3</v>
+      </c>
+      <c r="L105" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="M105" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="N105" t="str">
+        <v>Convicted</v>
+      </c>
+      <c r="Q105" t="str">
         <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:Q110"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -479,37 +479,34 @@
         <v>Invalid Date</v>
       </c>
       <c r="C2" t="str">
-        <v>EVANGELINE M. GABI</v>
+        <v>["EVANGELINE M. GABI"]</v>
       </c>
       <c r="D2" t="str">
-        <v>VII-14-INV 23F-299</v>
+        <v>["VII-14-INV 23F-299"]</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>[""]</v>
       </c>
       <c r="F2" t="str">
         <v>ESTAFA IN REL. TO R.A. 10175 KNOWN AS CYBERCRIME PREVENTION ACT OF 2021</v>
       </c>
-      <c r="H2" t="str">
-        <v>Invalid Date</v>
-      </c>
       <c r="I2" t="str">
         <v>J. R. CESAR</v>
       </c>
       <c r="J2" t="str">
-        <v>R-25552</v>
+        <v>["R-25552"]</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>["2"]</v>
       </c>
       <c r="L2" t="str">
         <v>Invalid Date</v>
       </c>
+      <c r="M2" t="str">
+        <v>[""]</v>
+      </c>
       <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
+        <v>["Pending"]</v>
       </c>
       <c r="Q2" t="str">
         <v>INDEX CARDS\ABALOS, LUCELLE y TUDTUD_0001.pdf</v>
@@ -4623,43 +4620,40 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>test232</v>
+        <v>VII-14-INQ-22C-134241</v>
       </c>
       <c r="B103" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C103" t="str">
-        <v>popo</v>
+        <v>darylss</v>
       </c>
       <c r="D103" t="str">
-        <v>["clemen","sofia","daryl","joshua"]</v>
+        <v>["testt","asda","asd"]</v>
       </c>
       <c r="E103" t="str">
-        <v>san isidro bohol</v>
+        <v>Anda Bohol</v>
       </c>
       <c r="F103" t="str">
-        <v>robbery</v>
-      </c>
-      <c r="H103" t="str">
-        <v>2026-03-25</v>
+        <v>asd</v>
       </c>
       <c r="I103" t="str">
-        <v>atty doroy</v>
+        <v>asdas</v>
       </c>
       <c r="J103" t="str">
-        <v>5675665</v>
+        <v>N/A</v>
       </c>
       <c r="K103" t="str">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L103" t="str">
+        <v>2026-03-26</v>
       </c>
       <c r="M103" t="str">
-        <v>guilty</v>
+        <v>Ongoing</v>
       </c>
       <c r="N103" t="str">
-        <v>Filed in court</v>
-      </c>
-      <c r="P103" t="str">
-        <v>2026-03-26</v>
+        <v>Convicted</v>
       </c>
       <c r="Q103" t="str">
         <v>N/A</v>
@@ -4673,22 +4667,31 @@
         <v>2026-03-18</v>
       </c>
       <c r="C104" t="str">
-        <v>daryl</v>
+        <v>test</v>
       </c>
       <c r="D104" t="str">
-        <v>["testt"]</v>
+        <v>["test1","test2","test3"]</v>
       </c>
       <c r="E104" t="str">
         <v>Anda Bohol</v>
       </c>
       <c r="F104" t="str">
-        <v>asd</v>
+        <v>attempted murder</v>
+      </c>
+      <c r="H104" t="str">
+        <v>2026-03-26</v>
       </c>
       <c r="I104" t="str">
-        <v>asdas</v>
+        <v>Atty. Joshua</v>
       </c>
       <c r="J104" t="str">
-        <v>N/A</v>
+        <v>4467565</v>
+      </c>
+      <c r="L104" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="M104" t="str">
+        <v>guilty</v>
       </c>
       <c r="N104" t="str">
         <v>Dismissed</v>
@@ -4699,48 +4702,274 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>VII-14-INQ-22C-134241</v>
+        <v>VII-14-INQ-22C-134242</v>
       </c>
       <c r="B105" t="str">
-        <v>2026-03-14</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C105" t="str">
-        <v>darylss</v>
+        <v>kian</v>
       </c>
       <c r="D105" t="str">
-        <v>["testt","asda","asd"]</v>
+        <v>["test14","tes4","test6"]</v>
       </c>
       <c r="E105" t="str">
         <v>Anda Bohol</v>
       </c>
       <c r="F105" t="str">
-        <v>asd</v>
+        <v>attempted murder</v>
+      </c>
+      <c r="H105" t="str">
+        <v>2026-03-26</v>
       </c>
       <c r="I105" t="str">
-        <v>asdas</v>
+        <v>Atty. Joshua</v>
       </c>
       <c r="J105" t="str">
-        <v>N/A</v>
+        <v>635464</v>
       </c>
       <c r="K105" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L105" t="str">
         <v>2026-03-26</v>
       </c>
       <c r="M105" t="str">
-        <v>Ongoing</v>
+        <v>attempted</v>
       </c>
       <c r="N105" t="str">
+        <v>Dismissed</v>
+      </c>
+      <c r="P105" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>VII-14-INQ-22C-13426</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2026-02-07</v>
+      </c>
+      <c r="C106" t="str">
+        <v>John Sotto</v>
+      </c>
+      <c r="D106" t="str">
+        <v>["Vico Sotto"]</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Booy, Tagbilaran City</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Viol. of R.A. 9262 (VAWC)</v>
+      </c>
+      <c r="G106" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="H106" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Pros. Doroy</v>
+      </c>
+      <c r="N106" t="str">
+        <v>Dismissed</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>VII-14-INQ-22C-13423</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C107" t="str">
+        <v>["aman"]</v>
+      </c>
+      <c r="D107" t="str">
+        <v>["shomin"]</v>
+      </c>
+      <c r="E107" t="str">
+        <v>["testt"]</v>
+      </c>
+      <c r="F107" t="str">
+        <v>murder</v>
+      </c>
+      <c r="G107" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="H107" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="I107" t="str">
+        <v>adolfo foroy</v>
+      </c>
+      <c r="J107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="N107" t="str">
         <v>Convicted</v>
       </c>
-      <c r="Q105" t="str">
-        <v>N/A</v>
+      <c r="P107" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>VII-345-67567</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C108" t="str">
+        <v>["kopiko","totong","sosoy"]</v>
+      </c>
+      <c r="D108" t="str">
+        <v>["Compuesto","Test 3","juancho"]</v>
+      </c>
+      <c r="E108" t="str">
+        <v>["calape","tubigon","sagbayan"]</v>
+      </c>
+      <c r="F108" t="str">
+        <v>murder</v>
+      </c>
+      <c r="H108" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Atty. Joshua</v>
+      </c>
+      <c r="J108" t="str">
+        <v>657453</v>
+      </c>
+      <c r="K108" t="str">
+        <v>2</v>
+      </c>
+      <c r="L108" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="M108" t="str">
+        <v>Robbery</v>
+      </c>
+      <c r="N108" t="str">
+        <v>Dismissed</v>
+      </c>
+      <c r="P108" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>VII-14-INQ-23H-195</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2023-07-29</v>
+      </c>
+      <c r="C109" t="str">
+        <v>["PNP-TAGBILARAN CITY"]</v>
+      </c>
+      <c r="D109" t="str">
+        <v>["ZAIMON ABAY y LUMAGBAS","JOSEPH LIM III y ZAFRA"]</v>
+      </c>
+      <c r="E109" t="str">
+        <v>["Tagbilaran City","Tagbilaran City"]</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Violation of Sec. 5, Art. II of R.A. 9165</v>
+      </c>
+      <c r="H109" t="str">
+        <v>2023-07-29</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Josie Vida C. Sempron</v>
+      </c>
+      <c r="J109" t="str">
+        <v>["R-27679","R-27679"]</v>
+      </c>
+      <c r="K109" t="str">
+        <v>["4","1"]</v>
+      </c>
+      <c r="L109" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M109" t="str">
+        <v>["murder","robbery"]</v>
+      </c>
+      <c r="N109" t="str">
+        <v>["Filed in Court","Filed in Court"]</v>
+      </c>
+      <c r="P109" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>VII-14-INQ-22C-13424175</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C110" t="str">
+        <v>["jep2","mimimng","dodong"]</v>
+      </c>
+      <c r="D110" t="str">
+        <v>["simba","totong","jopay kamusta kana"]</v>
+      </c>
+      <c r="E110" t="str">
+        <v>["taloto","koroko"]</v>
+      </c>
+      <c r="F110" t="str">
+        <v>murder</v>
+      </c>
+      <c r="G110" t="str">
+        <v>2026-02-14</v>
+      </c>
+      <c r="H110" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Atty. Doroy</v>
+      </c>
+      <c r="J110" t="str">
+        <v>["N/A","N/A","4534543"]</v>
+      </c>
+      <c r="K110" t="str">
+        <v>["2","2","2"]</v>
+      </c>
+      <c r="L110" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M110" t="str">
+        <v>["","","attempted"]</v>
+      </c>
+      <c r="N110" t="str">
+        <v>["Dismissed","Dismissed","Filed in Court"]</v>
+      </c>
+      <c r="P110" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>/uploads/index_cards/indexcard-1773238533278-115631718.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q110"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q104"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -4620,40 +4620,46 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>VII-14-INQ-22C-134241</v>
+        <v>VII-14-INQ-23H-195</v>
       </c>
       <c r="B103" t="str">
-        <v>2026-03-14</v>
+        <v>2023-07-29</v>
       </c>
       <c r="C103" t="str">
-        <v>darylss</v>
+        <v>["PNP-TAGBILARAN CITY"]</v>
       </c>
       <c r="D103" t="str">
-        <v>["testt","asda","asd"]</v>
+        <v>["ZAIMON ABAY y LUMAGBAS","JOSEPH LIM III y ZAFRA"]</v>
       </c>
       <c r="E103" t="str">
-        <v>Anda Bohol</v>
+        <v>["Tagbilaran City","Tagbilaran City"]</v>
       </c>
       <c r="F103" t="str">
-        <v>asd</v>
+        <v>Violation of Sec. 5, Art. II of R.A. 9165</v>
+      </c>
+      <c r="H103" t="str">
+        <v>2023-07-29</v>
       </c>
       <c r="I103" t="str">
-        <v>asdas</v>
+        <v>Josie Vida C. Sempron</v>
       </c>
       <c r="J103" t="str">
-        <v>N/A</v>
+        <v>["R-27679","R-27679"]</v>
       </c>
       <c r="K103" t="str">
-        <v>3</v>
+        <v>["4","1"]</v>
       </c>
       <c r="L103" t="str">
-        <v>2026-03-26</v>
+        <v>Invalid Date</v>
       </c>
       <c r="M103" t="str">
-        <v>Ongoing</v>
+        <v>["murder","robbery"]</v>
       </c>
       <c r="N103" t="str">
-        <v>Convicted</v>
+        <v>["Filed in Court","Filed in Court"]</v>
+      </c>
+      <c r="P103" t="str">
+        <v>2026-03-09</v>
       </c>
       <c r="Q103" t="str">
         <v>N/A</v>
@@ -4661,315 +4667,57 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>VII-14-INQ-22C-13424</v>
+        <v>Test_2123</v>
       </c>
       <c r="B104" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C104" t="str">
-        <v>test</v>
+        <v>["Kian Bullanday","Rainer Goloso","Ken Maniwang"]</v>
       </c>
       <c r="D104" t="str">
-        <v>["test1","test2","test3"]</v>
+        <v>["James Lloyd Antiola","Joshua Galamiton","Jeff Alexis Arcayan"]</v>
       </c>
       <c r="E104" t="str">
-        <v>Anda Bohol</v>
+        <v>["San Isidro Bohol","Jagna Bohol","Tagbilaran Bohol"]</v>
       </c>
       <c r="F104" t="str">
-        <v>attempted murder</v>
+        <v>Attempted Murder</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-15</v>
       </c>
       <c r="I104" t="str">
-        <v>Atty. Joshua</v>
+        <v xml:space="preserve">Atty.Arvin </v>
       </c>
       <c r="J104" t="str">
-        <v>4467565</v>
+        <v>["23434534","45634523423","56234"]</v>
+      </c>
+      <c r="K104" t="str">
+        <v>["3","1","1"]</v>
       </c>
       <c r="L104" t="str">
-        <v>2026-03-13</v>
+        <v>Invalid Date</v>
       </c>
       <c r="M104" t="str">
-        <v>guilty</v>
+        <v>["murder","attempted murder","robbery"]</v>
       </c>
       <c r="N104" t="str">
-        <v>Dismissed</v>
+        <v>["Filed in Court","Filed in Court","Filed in Court"]</v>
+      </c>
+      <c r="O104" t="str">
+        <v>community service</v>
+      </c>
+      <c r="P104" t="str">
+        <v>2026-03-29</v>
       </c>
       <c r="Q104" t="str">
         <v>N/A</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>VII-14-INQ-22C-134242</v>
-      </c>
-      <c r="B105" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="C105" t="str">
-        <v>kian</v>
-      </c>
-      <c r="D105" t="str">
-        <v>["test14","tes4","test6"]</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Anda Bohol</v>
-      </c>
-      <c r="F105" t="str">
-        <v>attempted murder</v>
-      </c>
-      <c r="H105" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="I105" t="str">
-        <v>Atty. Joshua</v>
-      </c>
-      <c r="J105" t="str">
-        <v>635464</v>
-      </c>
-      <c r="K105" t="str">
-        <v>2</v>
-      </c>
-      <c r="L105" t="str">
-        <v>2026-03-26</v>
-      </c>
-      <c r="M105" t="str">
-        <v>attempted</v>
-      </c>
-      <c r="N105" t="str">
-        <v>Dismissed</v>
-      </c>
-      <c r="P105" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="Q105" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>VII-14-INQ-22C-13426</v>
-      </c>
-      <c r="B106" t="str">
-        <v>2026-02-07</v>
-      </c>
-      <c r="C106" t="str">
-        <v>John Sotto</v>
-      </c>
-      <c r="D106" t="str">
-        <v>["Vico Sotto"]</v>
-      </c>
-      <c r="E106" t="str">
-        <v>Booy, Tagbilaran City</v>
-      </c>
-      <c r="F106" t="str">
-        <v>Viol. of R.A. 9262 (VAWC)</v>
-      </c>
-      <c r="G106" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="H106" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="I106" t="str">
-        <v>Pros. Doroy</v>
-      </c>
-      <c r="N106" t="str">
-        <v>Dismissed</v>
-      </c>
-      <c r="Q106" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>VII-14-INQ-22C-13423</v>
-      </c>
-      <c r="B107" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C107" t="str">
-        <v>["aman"]</v>
-      </c>
-      <c r="D107" t="str">
-        <v>["shomin"]</v>
-      </c>
-      <c r="E107" t="str">
-        <v>["testt"]</v>
-      </c>
-      <c r="F107" t="str">
-        <v>murder</v>
-      </c>
-      <c r="G107" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="H107" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="I107" t="str">
-        <v>adolfo foroy</v>
-      </c>
-      <c r="J107" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N107" t="str">
-        <v>Convicted</v>
-      </c>
-      <c r="P107" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="Q107" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>VII-345-67567</v>
-      </c>
-      <c r="B108" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C108" t="str">
-        <v>["kopiko","totong","sosoy"]</v>
-      </c>
-      <c r="D108" t="str">
-        <v>["Compuesto","Test 3","juancho"]</v>
-      </c>
-      <c r="E108" t="str">
-        <v>["calape","tubigon","sagbayan"]</v>
-      </c>
-      <c r="F108" t="str">
-        <v>murder</v>
-      </c>
-      <c r="H108" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="I108" t="str">
-        <v>Atty. Joshua</v>
-      </c>
-      <c r="J108" t="str">
-        <v>657453</v>
-      </c>
-      <c r="K108" t="str">
-        <v>2</v>
-      </c>
-      <c r="L108" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="M108" t="str">
-        <v>Robbery</v>
-      </c>
-      <c r="N108" t="str">
-        <v>Dismissed</v>
-      </c>
-      <c r="P108" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="Q108" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>VII-14-INQ-23H-195</v>
-      </c>
-      <c r="B109" t="str">
-        <v>2023-07-29</v>
-      </c>
-      <c r="C109" t="str">
-        <v>["PNP-TAGBILARAN CITY"]</v>
-      </c>
-      <c r="D109" t="str">
-        <v>["ZAIMON ABAY y LUMAGBAS","JOSEPH LIM III y ZAFRA"]</v>
-      </c>
-      <c r="E109" t="str">
-        <v>["Tagbilaran City","Tagbilaran City"]</v>
-      </c>
-      <c r="F109" t="str">
-        <v>Violation of Sec. 5, Art. II of R.A. 9165</v>
-      </c>
-      <c r="H109" t="str">
-        <v>2023-07-29</v>
-      </c>
-      <c r="I109" t="str">
-        <v>Josie Vida C. Sempron</v>
-      </c>
-      <c r="J109" t="str">
-        <v>["R-27679","R-27679"]</v>
-      </c>
-      <c r="K109" t="str">
-        <v>["4","1"]</v>
-      </c>
-      <c r="L109" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="M109" t="str">
-        <v>["murder","robbery"]</v>
-      </c>
-      <c r="N109" t="str">
-        <v>["Filed in Court","Filed in Court"]</v>
-      </c>
-      <c r="P109" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="Q109" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>VII-14-INQ-22C-13424175</v>
-      </c>
-      <c r="B110" t="str">
-        <v>2026-02-21</v>
-      </c>
-      <c r="C110" t="str">
-        <v>["jep2","mimimng","dodong"]</v>
-      </c>
-      <c r="D110" t="str">
-        <v>["simba","totong","jopay kamusta kana"]</v>
-      </c>
-      <c r="E110" t="str">
-        <v>["taloto","koroko"]</v>
-      </c>
-      <c r="F110" t="str">
-        <v>murder</v>
-      </c>
-      <c r="G110" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="H110" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="I110" t="str">
-        <v>Atty. Doroy</v>
-      </c>
-      <c r="J110" t="str">
-        <v>["N/A","N/A","4534543"]</v>
-      </c>
-      <c r="K110" t="str">
-        <v>["2","2","2"]</v>
-      </c>
-      <c r="L110" t="str">
-        <v>Invalid Date</v>
-      </c>
-      <c r="M110" t="str">
-        <v>["","","attempted"]</v>
-      </c>
-      <c r="N110" t="str">
-        <v>["Dismissed","Dismissed","Filed in Court"]</v>
-      </c>
-      <c r="P110" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="Q110" t="str">
-        <v>/uploads/index_cards/indexcard-1773238533278-115631718.png</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q108"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -4670,10 +4670,10 @@
         <v>Test_2123</v>
       </c>
       <c r="B104" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C104" t="str">
-        <v>["Kian Bullanday","Rainer Goloso","Ken Maniwang"]</v>
+        <v>["Kian Bullanday","Rainer Goloso","Ken Maniwang","Jennah Rose Antiola"]</v>
       </c>
       <c r="D104" t="str">
         <v>["James Lloyd Antiola","Joshua Galamiton","Jeff Alexis Arcayan"]</v>
@@ -4685,7 +4685,7 @@
         <v>Attempted Murder</v>
       </c>
       <c r="H104" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-09</v>
       </c>
       <c r="I104" t="str">
         <v xml:space="preserve">Atty.Arvin </v>
@@ -4700,24 +4700,212 @@
         <v>Invalid Date</v>
       </c>
       <c r="M104" t="str">
-        <v>["murder","attempted murder","robbery"]</v>
+        <v>["murder","","robbery"]</v>
       </c>
       <c r="N104" t="str">
-        <v>["Filed in Court","Filed in Court","Filed in Court"]</v>
+        <v>["Filed in Court","Convicted","Filed in Court"]</v>
       </c>
       <c r="O104" t="str">
         <v>community service</v>
       </c>
       <c r="P104" t="str">
-        <v>2026-03-29</v>
+        <v>2026-03-23</v>
       </c>
       <c r="Q104" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>0101010.11</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C105" t="str">
+        <v>["Birad","Carajay","udtuhan"]</v>
+      </c>
+      <c r="D105" t="str">
+        <v>["Tavera","Arcayan","bulanday"]</v>
+      </c>
+      <c r="E105" t="str">
+        <v>["Jagna","Taloto","Panglao"]</v>
+      </c>
+      <c r="F105" t="str">
+        <v>murder</v>
+      </c>
+      <c r="G105" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="H105" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="I105" t="str">
+        <v xml:space="preserve">Atty.Arvin </v>
+      </c>
+      <c r="J105" t="str">
+        <v>["N/A","N/A","N/A"]</v>
+      </c>
+      <c r="K105" t="str">
+        <v>["","",""]</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M105" t="str">
+        <v>["","",""]</v>
+      </c>
+      <c r="N105" t="str">
+        <v>["Filed in Court","Filed in Court","Omwoemwomfwomfw"]</v>
+      </c>
+      <c r="O105" t="str">
+        <v>100k</v>
+      </c>
+      <c r="P105" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>test12312</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="C106" t="str">
+        <v>["jaim","simmas","asoaa"]</v>
+      </c>
+      <c r="D106" t="str">
+        <v>["kasdas","fadsfdsf","svds"]</v>
+      </c>
+      <c r="E106" t="str">
+        <v>["asdasd","asdas","dghdfgd"]</v>
+      </c>
+      <c r="F106" t="str">
+        <v>murder</v>
+      </c>
+      <c r="H106" t="str">
+        <v>2026-03-22</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Atty. Joshua</v>
+      </c>
+      <c r="J106" t="str">
+        <v>["12312","8888",""]</v>
+      </c>
+      <c r="K106" t="str">
+        <v>["2","8",""]</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M106" t="str">
+        <v>["murder","guilty",""]</v>
+      </c>
+      <c r="N106" t="str">
+        <v>["Filed in Court","Filed in Court","Convicted"]</v>
+      </c>
+      <c r="P106" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>testtt33</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C107" t="str">
+        <v>["aaa","ssss","dddd"]</v>
+      </c>
+      <c r="D107" t="str">
+        <v>["afsda","dfdfdf","gfdgdf"]</v>
+      </c>
+      <c r="E107" t="str">
+        <v>["fdgf","dfdfddf","dfgdfg"]</v>
+      </c>
+      <c r="F107" t="str">
+        <v>attempted murder</v>
+      </c>
+      <c r="H107" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Atty. Joshua</v>
+      </c>
+      <c r="J107" t="str">
+        <v>["11234","asa22","q213"]</v>
+      </c>
+      <c r="K107" t="str">
+        <v>["1","2","2"]</v>
+      </c>
+      <c r="L107" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M107" t="str">
+        <v>["murder","guilty","murder"]</v>
+      </c>
+      <c r="N107" t="str">
+        <v>["Filed in Court","Filed in Court","Filed in Court"]</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>VII-14-INV-26C-134</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="C108" t="str">
+        <v>["Michael Jordan"]</v>
+      </c>
+      <c r="D108" t="str">
+        <v>["Lebron James","Anthony Davis"]</v>
+      </c>
+      <c r="E108" t="str">
+        <v>["Taloto, Tagbilaran City","Bool, Tagbilaran City"]</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Estafa</v>
+      </c>
+      <c r="H108" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Pros. Enerlas</v>
+      </c>
+      <c r="J108" t="str">
+        <v>["",""]</v>
+      </c>
+      <c r="K108" t="str">
+        <v>["",""]</v>
+      </c>
+      <c r="L108" t="str">
+        <v>Invalid Date</v>
+      </c>
+      <c r="M108" t="str">
+        <v>["",""]</v>
+      </c>
+      <c r="N108" t="str">
+        <v>["Dismissed","Dismissed"]</v>
+      </c>
+      <c r="Q108" t="str">
         <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -500,7 +500,7 @@
         <v>VII-14-INQ-20I-361</v>
       </c>
       <c r="B2" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C2" t="str">
         <v>TAGBILARAN CITY PNP</v>
@@ -562,7 +562,7 @@
         <v>VII-14-INQ-20I-360</v>
       </c>
       <c r="B3" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C3" t="str">
         <v>TAGBILARAN CITY PNP</v>
@@ -934,7 +934,7 @@
         <v>2005-19</v>
       </c>
       <c r="B9" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>2006-45</v>
       </c>
       <c r="B10" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -1120,7 +1120,7 @@
         <v>VII-14-INQ-20A-04</v>
       </c>
       <c r="B12" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C12" t="str">
         <v>SALARDA, MYRA A.</v>
@@ -1306,7 +1306,7 @@
         <v>96-3427-3429</v>
       </c>
       <c r="B15" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1430,7 +1430,7 @@
         <v>3434</v>
       </c>
       <c r="B17" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -2050,7 +2050,7 @@
         <v>VII-14-INV-22D-071</v>
       </c>
       <c r="B27" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C27" t="str">
         <v>CIDG-BOHOL</v>
@@ -2112,7 +2112,7 @@
         <v>VII-14-INV-22D-070</v>
       </c>
       <c r="B28" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C28" t="str">
         <v>CIDG-BOHOL</v>
@@ -2174,7 +2174,7 @@
         <v>VII-14-INQ-17A-027</v>
       </c>
       <c r="B29" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -2360,7 +2360,7 @@
         <v>24H-260</v>
       </c>
       <c r="B32" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C32" t="str">
         <v>CADAYDAY, NEMESIA</v>
@@ -2422,7 +2422,7 @@
         <v>24H-260</v>
       </c>
       <c r="B33" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C33" t="str">
         <v>CADAYDAY,NEMESIA</v>
@@ -2484,7 +2484,7 @@
         <v>24H-261</v>
       </c>
       <c r="B34" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C34" t="str">
         <v>ALIVIADO, KHY</v>
@@ -2546,7 +2546,7 @@
         <v>24H-261</v>
       </c>
       <c r="B35" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C35" t="str">
         <v>CADAYDAY,NEMESIA</v>
@@ -2608,7 +2608,7 @@
         <v>96-228</v>
       </c>
       <c r="B36" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -2670,7 +2670,7 @@
         <v>96-229</v>
       </c>
       <c r="B37" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -2732,7 +2732,7 @@
         <v>96-230</v>
       </c>
       <c r="B38" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -2794,7 +2794,7 @@
         <v>VII-14-INV-2OL-366</v>
       </c>
       <c r="B39" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C39" t="str">
         <v>PNP - TAGBILARAN CITY</v>
@@ -2980,7 +2980,7 @@
         <v>96-306</v>
       </c>
       <c r="B42" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3042,7 +3042,7 @@
         <v>96-307</v>
       </c>
       <c r="B43" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3104,7 +3104,7 @@
         <v>96-308</v>
       </c>
       <c r="B44" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3352,7 +3352,7 @@
         <v>VII-14-INQ-221-197</v>
       </c>
       <c r="B48" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C48" t="str">
         <v>PDEA-BOHOL</v>
@@ -3476,7 +3476,7 @@
         <v>VII-14-INQ-221-196</v>
       </c>
       <c r="B50" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C50" t="str">
         <v>PDEA-BOHOL</v>
@@ -3538,7 +3538,7 @@
         <v>3145</v>
       </c>
       <c r="B51" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3600,7 +3600,7 @@
         <v>3144</v>
       </c>
       <c r="B52" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3786,7 +3786,7 @@
         <v>VII-14-INV-175-0325</v>
       </c>
       <c r="B55" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3972,7 +3972,7 @@
         <v>VII-14-INV-20A-27</v>
       </c>
       <c r="B58" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C58" t="str">
         <v>CIDG-BOHOL</v>
@@ -4034,7 +4034,7 @@
         <v>VII-14-INV-20A-26</v>
       </c>
       <c r="B59" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C59" t="str">
         <v>CIDG-BOHOL</v>
@@ -4158,7 +4158,7 @@
         <v>2000-129</v>
       </c>
       <c r="B61" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4220,7 +4220,7 @@
         <v>2000-130</v>
       </c>
       <c r="B62" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4282,7 +4282,7 @@
         <v>2000-131</v>
       </c>
       <c r="B63" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4344,7 +4344,7 @@
         <v>2000-132</v>
       </c>
       <c r="B64" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4406,7 +4406,7 @@
         <v>2000-133</v>
       </c>
       <c r="B65" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4468,7 +4468,7 @@
         <v>2000-134</v>
       </c>
       <c r="B66" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
         <v>2000-135</v>
       </c>
       <c r="B67" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4592,7 +4592,7 @@
         <v>2000-136</v>
       </c>
       <c r="B68" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4654,7 +4654,7 @@
         <v>2000-137</v>
       </c>
       <c r="B69" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4716,7 +4716,7 @@
         <v>2000-138</v>
       </c>
       <c r="B70" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4778,7 +4778,7 @@
         <v>2000-139</v>
       </c>
       <c r="B71" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -4840,7 +4840,7 @@
         <v>VII-14-INQ-24K-285</v>
       </c>
       <c r="B72" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C72" t="str">
         <v>NBI-CEBU OFFICE -MANDAUE CITY</v>
@@ -4902,7 +4902,7 @@
         <v>99-317</v>
       </c>
       <c r="B73" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -4964,7 +4964,7 @@
         <v>VII-14-INV-20H-207</v>
       </c>
       <c r="B74" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C74" t="str">
         <v>BINAMIRA, GARRY NOEL E.</v>
@@ -5026,7 +5026,7 @@
         <v>24J-242</v>
       </c>
       <c r="B75" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C75" t="str">
         <v>PDEA-BOHOL</v>
@@ -5088,7 +5088,7 @@
         <v>24J-243</v>
       </c>
       <c r="B76" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C76" t="str">
         <v>PDEA-BOHOL</v>
@@ -5150,7 +5150,7 @@
         <v>24J-244</v>
       </c>
       <c r="B77" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C77" t="str">
         <v>PDEA-BOHOL</v>
@@ -5212,7 +5212,7 @@
         <v>24J-245</v>
       </c>
       <c r="B78" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C78" t="str">
         <v>PDEA-BOHOL</v>
@@ -5336,7 +5336,7 @@
         <v>89-289 89-289-A 89-289-B 89-289-C 89-289-D</v>
       </c>
       <c r="B80" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C80" t="str">
         <v/>
@@ -5398,7 +5398,7 @@
         <v>VII-14-INV-21A-079</v>
       </c>
       <c r="B81" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C81" t="str">
         <v>STARLITE MARINE INDUSTRIAL SERVICES CORP.</v>
@@ -5460,7 +5460,7 @@
         <v>24K-300</v>
       </c>
       <c r="B82" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C82" t="str">
         <v>PNP - TAGBILARAN CITY</v>
@@ -6452,7 +6452,7 @@
         <v>96-1464</v>
       </c>
       <c r="B98" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -6700,7 +6700,7 @@
         <v>92-195</v>
       </c>
       <c r="B102" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -6762,7 +6762,7 @@
         <v>VII-14-INV-24B-55</v>
       </c>
       <c r="B103" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C103" t="str">
         <v>BAJA, NOEL B.</v>
@@ -6824,7 +6824,7 @@
         <v>86-226</v>
       </c>
       <c r="B104" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -6886,7 +6886,7 @@
         <v>97-3828</v>
       </c>
       <c r="B105" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -6948,7 +6948,7 @@
         <v>97-3829</v>
       </c>
       <c r="B106" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -7010,7 +7010,7 @@
         <v>97-3830</v>
       </c>
       <c r="B107" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C107" t="str">
         <v/>
@@ -7072,7 +7072,7 @@
         <v>97-3831</v>
       </c>
       <c r="B108" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C108" t="str">
         <v/>
@@ -7754,7 +7754,7 @@
         <v>3510</v>
       </c>
       <c r="B119" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C119" t="str">
         <v/>
@@ -7816,7 +7816,7 @@
         <v>96-2673</v>
       </c>
       <c r="B120" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C120" t="str">
         <v/>
@@ -7878,7 +7878,7 @@
         <v>96-2674</v>
       </c>
       <c r="B121" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C121" t="str">
         <v/>
@@ -7940,7 +7940,7 @@
         <v>96-2675</v>
       </c>
       <c r="B122" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C122" t="str">
         <v/>
@@ -8002,7 +8002,7 @@
         <v>97-3037</v>
       </c>
       <c r="B123" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C123" t="str">
         <v/>
@@ -8064,7 +8064,7 @@
         <v>97-3038</v>
       </c>
       <c r="B124" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C124" t="str">
         <v/>
@@ -8126,7 +8126,7 @@
         <v>97-3039</v>
       </c>
       <c r="B125" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C125" t="str">
         <v/>
@@ -8188,7 +8188,7 @@
         <v>97-1336</v>
       </c>
       <c r="B126" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -8250,7 +8250,7 @@
         <v>97-1336</v>
       </c>
       <c r="B127" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C127" t="str">
         <v/>
@@ -8374,7 +8374,7 @@
         <v>97-1339</v>
       </c>
       <c r="B129" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C129" t="str">
         <v/>
@@ -8436,7 +8436,7 @@
         <v>97-1340</v>
       </c>
       <c r="B130" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C130" t="str">
         <v/>
@@ -8498,7 +8498,7 @@
         <v>97-1341</v>
       </c>
       <c r="B131" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C131" t="str">
         <v/>
@@ -8560,7 +8560,7 @@
         <v>96-2554</v>
       </c>
       <c r="B132" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -8622,7 +8622,7 @@
         <v>96-2555</v>
       </c>
       <c r="B133" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -8684,7 +8684,7 @@
         <v>96-2556</v>
       </c>
       <c r="B134" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -8746,7 +8746,7 @@
         <v>96-2557</v>
       </c>
       <c r="B135" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -8808,7 +8808,7 @@
         <v>96-2558</v>
       </c>
       <c r="B136" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C136" t="str">
         <v/>
@@ -8870,7 +8870,7 @@
         <v>24l-222</v>
       </c>
       <c r="B137" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C137" t="str">
         <v>TAGBILARAN CITY - PNP</v>
@@ -8932,7 +8932,7 @@
         <v>24l-223</v>
       </c>
       <c r="B138" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C138" t="str">
         <v>TAGBILARAN CITY - PNP</v>
@@ -9366,7 +9366,7 @@
         <v>97-397</v>
       </c>
       <c r="B145" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C145" t="str">
         <v/>
@@ -9428,7 +9428,7 @@
         <v>2005-537</v>
       </c>
       <c r="B146" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C146" t="str">
         <v/>
@@ -9738,7 +9738,7 @@
         <v>2002-999</v>
       </c>
       <c r="B151" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C151" t="str">
         <v/>
@@ -9800,7 +9800,7 @@
         <v>2002-1000</v>
       </c>
       <c r="B152" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C152" t="str">
         <v/>
@@ -9862,7 +9862,7 @@
         <v>2002-1001</v>
       </c>
       <c r="B153" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C153" t="str">
         <v/>
@@ -9924,7 +9924,7 @@
         <v>2002-1002</v>
       </c>
       <c r="B154" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C154" t="str">
         <v/>
@@ -9986,7 +9986,7 @@
         <v>3961</v>
       </c>
       <c r="B155" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C155" t="str">
         <v/>
@@ -10048,7 +10048,7 @@
         <v>VII-14-INQ-23B-061</v>
       </c>
       <c r="B156" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C156" t="str">
         <v>PIU-BOHOL PPO</v>
@@ -10110,7 +10110,7 @@
         <v>VII-14-INQ-23B-061</v>
       </c>
       <c r="B157" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C157" t="str">
         <v>PIU BOHOL PPO</v>
@@ -10172,7 +10172,7 @@
         <v>VII-14-INQ-23B-062</v>
       </c>
       <c r="B158" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C158" t="str">
         <v>PIU-BOHOL PPO</v>
@@ -10234,7 +10234,7 @@
         <v>VII-14-INQ-23B-062</v>
       </c>
       <c r="B159" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C159" t="str">
         <v>PIU BOHOL PPO</v>
@@ -10420,7 +10420,7 @@
         <v>93-463</v>
       </c>
       <c r="B162" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C162" t="str">
         <v/>
@@ -10482,7 +10482,7 @@
         <v>93-464</v>
       </c>
       <c r="B163" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C163" t="str">
         <v/>
@@ -10544,7 +10544,7 @@
         <v>96-1680</v>
       </c>
       <c r="B164" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C164" t="str">
         <v/>
@@ -10606,7 +10606,7 @@
         <v>96-1681</v>
       </c>
       <c r="B165" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C165" t="str">
         <v/>
@@ -10668,7 +10668,7 @@
         <v>96-1682</v>
       </c>
       <c r="B166" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C166" t="str">
         <v/>
@@ -10730,7 +10730,7 @@
         <v>96-1697</v>
       </c>
       <c r="B167" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C167" t="str">
         <v/>
@@ -10792,7 +10792,7 @@
         <v>96-1698</v>
       </c>
       <c r="B168" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C168" t="str">
         <v/>
@@ -10854,7 +10854,7 @@
         <v>96-1699</v>
       </c>
       <c r="B169" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C169" t="str">
         <v/>
@@ -10978,7 +10978,7 @@
         <v>VII-14-INQ-24J-257</v>
       </c>
       <c r="B171" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C171" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -11040,7 +11040,7 @@
         <v>VII-14-INQ-24J-257</v>
       </c>
       <c r="B172" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C172" t="str">
         <v>PNP- TAGBILARAN CITY</v>
@@ -11102,7 +11102,7 @@
         <v>96-831</v>
       </c>
       <c r="B173" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C173" t="str">
         <v/>
@@ -11164,7 +11164,7 @@
         <v>VII-14-INV-24J-316</v>
       </c>
       <c r="B174" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C174" t="str">
         <v>ROSALEJOS, ALFONSO LIGO</v>
@@ -11226,7 +11226,7 @@
         <v>VII-14-INV-24J-316 b</v>
       </c>
       <c r="B175" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C175" t="str">
         <v>ROSALEJOS, ALFONSO LIGO</v>
@@ -11288,7 +11288,7 @@
         <v>97-3034</v>
       </c>
       <c r="B176" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -11350,7 +11350,7 @@
         <v>97-3035</v>
       </c>
       <c r="B177" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -11412,7 +11412,7 @@
         <v>97-3036</v>
       </c>
       <c r="B178" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C178" t="str">
         <v/>
@@ -11474,7 +11474,7 @@
         <v>96-1724</v>
       </c>
       <c r="B179" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C179" t="str">
         <v/>
@@ -11536,7 +11536,7 @@
         <v>96-1725</v>
       </c>
       <c r="B180" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C180" t="str">
         <v/>
@@ -11598,7 +11598,7 @@
         <v>96-1726</v>
       </c>
       <c r="B181" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -11660,7 +11660,7 @@
         <v>96-1574</v>
       </c>
       <c r="B182" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -11722,7 +11722,7 @@
         <v>96-1575</v>
       </c>
       <c r="B183" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -11784,7 +11784,7 @@
         <v>96-1576</v>
       </c>
       <c r="B184" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -11846,7 +11846,7 @@
         <v>98-004</v>
       </c>
       <c r="B185" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C185" t="str">
         <v/>
@@ -11908,7 +11908,7 @@
         <v>98-005</v>
       </c>
       <c r="B186" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -12280,7 +12280,7 @@
         <v>VII-14-INQ-20K-408</v>
       </c>
       <c r="B192" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C192" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -12342,7 +12342,7 @@
         <v>VII-14-INQ-20K-408</v>
       </c>
       <c r="B193" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C193" t="str">
         <v>PNP TAGBILARAN CITY</v>
@@ -12466,7 +12466,7 @@
         <v>VII-14-INQ-19E-197</v>
       </c>
       <c r="B195" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C195" t="str">
         <v>TAGBILARAN CITY POLICE</v>
@@ -13396,7 +13396,7 @@
         <v>VII-14-INV-20E-99</v>
       </c>
       <c r="B210" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C210" t="str">
         <v>FERNANDEZ, EULALIA A.</v>
@@ -13458,7 +13458,7 @@
         <v>VII-14-INV-18D-0132</v>
       </c>
       <c r="B211" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C211" t="str">
         <v>FCB, REP BY: GALAB, ANTHONY B.</v>
@@ -13520,7 +13520,7 @@
         <v>VII-14-INV-17H-0230</v>
       </c>
       <c r="B212" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C212" t="str">
         <v>A-1-BY TAGASLING, JOSEPHINE B.</v>
@@ -13582,7 +13582,7 @@
         <v>VII-14-INV-17H-0230 -A</v>
       </c>
       <c r="B213" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C213" t="str">
         <v>A-1-BY TAGASLING, JOSEPHINE B.</v>
@@ -13644,7 +13644,7 @@
         <v>VII-14-INV-18K-445</v>
       </c>
       <c r="B214" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C214" t="str">
         <v>GALLA, JOHN S.</v>
@@ -13706,7 +13706,7 @@
         <v>VII-14-INV-20E-100</v>
       </c>
       <c r="B215" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C215" t="str">
         <v>FERNANDEZ, EULALIA A.</v>
@@ -13768,7 +13768,7 @@
         <v>VII-14-INV-21B-30</v>
       </c>
       <c r="B216" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C216" t="str">
         <v>CIDG-BOHOL</v>
@@ -13830,7 +13830,7 @@
         <v>VII-14-INV-21B-31</v>
       </c>
       <c r="B217" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C217" t="str">
         <v>CIDG-BOHOL</v>
@@ -13892,7 +13892,7 @@
         <v>24E-175</v>
       </c>
       <c r="B218" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C218" t="str">
         <v>VICTORIANO B. TIROL III AND WILL TYRON B. TIROL</v>
@@ -13954,7 +13954,7 @@
         <v>24E-176</v>
       </c>
       <c r="B219" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C219" t="str">
         <v>VICTORIANO B. TIROL III AND WILL TYRON B. TIROL</v>
@@ -14016,7 +14016,7 @@
         <v>97-1371</v>
       </c>
       <c r="B220" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C220" t="str">
         <v/>
@@ -14078,7 +14078,7 @@
         <v>VII-14-INQ-191-360</v>
       </c>
       <c r="B221" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C221" t="str">
         <v>PNP - TAGBILARAN CITY</v>
@@ -14140,7 +14140,7 @@
         <v>VII-14-INV-22B-037</v>
       </c>
       <c r="B222" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C222" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14202,7 +14202,7 @@
         <v>VII-14-INV-22B-038</v>
       </c>
       <c r="B223" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C223" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14264,7 +14264,7 @@
         <v>VII-14-INV-22B-039</v>
       </c>
       <c r="B224" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C224" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14326,7 +14326,7 @@
         <v>VII-14-INV-22B-040</v>
       </c>
       <c r="B225" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C225" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14388,7 +14388,7 @@
         <v>3636</v>
       </c>
       <c r="B226" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C226" t="str">
         <v/>
@@ -14450,7 +14450,7 @@
         <v>3341</v>
       </c>
       <c r="B227" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C227" t="str">
         <v/>
@@ -14512,7 +14512,7 @@
         <v>VII-14-INQ-22G-131</v>
       </c>
       <c r="B228" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C228" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -14636,7 +14636,7 @@
         <v>VII-14-INV-22L-453</v>
       </c>
       <c r="B230" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C230" t="str">
         <v>TAMPOS, MARIA IVY R.</v>
@@ -14822,7 +14822,7 @@
         <v>3430</v>
       </c>
       <c r="B233" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C233" t="str">
         <v/>
@@ -14884,7 +14884,7 @@
         <v>98-1063</v>
       </c>
       <c r="B234" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C234" t="str">
         <v/>
@@ -14946,7 +14946,7 @@
         <v>98-1063-A</v>
       </c>
       <c r="B235" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C235" t="str">
         <v/>
@@ -15008,7 +15008,7 @@
         <v>97-360</v>
       </c>
       <c r="B236" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C236" t="str">
         <v/>
@@ -15070,7 +15070,7 @@
         <v>97-361</v>
       </c>
       <c r="B237" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C237" t="str">
         <v/>
@@ -15132,7 +15132,7 @@
         <v>97-362</v>
       </c>
       <c r="B238" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C238" t="str">
         <v/>
@@ -15194,7 +15194,7 @@
         <v>3633</v>
       </c>
       <c r="B239" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C239" t="str">
         <v/>
@@ -15256,7 +15256,7 @@
         <v>362</v>
       </c>
       <c r="B240" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C240" t="str">
         <v/>
@@ -15380,7 +15380,7 @@
         <v>VII-14-INQ-19B-005</v>
       </c>
       <c r="B242" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C242" t="str">
         <v>NBI, TAGBILARAN CITY</v>
@@ -15442,7 +15442,7 @@
         <v>97-1337</v>
       </c>
       <c r="B243" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C243" t="str">
         <v/>
@@ -15566,7 +15566,7 @@
         <v>VII-14-INV-24I-286</v>
       </c>
       <c r="B245" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C245" t="str">
         <v>XU, FLORIE MUNEZ</v>
@@ -15628,7 +15628,7 @@
         <v>VII-14-INV-24I-287</v>
       </c>
       <c r="B246" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C246" t="str">
         <v>XU, FLORIE MUNEZ</v>
@@ -15690,7 +15690,7 @@
         <v>VII-14-INV-24I-288</v>
       </c>
       <c r="B247" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C247" t="str">
         <v>XU, FLORIE MUNEZ</v>
@@ -15938,7 +15938,7 @@
         <v>95-999</v>
       </c>
       <c r="B251" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C251" t="str">
         <v/>
@@ -16000,7 +16000,7 @@
         <v>24l-224</v>
       </c>
       <c r="B252" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C252" t="str">
         <v>LAIZA LOPEZ y BAUTISTA</v>
@@ -16062,7 +16062,7 @@
         <v>VII-14-INV-20J-284</v>
       </c>
       <c r="B253" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C253" t="str">
         <v>SSS-TAGBILARAN  CITY</v>
@@ -16124,7 +16124,7 @@
         <v>VII-14-INQ-19K-456</v>
       </c>
       <c r="B254" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C254" t="str">
         <v>BPPO, PIB, TAGBILARAN CITY</v>
@@ -16248,7 +16248,7 @@
         <v>VII-14-INV-22C-113</v>
       </c>
       <c r="B256" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C256" t="str">
         <v>ALBELDA, ANALOU S.</v>
@@ -16310,7 +16310,7 @@
         <v>VII-14-INQ-19L-476</v>
       </c>
       <c r="B257" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C257" t="str">
         <v>TAGB. CITY PNP</v>
@@ -16372,7 +16372,7 @@
         <v>VII-14-INQ-19L-336</v>
       </c>
       <c r="B258" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C258" t="str">
         <v>PNP, BOHOL</v>
@@ -16434,7 +16434,7 @@
         <v>VII-14-INQ-19I-336</v>
       </c>
       <c r="B259" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C259" t="str">
         <v>PNP, BOHOL</v>
@@ -16496,7 +16496,7 @@
         <v>VII-14-INQ-20K-409</v>
       </c>
       <c r="B260" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C260" t="str">
         <v>PNP TAGBILARAN CITY</v>
@@ -16558,7 +16558,7 @@
         <v>VII-14-INQ-20B-57</v>
       </c>
       <c r="B261" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C261" t="str">
         <v>PNP, BOHOL</v>
@@ -16620,7 +16620,7 @@
         <v>97-2372</v>
       </c>
       <c r="B262" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C262" t="str">
         <v/>
@@ -16682,7 +16682,7 @@
         <v>97-2373</v>
       </c>
       <c r="B263" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C263" t="str">
         <v/>
@@ -16744,7 +16744,7 @@
         <v>97-2374</v>
       </c>
       <c r="B264" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C264" t="str">
         <v/>
@@ -16868,7 +16868,7 @@
         <v>97-1622-A</v>
       </c>
       <c r="B266" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C266" t="str">
         <v/>
@@ -16930,7 +16930,7 @@
         <v>VII-14-INV-22H-328</v>
       </c>
       <c r="B267" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C267" t="str">
         <v>PDEA-BOHOL</v>
@@ -17054,7 +17054,7 @@
         <v>VII-14-INV-18K-252</v>
       </c>
       <c r="B269" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C269" t="str">
         <v>NBI, BOHOL                                            REP BY: RENNAN AUGUSTUS OLIVA</v>
@@ -17116,7 +17116,7 @@
         <v>VII-14-INV-18K-253</v>
       </c>
       <c r="B270" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C270" t="str">
         <v>NBI, BOHOL                                            REP BY: RENNAN AUGUSTUS OLIVA</v>
@@ -17240,7 +17240,7 @@
         <v>97-420</v>
       </c>
       <c r="B272" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C272" t="str">
         <v/>
@@ -17302,7 +17302,7 @@
         <v>97-421</v>
       </c>
       <c r="B273" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C273" t="str">
         <v/>
@@ -17364,7 +17364,7 @@
         <v>96-4164</v>
       </c>
       <c r="B274" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C274" t="str">
         <v/>
@@ -17426,7 +17426,7 @@
         <v>96-4165</v>
       </c>
       <c r="B275" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C275" t="str">
         <v/>
@@ -17488,7 +17488,7 @@
         <v>96-141</v>
       </c>
       <c r="B276" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C276" t="str">
         <v/>
@@ -17550,7 +17550,7 @@
         <v>96-1539</v>
       </c>
       <c r="B277" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C277" t="str">
         <v/>
@@ -17612,7 +17612,7 @@
         <v>96-1540</v>
       </c>
       <c r="B278" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C278" t="str">
         <v/>
@@ -17674,7 +17674,7 @@
         <v>96-1542</v>
       </c>
       <c r="B279" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C279" t="str">
         <v/>
@@ -17736,7 +17736,7 @@
         <v>96-1287</v>
       </c>
       <c r="B280" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C280" t="str">
         <v/>
@@ -17798,7 +17798,7 @@
         <v>96-1287-A</v>
       </c>
       <c r="B281" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C281" t="str">
         <v/>
@@ -18108,7 +18108,7 @@
         <v>VII-14-INV-22K-415</v>
       </c>
       <c r="B286" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C286" t="str">
         <v>BANAIS, PANFILO &amp; ANGALOT, CHRISTIAN</v>
@@ -18604,7 +18604,7 @@
         <v>VII-14-INQ-24E-103</v>
       </c>
       <c r="B294" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C294" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18666,7 +18666,7 @@
         <v>VII-14-INQ-24E-104</v>
       </c>
       <c r="B295" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C295" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18852,7 +18852,7 @@
         <v>VII-14-INQ-24K-311</v>
       </c>
       <c r="B298" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C298" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18914,7 +18914,7 @@
         <v>VII-14-INQ-24K-312</v>
       </c>
       <c r="B299" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C299" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18976,7 +18976,7 @@
         <v>VII-14-INQ-19I-351</v>
       </c>
       <c r="B300" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C300" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -19038,7 +19038,7 @@
         <v>VII-14-INQ-19I-350</v>
       </c>
       <c r="B301" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C301" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -19100,7 +19100,7 @@
         <v>VII-14-INQ-19D-164</v>
       </c>
       <c r="B302" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C302" t="str">
         <v>TAGBILARAN CITY POLICE</v>
@@ -19162,7 +19162,7 @@
         <v>VII-14-INV-17J-0328</v>
       </c>
       <c r="B303" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C303" t="str">
         <v/>
@@ -19224,7 +19224,7 @@
         <v>VII-14-INV-17J-0358</v>
       </c>
       <c r="B304" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C304" t="str">
         <v/>
@@ -19286,7 +19286,7 @@
         <v>VII-14-INV-17J-0357</v>
       </c>
       <c r="B305" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C305" t="str">
         <v/>
@@ -19348,7 +19348,7 @@
         <v>INV-14-INV-17J-0303</v>
       </c>
       <c r="B306" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C306" t="str">
         <v>MAMAC, PATRICK SISTER Y.</v>
@@ -19410,7 +19410,7 @@
         <v>VII-14-INV-24I-289</v>
       </c>
       <c r="B307" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C307" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19472,7 +19472,7 @@
         <v>VII-14-INV-24I-290</v>
       </c>
       <c r="B308" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C308" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19534,7 +19534,7 @@
         <v>VII-14-INV-24I-291</v>
       </c>
       <c r="B309" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C309" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19596,7 +19596,7 @@
         <v>VII-14-INV-24I-292</v>
       </c>
       <c r="B310" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C310" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19658,7 +19658,7 @@
         <v>VII-14-INV-24I-293</v>
       </c>
       <c r="B311" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C311" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19720,7 +19720,7 @@
         <v>VII-14-INV-24I-294</v>
       </c>
       <c r="B312" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C312" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19782,7 +19782,7 @@
         <v>VII-14-INV-24I-295</v>
       </c>
       <c r="B313" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C313" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19844,7 +19844,7 @@
         <v>VII-14-INV-24I-296</v>
       </c>
       <c r="B314" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C314" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19906,7 +19906,7 @@
         <v>VII-14-INV-24I-297</v>
       </c>
       <c r="B315" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C315" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19968,7 +19968,7 @@
         <v>VII-14-INV-24I-298</v>
       </c>
       <c r="B316" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C316" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20030,7 +20030,7 @@
         <v>VII-14-INV-24I-299</v>
       </c>
       <c r="B317" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C317" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20092,7 +20092,7 @@
         <v>VII-14-INV-24I-300</v>
       </c>
       <c r="B318" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C318" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20154,7 +20154,7 @@
         <v>VII-14-INV-24I-301</v>
       </c>
       <c r="B319" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C319" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20216,7 +20216,7 @@
         <v>VII-14-INQ-19F-201 C</v>
       </c>
       <c r="B320" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C320" t="str">
         <v>TAGBILARAN CITY POLICE STATION</v>
@@ -20340,7 +20340,7 @@
         <v>VII-14-INQ-24J-258</v>
       </c>
       <c r="B322" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C322" t="str">
         <v>PNP- TAGBILARAN CITY</v>
@@ -20402,7 +20402,7 @@
         <v>96-3001-3003</v>
       </c>
       <c r="B323" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C323" t="str">
         <v/>
@@ -20712,7 +20712,7 @@
         <v>97-251-253</v>
       </c>
       <c r="B328" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C328" t="str">
         <v/>
@@ -20774,7 +20774,7 @@
         <v>97-254-256</v>
       </c>
       <c r="B329" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C329" t="str">
         <v/>
@@ -20836,7 +20836,7 @@
         <v>VII-14-INQ-20J-406</v>
       </c>
       <c r="B330" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C330" t="str">
         <v>BUQUIL, JONIEL</v>
@@ -20898,7 +20898,7 @@
         <v>94-219</v>
       </c>
       <c r="B331" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C331" t="str">
         <v/>
@@ -21580,7 +21580,7 @@
         <v>96-4512-4514</v>
       </c>
       <c r="B342" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C342" t="str">
         <v/>
@@ -21704,7 +21704,7 @@
         <v>VII-14-INQ-22F-116</v>
       </c>
       <c r="B344" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C344" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -21766,7 +21766,7 @@
         <v>VII-14-INQ-22F-116</v>
       </c>
       <c r="B345" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C345" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -21828,7 +21828,7 @@
         <v>VII-14-INQ-22F-118</v>
       </c>
       <c r="B346" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C346" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -21890,7 +21890,7 @@
         <v>VII-14-INQ-22F-118</v>
       </c>
       <c r="B347" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C347" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -22262,7 +22262,7 @@
         <v>92-433</v>
       </c>
       <c r="B353" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C353" t="str">
         <v/>
@@ -22324,7 +22324,7 @@
         <v>96-1345</v>
       </c>
       <c r="B354" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C354" t="str">
         <v/>
@@ -22386,7 +22386,7 @@
         <v>99-290</v>
       </c>
       <c r="B355" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C355" t="str">
         <v/>
@@ -22510,7 +22510,7 @@
         <v>VII-14-INQ-18l-174</v>
       </c>
       <c r="B357" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C357" t="str">
         <v>PIB-SOG Bohol</v>
@@ -22572,7 +22572,7 @@
         <v>VII-14-INQ-18l-177</v>
       </c>
       <c r="B358" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C358" t="str">
         <v>PIB-SOG Bohol</v>
@@ -22758,7 +22758,7 @@
         <v>VII-14-INV-20J-275</v>
       </c>
       <c r="B361" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C361" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -22820,7 +22820,7 @@
         <v>VII-14-INV-20J-276</v>
       </c>
       <c r="B362" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C362" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -22882,7 +22882,7 @@
         <v>VII-14-INV-20J-277</v>
       </c>
       <c r="B363" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C363" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -22944,7 +22944,7 @@
         <v>VII-14-INV-20J-278</v>
       </c>
       <c r="B364" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C364" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23006,7 +23006,7 @@
         <v>VII-14-INV-20J-279</v>
       </c>
       <c r="B365" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C365" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23068,7 +23068,7 @@
         <v>VII-14-INV-20J-280</v>
       </c>
       <c r="B366" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C366" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23130,7 +23130,7 @@
         <v>VII-14-INV-20J-281</v>
       </c>
       <c r="B367" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C367" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23192,7 +23192,7 @@
         <v>VII-14-INV-20J-283</v>
       </c>
       <c r="B368" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C368" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23254,7 +23254,7 @@
         <v>96-1607</v>
       </c>
       <c r="B369" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C369" t="str">
         <v/>
@@ -23316,7 +23316,7 @@
         <v>96-1607-A</v>
       </c>
       <c r="B370" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C370" t="str">
         <v/>
@@ -23378,7 +23378,7 @@
         <v>24J-240</v>
       </c>
       <c r="B371" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C371" t="str">
         <v>CITY PNP-TAGBILARAN CITY</v>
@@ -23440,7 +23440,7 @@
         <v>24J-241</v>
       </c>
       <c r="B372" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C372" t="str">
         <v>CITY PNP-TAGBILARAN CITY</v>
@@ -23626,7 +23626,7 @@
         <v>VII-14-INQ-21l-191</v>
       </c>
       <c r="B375" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C375" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -23688,7 +23688,7 @@
         <v>VII-14-INQ-21l-192</v>
       </c>
       <c r="B376" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C376" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -23750,7 +23750,7 @@
         <v>96-1820</v>
       </c>
       <c r="B377" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C377" t="str">
         <v/>
@@ -23812,7 +23812,7 @@
         <v>96-1821</v>
       </c>
       <c r="B378" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C378" t="str">
         <v/>
@@ -23874,7 +23874,7 @@
         <v>96-1822</v>
       </c>
       <c r="B379" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C379" t="str">
         <v/>
@@ -23936,7 +23936,7 @@
         <v>96-772</v>
       </c>
       <c r="B380" t="str">
-        <v>April 9, 2026</v>
+        <v>April 10, 2026</v>
       </c>
       <c r="C380" t="str">
         <v/>

--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -500,7 +500,7 @@
         <v>VII-14-INQ-20I-361</v>
       </c>
       <c r="B2" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>TAGBILARAN CITY PNP</v>
@@ -562,7 +562,7 @@
         <v>VII-14-INQ-20I-360</v>
       </c>
       <c r="B3" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C3" t="str">
         <v>TAGBILARAN CITY PNP</v>
@@ -934,7 +934,7 @@
         <v>2005-19</v>
       </c>
       <c r="B9" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -996,7 +996,7 @@
         <v>2006-45</v>
       </c>
       <c r="B10" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -1120,7 +1120,7 @@
         <v>VII-14-INQ-20A-04</v>
       </c>
       <c r="B12" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C12" t="str">
         <v>SALARDA, MYRA A.</v>
@@ -1306,7 +1306,7 @@
         <v>96-3427-3429</v>
       </c>
       <c r="B15" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1430,7 +1430,7 @@
         <v>3434</v>
       </c>
       <c r="B17" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -2050,7 +2050,7 @@
         <v>VII-14-INV-22D-071</v>
       </c>
       <c r="B27" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C27" t="str">
         <v>CIDG-BOHOL</v>
@@ -2112,7 +2112,7 @@
         <v>VII-14-INV-22D-070</v>
       </c>
       <c r="B28" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C28" t="str">
         <v>CIDG-BOHOL</v>
@@ -2174,7 +2174,7 @@
         <v>VII-14-INQ-17A-027</v>
       </c>
       <c r="B29" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -2360,7 +2360,7 @@
         <v>24H-260</v>
       </c>
       <c r="B32" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C32" t="str">
         <v>CADAYDAY, NEMESIA</v>
@@ -2422,7 +2422,7 @@
         <v>24H-260</v>
       </c>
       <c r="B33" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C33" t="str">
         <v>CADAYDAY,NEMESIA</v>
@@ -2484,7 +2484,7 @@
         <v>24H-261</v>
       </c>
       <c r="B34" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C34" t="str">
         <v>ALIVIADO, KHY</v>
@@ -2546,7 +2546,7 @@
         <v>24H-261</v>
       </c>
       <c r="B35" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>CADAYDAY,NEMESIA</v>
@@ -2608,7 +2608,7 @@
         <v>96-228</v>
       </c>
       <c r="B36" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -2670,7 +2670,7 @@
         <v>96-229</v>
       </c>
       <c r="B37" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -2732,7 +2732,7 @@
         <v>96-230</v>
       </c>
       <c r="B38" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -2794,7 +2794,7 @@
         <v>VII-14-INV-2OL-366</v>
       </c>
       <c r="B39" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C39" t="str">
         <v>PNP - TAGBILARAN CITY</v>
@@ -2980,7 +2980,7 @@
         <v>96-306</v>
       </c>
       <c r="B42" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -3042,7 +3042,7 @@
         <v>96-307</v>
       </c>
       <c r="B43" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -3104,7 +3104,7 @@
         <v>96-308</v>
       </c>
       <c r="B44" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -3352,7 +3352,7 @@
         <v>VII-14-INQ-221-197</v>
       </c>
       <c r="B48" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C48" t="str">
         <v>PDEA-BOHOL</v>
@@ -3476,7 +3476,7 @@
         <v>VII-14-INQ-221-196</v>
       </c>
       <c r="B50" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C50" t="str">
         <v>PDEA-BOHOL</v>
@@ -3538,7 +3538,7 @@
         <v>3145</v>
       </c>
       <c r="B51" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -3600,7 +3600,7 @@
         <v>3144</v>
       </c>
       <c r="B52" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -3786,7 +3786,7 @@
         <v>VII-14-INV-175-0325</v>
       </c>
       <c r="B55" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -3972,7 +3972,7 @@
         <v>VII-14-INV-20A-27</v>
       </c>
       <c r="B58" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C58" t="str">
         <v>CIDG-BOHOL</v>
@@ -4034,7 +4034,7 @@
         <v>VII-14-INV-20A-26</v>
       </c>
       <c r="B59" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C59" t="str">
         <v>CIDG-BOHOL</v>
@@ -4158,7 +4158,7 @@
         <v>2000-129</v>
       </c>
       <c r="B61" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -4220,7 +4220,7 @@
         <v>2000-130</v>
       </c>
       <c r="B62" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -4282,7 +4282,7 @@
         <v>2000-131</v>
       </c>
       <c r="B63" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -4344,7 +4344,7 @@
         <v>2000-132</v>
       </c>
       <c r="B64" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -4406,7 +4406,7 @@
         <v>2000-133</v>
       </c>
       <c r="B65" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -4468,7 +4468,7 @@
         <v>2000-134</v>
       </c>
       <c r="B66" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
         <v>2000-135</v>
       </c>
       <c r="B67" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -4592,7 +4592,7 @@
         <v>2000-136</v>
       </c>
       <c r="B68" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -4654,7 +4654,7 @@
         <v>2000-137</v>
       </c>
       <c r="B69" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -4716,7 +4716,7 @@
         <v>2000-138</v>
       </c>
       <c r="B70" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -4778,7 +4778,7 @@
         <v>2000-139</v>
       </c>
       <c r="B71" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -4840,7 +4840,7 @@
         <v>VII-14-INQ-24K-285</v>
       </c>
       <c r="B72" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C72" t="str">
         <v>NBI-CEBU OFFICE -MANDAUE CITY</v>
@@ -4902,7 +4902,7 @@
         <v>99-317</v>
       </c>
       <c r="B73" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -4964,7 +4964,7 @@
         <v>VII-14-INV-20H-207</v>
       </c>
       <c r="B74" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C74" t="str">
         <v>BINAMIRA, GARRY NOEL E.</v>
@@ -5026,7 +5026,7 @@
         <v>24J-242</v>
       </c>
       <c r="B75" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C75" t="str">
         <v>PDEA-BOHOL</v>
@@ -5088,7 +5088,7 @@
         <v>24J-243</v>
       </c>
       <c r="B76" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C76" t="str">
         <v>PDEA-BOHOL</v>
@@ -5150,7 +5150,7 @@
         <v>24J-244</v>
       </c>
       <c r="B77" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C77" t="str">
         <v>PDEA-BOHOL</v>
@@ -5212,7 +5212,7 @@
         <v>24J-245</v>
       </c>
       <c r="B78" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C78" t="str">
         <v>PDEA-BOHOL</v>
@@ -5336,7 +5336,7 @@
         <v>89-289 89-289-A 89-289-B 89-289-C 89-289-D</v>
       </c>
       <c r="B80" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C80" t="str">
         <v/>
@@ -5398,7 +5398,7 @@
         <v>VII-14-INV-21A-079</v>
       </c>
       <c r="B81" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C81" t="str">
         <v>STARLITE MARINE INDUSTRIAL SERVICES CORP.</v>
@@ -5460,7 +5460,7 @@
         <v>24K-300</v>
       </c>
       <c r="B82" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C82" t="str">
         <v>PNP - TAGBILARAN CITY</v>
@@ -6452,7 +6452,7 @@
         <v>96-1464</v>
       </c>
       <c r="B98" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -6700,7 +6700,7 @@
         <v>92-195</v>
       </c>
       <c r="B102" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -6762,7 +6762,7 @@
         <v>VII-14-INV-24B-55</v>
       </c>
       <c r="B103" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C103" t="str">
         <v>BAJA, NOEL B.</v>
@@ -6824,7 +6824,7 @@
         <v>86-226</v>
       </c>
       <c r="B104" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -6886,7 +6886,7 @@
         <v>97-3828</v>
       </c>
       <c r="B105" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -6948,7 +6948,7 @@
         <v>97-3829</v>
       </c>
       <c r="B106" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C106" t="str">
         <v/>
@@ -7010,7 +7010,7 @@
         <v>97-3830</v>
       </c>
       <c r="B107" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C107" t="str">
         <v/>
@@ -7072,7 +7072,7 @@
         <v>97-3831</v>
       </c>
       <c r="B108" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C108" t="str">
         <v/>
@@ -7754,7 +7754,7 @@
         <v>3510</v>
       </c>
       <c r="B119" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C119" t="str">
         <v/>
@@ -7816,7 +7816,7 @@
         <v>96-2673</v>
       </c>
       <c r="B120" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C120" t="str">
         <v/>
@@ -7878,7 +7878,7 @@
         <v>96-2674</v>
       </c>
       <c r="B121" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C121" t="str">
         <v/>
@@ -7940,7 +7940,7 @@
         <v>96-2675</v>
       </c>
       <c r="B122" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C122" t="str">
         <v/>
@@ -8002,7 +8002,7 @@
         <v>97-3037</v>
       </c>
       <c r="B123" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C123" t="str">
         <v/>
@@ -8064,7 +8064,7 @@
         <v>97-3038</v>
       </c>
       <c r="B124" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C124" t="str">
         <v/>
@@ -8126,7 +8126,7 @@
         <v>97-3039</v>
       </c>
       <c r="B125" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C125" t="str">
         <v/>
@@ -8188,7 +8188,7 @@
         <v>97-1336</v>
       </c>
       <c r="B126" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -8250,7 +8250,7 @@
         <v>97-1336</v>
       </c>
       <c r="B127" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C127" t="str">
         <v/>
@@ -8374,7 +8374,7 @@
         <v>97-1339</v>
       </c>
       <c r="B129" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C129" t="str">
         <v/>
@@ -8436,7 +8436,7 @@
         <v>97-1340</v>
       </c>
       <c r="B130" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C130" t="str">
         <v/>
@@ -8498,7 +8498,7 @@
         <v>97-1341</v>
       </c>
       <c r="B131" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C131" t="str">
         <v/>
@@ -8560,7 +8560,7 @@
         <v>96-2554</v>
       </c>
       <c r="B132" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C132" t="str">
         <v/>
@@ -8622,7 +8622,7 @@
         <v>96-2555</v>
       </c>
       <c r="B133" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C133" t="str">
         <v/>
@@ -8684,7 +8684,7 @@
         <v>96-2556</v>
       </c>
       <c r="B134" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C134" t="str">
         <v/>
@@ -8746,7 +8746,7 @@
         <v>96-2557</v>
       </c>
       <c r="B135" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -8808,7 +8808,7 @@
         <v>96-2558</v>
       </c>
       <c r="B136" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C136" t="str">
         <v/>
@@ -8870,7 +8870,7 @@
         <v>24l-222</v>
       </c>
       <c r="B137" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C137" t="str">
         <v>TAGBILARAN CITY - PNP</v>
@@ -8932,7 +8932,7 @@
         <v>24l-223</v>
       </c>
       <c r="B138" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C138" t="str">
         <v>TAGBILARAN CITY - PNP</v>
@@ -9366,7 +9366,7 @@
         <v>97-397</v>
       </c>
       <c r="B145" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C145" t="str">
         <v/>
@@ -9428,7 +9428,7 @@
         <v>2005-537</v>
       </c>
       <c r="B146" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C146" t="str">
         <v/>
@@ -9738,7 +9738,7 @@
         <v>2002-999</v>
       </c>
       <c r="B151" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C151" t="str">
         <v/>
@@ -9800,7 +9800,7 @@
         <v>2002-1000</v>
       </c>
       <c r="B152" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C152" t="str">
         <v/>
@@ -9862,7 +9862,7 @@
         <v>2002-1001</v>
       </c>
       <c r="B153" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C153" t="str">
         <v/>
@@ -9924,7 +9924,7 @@
         <v>2002-1002</v>
       </c>
       <c r="B154" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C154" t="str">
         <v/>
@@ -9986,7 +9986,7 @@
         <v>3961</v>
       </c>
       <c r="B155" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C155" t="str">
         <v/>
@@ -10048,7 +10048,7 @@
         <v>VII-14-INQ-23B-061</v>
       </c>
       <c r="B156" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C156" t="str">
         <v>PIU-BOHOL PPO</v>
@@ -10110,7 +10110,7 @@
         <v>VII-14-INQ-23B-061</v>
       </c>
       <c r="B157" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C157" t="str">
         <v>PIU BOHOL PPO</v>
@@ -10172,7 +10172,7 @@
         <v>VII-14-INQ-23B-062</v>
       </c>
       <c r="B158" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C158" t="str">
         <v>PIU-BOHOL PPO</v>
@@ -10234,7 +10234,7 @@
         <v>VII-14-INQ-23B-062</v>
       </c>
       <c r="B159" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C159" t="str">
         <v>PIU BOHOL PPO</v>
@@ -10420,7 +10420,7 @@
         <v>93-463</v>
       </c>
       <c r="B162" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C162" t="str">
         <v/>
@@ -10482,7 +10482,7 @@
         <v>93-464</v>
       </c>
       <c r="B163" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C163" t="str">
         <v/>
@@ -10544,7 +10544,7 @@
         <v>96-1680</v>
       </c>
       <c r="B164" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C164" t="str">
         <v/>
@@ -10606,7 +10606,7 @@
         <v>96-1681</v>
       </c>
       <c r="B165" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C165" t="str">
         <v/>
@@ -10668,7 +10668,7 @@
         <v>96-1682</v>
       </c>
       <c r="B166" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C166" t="str">
         <v/>
@@ -10730,7 +10730,7 @@
         <v>96-1697</v>
       </c>
       <c r="B167" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C167" t="str">
         <v/>
@@ -10792,7 +10792,7 @@
         <v>96-1698</v>
       </c>
       <c r="B168" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C168" t="str">
         <v/>
@@ -10854,7 +10854,7 @@
         <v>96-1699</v>
       </c>
       <c r="B169" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C169" t="str">
         <v/>
@@ -10978,7 +10978,7 @@
         <v>VII-14-INQ-24J-257</v>
       </c>
       <c r="B171" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C171" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -11040,7 +11040,7 @@
         <v>VII-14-INQ-24J-257</v>
       </c>
       <c r="B172" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C172" t="str">
         <v>PNP- TAGBILARAN CITY</v>
@@ -11102,7 +11102,7 @@
         <v>96-831</v>
       </c>
       <c r="B173" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C173" t="str">
         <v/>
@@ -11164,7 +11164,7 @@
         <v>VII-14-INV-24J-316</v>
       </c>
       <c r="B174" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C174" t="str">
         <v>ROSALEJOS, ALFONSO LIGO</v>
@@ -11226,7 +11226,7 @@
         <v>VII-14-INV-24J-316 b</v>
       </c>
       <c r="B175" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C175" t="str">
         <v>ROSALEJOS, ALFONSO LIGO</v>
@@ -11288,7 +11288,7 @@
         <v>97-3034</v>
       </c>
       <c r="B176" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C176" t="str">
         <v/>
@@ -11350,7 +11350,7 @@
         <v>97-3035</v>
       </c>
       <c r="B177" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C177" t="str">
         <v/>
@@ -11412,7 +11412,7 @@
         <v>97-3036</v>
       </c>
       <c r="B178" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C178" t="str">
         <v/>
@@ -11474,7 +11474,7 @@
         <v>96-1724</v>
       </c>
       <c r="B179" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C179" t="str">
         <v/>
@@ -11536,7 +11536,7 @@
         <v>96-1725</v>
       </c>
       <c r="B180" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C180" t="str">
         <v/>
@@ -11598,7 +11598,7 @@
         <v>96-1726</v>
       </c>
       <c r="B181" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C181" t="str">
         <v/>
@@ -11660,7 +11660,7 @@
         <v>96-1574</v>
       </c>
       <c r="B182" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C182" t="str">
         <v/>
@@ -11722,7 +11722,7 @@
         <v>96-1575</v>
       </c>
       <c r="B183" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C183" t="str">
         <v/>
@@ -11784,7 +11784,7 @@
         <v>96-1576</v>
       </c>
       <c r="B184" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C184" t="str">
         <v/>
@@ -11846,7 +11846,7 @@
         <v>98-004</v>
       </c>
       <c r="B185" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C185" t="str">
         <v/>
@@ -11908,7 +11908,7 @@
         <v>98-005</v>
       </c>
       <c r="B186" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C186" t="str">
         <v/>
@@ -12280,7 +12280,7 @@
         <v>VII-14-INQ-20K-408</v>
       </c>
       <c r="B192" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C192" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -12342,7 +12342,7 @@
         <v>VII-14-INQ-20K-408</v>
       </c>
       <c r="B193" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C193" t="str">
         <v>PNP TAGBILARAN CITY</v>
@@ -12466,7 +12466,7 @@
         <v>VII-14-INQ-19E-197</v>
       </c>
       <c r="B195" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C195" t="str">
         <v>TAGBILARAN CITY POLICE</v>
@@ -13396,7 +13396,7 @@
         <v>VII-14-INV-20E-99</v>
       </c>
       <c r="B210" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C210" t="str">
         <v>FERNANDEZ, EULALIA A.</v>
@@ -13458,7 +13458,7 @@
         <v>VII-14-INV-18D-0132</v>
       </c>
       <c r="B211" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C211" t="str">
         <v>FCB, REP BY: GALAB, ANTHONY B.</v>
@@ -13520,7 +13520,7 @@
         <v>VII-14-INV-17H-0230</v>
       </c>
       <c r="B212" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C212" t="str">
         <v>A-1-BY TAGASLING, JOSEPHINE B.</v>
@@ -13582,7 +13582,7 @@
         <v>VII-14-INV-17H-0230 -A</v>
       </c>
       <c r="B213" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C213" t="str">
         <v>A-1-BY TAGASLING, JOSEPHINE B.</v>
@@ -13644,7 +13644,7 @@
         <v>VII-14-INV-18K-445</v>
       </c>
       <c r="B214" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C214" t="str">
         <v>GALLA, JOHN S.</v>
@@ -13706,7 +13706,7 @@
         <v>VII-14-INV-20E-100</v>
       </c>
       <c r="B215" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C215" t="str">
         <v>FERNANDEZ, EULALIA A.</v>
@@ -13768,7 +13768,7 @@
         <v>VII-14-INV-21B-30</v>
       </c>
       <c r="B216" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C216" t="str">
         <v>CIDG-BOHOL</v>
@@ -13830,7 +13830,7 @@
         <v>VII-14-INV-21B-31</v>
       </c>
       <c r="B217" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C217" t="str">
         <v>CIDG-BOHOL</v>
@@ -13892,7 +13892,7 @@
         <v>24E-175</v>
       </c>
       <c r="B218" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C218" t="str">
         <v>VICTORIANO B. TIROL III AND WILL TYRON B. TIROL</v>
@@ -13954,7 +13954,7 @@
         <v>24E-176</v>
       </c>
       <c r="B219" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C219" t="str">
         <v>VICTORIANO B. TIROL III AND WILL TYRON B. TIROL</v>
@@ -14016,7 +14016,7 @@
         <v>97-1371</v>
       </c>
       <c r="B220" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C220" t="str">
         <v/>
@@ -14078,7 +14078,7 @@
         <v>VII-14-INQ-191-360</v>
       </c>
       <c r="B221" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C221" t="str">
         <v>PNP - TAGBILARAN CITY</v>
@@ -14140,7 +14140,7 @@
         <v>VII-14-INV-22B-037</v>
       </c>
       <c r="B222" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C222" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14202,7 +14202,7 @@
         <v>VII-14-INV-22B-038</v>
       </c>
       <c r="B223" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C223" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14264,7 +14264,7 @@
         <v>VII-14-INV-22B-039</v>
       </c>
       <c r="B224" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C224" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14326,7 +14326,7 @@
         <v>VII-14-INV-22B-040</v>
       </c>
       <c r="B225" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C225" t="str">
         <v>NICOLE OPENDO y GALES</v>
@@ -14388,7 +14388,7 @@
         <v>3636</v>
       </c>
       <c r="B226" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C226" t="str">
         <v/>
@@ -14450,7 +14450,7 @@
         <v>3341</v>
       </c>
       <c r="B227" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C227" t="str">
         <v/>
@@ -14512,7 +14512,7 @@
         <v>VII-14-INQ-22G-131</v>
       </c>
       <c r="B228" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C228" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -14636,7 +14636,7 @@
         <v>VII-14-INV-22L-453</v>
       </c>
       <c r="B230" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C230" t="str">
         <v>TAMPOS, MARIA IVY R.</v>
@@ -14822,7 +14822,7 @@
         <v>3430</v>
       </c>
       <c r="B233" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C233" t="str">
         <v/>
@@ -14884,7 +14884,7 @@
         <v>98-1063</v>
       </c>
       <c r="B234" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C234" t="str">
         <v/>
@@ -14946,7 +14946,7 @@
         <v>98-1063-A</v>
       </c>
       <c r="B235" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C235" t="str">
         <v/>
@@ -15008,7 +15008,7 @@
         <v>97-360</v>
       </c>
       <c r="B236" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C236" t="str">
         <v/>
@@ -15070,7 +15070,7 @@
         <v>97-361</v>
       </c>
       <c r="B237" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C237" t="str">
         <v/>
@@ -15132,7 +15132,7 @@
         <v>97-362</v>
       </c>
       <c r="B238" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C238" t="str">
         <v/>
@@ -15194,7 +15194,7 @@
         <v>3633</v>
       </c>
       <c r="B239" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C239" t="str">
         <v/>
@@ -15256,7 +15256,7 @@
         <v>362</v>
       </c>
       <c r="B240" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C240" t="str">
         <v/>
@@ -15380,7 +15380,7 @@
         <v>VII-14-INQ-19B-005</v>
       </c>
       <c r="B242" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C242" t="str">
         <v>NBI, TAGBILARAN CITY</v>
@@ -15442,7 +15442,7 @@
         <v>97-1337</v>
       </c>
       <c r="B243" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C243" t="str">
         <v/>
@@ -15566,7 +15566,7 @@
         <v>VII-14-INV-24I-286</v>
       </c>
       <c r="B245" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C245" t="str">
         <v>XU, FLORIE MUNEZ</v>
@@ -15628,7 +15628,7 @@
         <v>VII-14-INV-24I-287</v>
       </c>
       <c r="B246" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C246" t="str">
         <v>XU, FLORIE MUNEZ</v>
@@ -15690,7 +15690,7 @@
         <v>VII-14-INV-24I-288</v>
       </c>
       <c r="B247" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C247" t="str">
         <v>XU, FLORIE MUNEZ</v>
@@ -15814,7 +15814,7 @@
         <v>VII-14-INV 24B-45</v>
       </c>
       <c r="B249" t="str">
-        <v>February 13, 2024</v>
+        <v/>
       </c>
       <c r="C249" t="str">
         <v>TARIAO, ROSALINDA R.</v>
@@ -15876,7 +15876,7 @@
         <v>VII-14-INV 24B-45</v>
       </c>
       <c r="B250" t="str">
-        <v>February 13, 2024</v>
+        <v/>
       </c>
       <c r="C250" t="str">
         <v>TARIAO, ROSALINDA R.</v>
@@ -15938,7 +15938,7 @@
         <v>95-999</v>
       </c>
       <c r="B251" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C251" t="str">
         <v/>
@@ -16000,7 +16000,7 @@
         <v>24l-224</v>
       </c>
       <c r="B252" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C252" t="str">
         <v>LAIZA LOPEZ y BAUTISTA</v>
@@ -16062,7 +16062,7 @@
         <v>VII-14-INV-20J-284</v>
       </c>
       <c r="B253" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C253" t="str">
         <v>SSS-TAGBILARAN  CITY</v>
@@ -16124,7 +16124,7 @@
         <v>VII-14-INQ-19K-456</v>
       </c>
       <c r="B254" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C254" t="str">
         <v>BPPO, PIB, TAGBILARAN CITY</v>
@@ -16248,7 +16248,7 @@
         <v>VII-14-INV-22C-113</v>
       </c>
       <c r="B256" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C256" t="str">
         <v>ALBELDA, ANALOU S.</v>
@@ -16310,7 +16310,7 @@
         <v>VII-14-INQ-19L-476</v>
       </c>
       <c r="B257" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C257" t="str">
         <v>TAGB. CITY PNP</v>
@@ -16372,7 +16372,7 @@
         <v>VII-14-INQ-19L-336</v>
       </c>
       <c r="B258" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C258" t="str">
         <v>PNP, BOHOL</v>
@@ -16434,7 +16434,7 @@
         <v>VII-14-INQ-19I-336</v>
       </c>
       <c r="B259" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C259" t="str">
         <v>PNP, BOHOL</v>
@@ -16496,7 +16496,7 @@
         <v>VII-14-INQ-20K-409</v>
       </c>
       <c r="B260" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C260" t="str">
         <v>PNP TAGBILARAN CITY</v>
@@ -16558,7 +16558,7 @@
         <v>VII-14-INQ-20B-57</v>
       </c>
       <c r="B261" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C261" t="str">
         <v>PNP, BOHOL</v>
@@ -16620,7 +16620,7 @@
         <v>97-2372</v>
       </c>
       <c r="B262" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C262" t="str">
         <v/>
@@ -16682,7 +16682,7 @@
         <v>97-2373</v>
       </c>
       <c r="B263" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C263" t="str">
         <v/>
@@ -16744,7 +16744,7 @@
         <v>97-2374</v>
       </c>
       <c r="B264" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C264" t="str">
         <v/>
@@ -16868,7 +16868,7 @@
         <v>97-1622-A</v>
       </c>
       <c r="B266" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C266" t="str">
         <v/>
@@ -16930,7 +16930,7 @@
         <v>VII-14-INV-22H-328</v>
       </c>
       <c r="B267" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C267" t="str">
         <v>PDEA-BOHOL</v>
@@ -17054,7 +17054,7 @@
         <v>VII-14-INV-18K-252</v>
       </c>
       <c r="B269" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C269" t="str">
         <v>NBI, BOHOL                                            REP BY: RENNAN AUGUSTUS OLIVA</v>
@@ -17116,7 +17116,7 @@
         <v>VII-14-INV-18K-253</v>
       </c>
       <c r="B270" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C270" t="str">
         <v>NBI, BOHOL                                            REP BY: RENNAN AUGUSTUS OLIVA</v>
@@ -17240,7 +17240,7 @@
         <v>97-420</v>
       </c>
       <c r="B272" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C272" t="str">
         <v/>
@@ -17302,7 +17302,7 @@
         <v>97-421</v>
       </c>
       <c r="B273" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C273" t="str">
         <v/>
@@ -17364,7 +17364,7 @@
         <v>96-4164</v>
       </c>
       <c r="B274" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C274" t="str">
         <v/>
@@ -17426,7 +17426,7 @@
         <v>96-4165</v>
       </c>
       <c r="B275" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C275" t="str">
         <v/>
@@ -17488,7 +17488,7 @@
         <v>96-141</v>
       </c>
       <c r="B276" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C276" t="str">
         <v/>
@@ -17550,7 +17550,7 @@
         <v>96-1539</v>
       </c>
       <c r="B277" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C277" t="str">
         <v/>
@@ -17612,7 +17612,7 @@
         <v>96-1540</v>
       </c>
       <c r="B278" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C278" t="str">
         <v/>
@@ -17674,7 +17674,7 @@
         <v>96-1542</v>
       </c>
       <c r="B279" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C279" t="str">
         <v/>
@@ -17736,7 +17736,7 @@
         <v>96-1287</v>
       </c>
       <c r="B280" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C280" t="str">
         <v/>
@@ -17798,7 +17798,7 @@
         <v>96-1287-A</v>
       </c>
       <c r="B281" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C281" t="str">
         <v/>
@@ -18108,7 +18108,7 @@
         <v>VII-14-INV-22K-415</v>
       </c>
       <c r="B286" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C286" t="str">
         <v>BANAIS, PANFILO &amp; ANGALOT, CHRISTIAN</v>
@@ -18604,7 +18604,7 @@
         <v>VII-14-INQ-24E-103</v>
       </c>
       <c r="B294" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C294" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18666,7 +18666,7 @@
         <v>VII-14-INQ-24E-104</v>
       </c>
       <c r="B295" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C295" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18852,7 +18852,7 @@
         <v>VII-14-INQ-24K-311</v>
       </c>
       <c r="B298" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C298" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18914,7 +18914,7 @@
         <v>VII-14-INQ-24K-312</v>
       </c>
       <c r="B299" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C299" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -18976,7 +18976,7 @@
         <v>VII-14-INQ-19I-351</v>
       </c>
       <c r="B300" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C300" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -19038,7 +19038,7 @@
         <v>VII-14-INQ-19I-350</v>
       </c>
       <c r="B301" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C301" t="str">
         <v>PNP-TABILARAN CITY</v>
@@ -19100,7 +19100,7 @@
         <v>VII-14-INQ-19D-164</v>
       </c>
       <c r="B302" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C302" t="str">
         <v>TAGBILARAN CITY POLICE</v>
@@ -19162,7 +19162,7 @@
         <v>VII-14-INV-17J-0328</v>
       </c>
       <c r="B303" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C303" t="str">
         <v/>
@@ -19224,7 +19224,7 @@
         <v>VII-14-INV-17J-0358</v>
       </c>
       <c r="B304" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C304" t="str">
         <v/>
@@ -19286,7 +19286,7 @@
         <v>VII-14-INV-17J-0357</v>
       </c>
       <c r="B305" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C305" t="str">
         <v/>
@@ -19348,7 +19348,7 @@
         <v>INV-14-INV-17J-0303</v>
       </c>
       <c r="B306" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C306" t="str">
         <v>MAMAC, PATRICK SISTER Y.</v>
@@ -19410,7 +19410,7 @@
         <v>VII-14-INV-24I-289</v>
       </c>
       <c r="B307" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C307" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19472,7 +19472,7 @@
         <v>VII-14-INV-24I-290</v>
       </c>
       <c r="B308" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C308" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19534,7 +19534,7 @@
         <v>VII-14-INV-24I-291</v>
       </c>
       <c r="B309" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C309" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19596,7 +19596,7 @@
         <v>VII-14-INV-24I-292</v>
       </c>
       <c r="B310" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C310" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19658,7 +19658,7 @@
         <v>VII-14-INV-24I-293</v>
       </c>
       <c r="B311" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C311" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19720,7 +19720,7 @@
         <v>VII-14-INV-24I-294</v>
       </c>
       <c r="B312" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C312" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19782,7 +19782,7 @@
         <v>VII-14-INV-24I-295</v>
       </c>
       <c r="B313" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C313" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19844,7 +19844,7 @@
         <v>VII-14-INV-24I-296</v>
       </c>
       <c r="B314" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C314" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19906,7 +19906,7 @@
         <v>VII-14-INV-24I-297</v>
       </c>
       <c r="B315" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C315" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -19968,7 +19968,7 @@
         <v>VII-14-INV-24I-298</v>
       </c>
       <c r="B316" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C316" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20030,7 +20030,7 @@
         <v>VII-14-INV-24I-299</v>
       </c>
       <c r="B317" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C317" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20092,7 +20092,7 @@
         <v>VII-14-INV-24I-300</v>
       </c>
       <c r="B318" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C318" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20154,7 +20154,7 @@
         <v>VII-14-INV-24I-301</v>
       </c>
       <c r="B319" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C319" t="str">
         <v>VERGABERA, NORBERTO JR.</v>
@@ -20216,7 +20216,7 @@
         <v>VII-14-INQ-19F-201 C</v>
       </c>
       <c r="B320" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C320" t="str">
         <v>TAGBILARAN CITY POLICE STATION</v>
@@ -20340,7 +20340,7 @@
         <v>VII-14-INQ-24J-258</v>
       </c>
       <c r="B322" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C322" t="str">
         <v>PNP- TAGBILARAN CITY</v>
@@ -20402,7 +20402,7 @@
         <v>96-3001-3003</v>
       </c>
       <c r="B323" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C323" t="str">
         <v/>
@@ -20712,7 +20712,7 @@
         <v>97-251-253</v>
       </c>
       <c r="B328" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C328" t="str">
         <v/>
@@ -20774,7 +20774,7 @@
         <v>97-254-256</v>
       </c>
       <c r="B329" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C329" t="str">
         <v/>
@@ -20836,7 +20836,7 @@
         <v>VII-14-INQ-20J-406</v>
       </c>
       <c r="B330" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C330" t="str">
         <v>BUQUIL, JONIEL</v>
@@ -20898,7 +20898,7 @@
         <v>94-219</v>
       </c>
       <c r="B331" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C331" t="str">
         <v/>
@@ -21580,7 +21580,7 @@
         <v>96-4512-4514</v>
       </c>
       <c r="B342" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C342" t="str">
         <v/>
@@ -21704,7 +21704,7 @@
         <v>VII-14-INQ-22F-116</v>
       </c>
       <c r="B344" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C344" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -21766,7 +21766,7 @@
         <v>VII-14-INQ-22F-116</v>
       </c>
       <c r="B345" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C345" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -21828,7 +21828,7 @@
         <v>VII-14-INQ-22F-118</v>
       </c>
       <c r="B346" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C346" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -21890,7 +21890,7 @@
         <v>VII-14-INQ-22F-118</v>
       </c>
       <c r="B347" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C347" t="str">
         <v>BPPO, PIU BOHOL</v>
@@ -22262,7 +22262,7 @@
         <v>92-433</v>
       </c>
       <c r="B353" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C353" t="str">
         <v/>
@@ -22324,7 +22324,7 @@
         <v>96-1345</v>
       </c>
       <c r="B354" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C354" t="str">
         <v/>
@@ -22386,7 +22386,7 @@
         <v>99-290</v>
       </c>
       <c r="B355" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C355" t="str">
         <v/>
@@ -22510,7 +22510,7 @@
         <v>VII-14-INQ-18l-174</v>
       </c>
       <c r="B357" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C357" t="str">
         <v>PIB-SOG Bohol</v>
@@ -22572,7 +22572,7 @@
         <v>VII-14-INQ-18l-177</v>
       </c>
       <c r="B358" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C358" t="str">
         <v>PIB-SOG Bohol</v>
@@ -22758,7 +22758,7 @@
         <v>VII-14-INV-20J-275</v>
       </c>
       <c r="B361" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C361" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -22820,7 +22820,7 @@
         <v>VII-14-INV-20J-276</v>
       </c>
       <c r="B362" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C362" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -22882,7 +22882,7 @@
         <v>VII-14-INV-20J-277</v>
       </c>
       <c r="B363" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C363" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -22944,7 +22944,7 @@
         <v>VII-14-INV-20J-278</v>
       </c>
       <c r="B364" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C364" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23006,7 +23006,7 @@
         <v>VII-14-INV-20J-279</v>
       </c>
       <c r="B365" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C365" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23068,7 +23068,7 @@
         <v>VII-14-INV-20J-280</v>
       </c>
       <c r="B366" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C366" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23130,7 +23130,7 @@
         <v>VII-14-INV-20J-281</v>
       </c>
       <c r="B367" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C367" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23192,7 +23192,7 @@
         <v>VII-14-INV-20J-283</v>
       </c>
       <c r="B368" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C368" t="str">
         <v>PATTI MAE REGINE L. CLERIGO</v>
@@ -23254,7 +23254,7 @@
         <v>96-1607</v>
       </c>
       <c r="B369" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C369" t="str">
         <v/>
@@ -23316,7 +23316,7 @@
         <v>96-1607-A</v>
       </c>
       <c r="B370" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C370" t="str">
         <v/>
@@ -23378,7 +23378,7 @@
         <v>24J-240</v>
       </c>
       <c r="B371" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C371" t="str">
         <v>CITY PNP-TAGBILARAN CITY</v>
@@ -23440,7 +23440,7 @@
         <v>24J-241</v>
       </c>
       <c r="B372" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C372" t="str">
         <v>CITY PNP-TAGBILARAN CITY</v>
@@ -23626,7 +23626,7 @@
         <v>VII-14-INQ-21l-191</v>
       </c>
       <c r="B375" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C375" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -23688,7 +23688,7 @@
         <v>VII-14-INQ-21l-192</v>
       </c>
       <c r="B376" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C376" t="str">
         <v>PNP-TAGBILARAN CITY</v>
@@ -23750,7 +23750,7 @@
         <v>96-1820</v>
       </c>
       <c r="B377" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C377" t="str">
         <v/>
@@ -23812,7 +23812,7 @@
         <v>96-1821</v>
       </c>
       <c r="B378" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C378" t="str">
         <v/>
@@ -23874,7 +23874,7 @@
         <v>96-1822</v>
       </c>
       <c r="B379" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C379" t="str">
         <v/>
@@ -23936,7 +23936,7 @@
         <v>96-772</v>
       </c>
       <c r="B380" t="str">
-        <v>April 10, 2026</v>
+        <v/>
       </c>
       <c r="C380" t="str">
         <v/>

--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T381</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -35,17 +35,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="10">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="m/d/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-m"/>
-    <numFmt numFmtId="168" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="169" formatCode="mm/yyyy"/>
-    <numFmt numFmtId="170" formatCode="mm\-dd\-yyyy"/>
-    <numFmt numFmtId="171" formatCode="mm/dd"/>
-    <numFmt numFmtId="172" formatCode="m/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -409,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T380"/>
+  <dimension ref="A1:T381"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -23993,10 +23984,72 @@
         <v>CUTAMORA, FLAVIA_0001.pdf</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Test3</v>
+      </c>
+      <c r="B381" t="str">
+        <v>April 22, 2026</v>
+      </c>
+      <c r="C381" t="str">
+        <v>s</v>
+      </c>
+      <c r="D381" t="str">
+        <v>sdf</v>
+      </c>
+      <c r="E381" t="str">
+        <v>sdfs</v>
+      </c>
+      <c r="F381" t="str">
+        <v>dfsdf</v>
+      </c>
+      <c r="G381" t="str">
+        <v/>
+      </c>
+      <c r="H381" t="str">
+        <v>April 15, 2026</v>
+      </c>
+      <c r="I381" t="str">
+        <v>ada</v>
+      </c>
+      <c r="J381" t="str">
+        <v/>
+      </c>
+      <c r="K381" t="str">
+        <v/>
+      </c>
+      <c r="L381" t="str">
+        <v/>
+      </c>
+      <c r="M381" t="str">
+        <v>zc</v>
+      </c>
+      <c r="N381" t="str">
+        <v>asd</v>
+      </c>
+      <c r="O381" t="str">
+        <v/>
+      </c>
+      <c r="P381" t="str">
+        <v>s</v>
+      </c>
+      <c r="Q381" t="str">
+        <v>Filed in Court</v>
+      </c>
+      <c r="R381" t="str">
+        <v>a</v>
+      </c>
+      <c r="S381" t="str">
+        <v>April 14, 2026</v>
+      </c>
+      <c r="T381" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T380"/>
+  <autoFilter ref="A1:T381"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T380"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T381"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T383</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T381"/>
+  <dimension ref="A1:T383"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -23989,7 +23989,7 @@
         <v>Test3</v>
       </c>
       <c r="B381" t="str">
-        <v>April 22, 2026</v>
+        <v>April 21, 2026</v>
       </c>
       <c r="C381" t="str">
         <v>s</v>
@@ -24007,7 +24007,7 @@
         <v/>
       </c>
       <c r="H381" t="str">
-        <v>April 15, 2026</v>
+        <v>April 14, 2026</v>
       </c>
       <c r="I381" t="str">
         <v>ada</v>
@@ -24022,10 +24022,10 @@
         <v/>
       </c>
       <c r="M381" t="str">
-        <v>zc</v>
+        <v>343dfd</v>
       </c>
       <c r="N381" t="str">
-        <v>asd</v>
+        <v>gdfgdfgdf</v>
       </c>
       <c r="O381" t="str">
         <v/>
@@ -24040,16 +24040,140 @@
         <v>a</v>
       </c>
       <c r="S381" t="str">
-        <v>April 14, 2026</v>
+        <v>April 13, 2026</v>
       </c>
       <c r="T381" t="str">
         <v>N/A</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Test3</v>
+      </c>
+      <c r="B382" t="str">
+        <v>April 21, 2026</v>
+      </c>
+      <c r="C382" t="str">
+        <v>s</v>
+      </c>
+      <c r="D382" t="str">
+        <v>sdfsfds</v>
+      </c>
+      <c r="E382" t="str">
+        <v>s</v>
+      </c>
+      <c r="F382" t="str">
+        <v>dfsdf</v>
+      </c>
+      <c r="G382" t="str">
+        <v/>
+      </c>
+      <c r="H382" t="str">
+        <v>April 14, 2026</v>
+      </c>
+      <c r="I382" t="str">
+        <v>ada</v>
+      </c>
+      <c r="J382" t="str">
+        <v/>
+      </c>
+      <c r="K382" t="str">
+        <v/>
+      </c>
+      <c r="L382" t="str">
+        <v/>
+      </c>
+      <c r="M382" t="str">
+        <v>sdfsdf</v>
+      </c>
+      <c r="N382" t="str">
+        <v>dfgdfgdfg</v>
+      </c>
+      <c r="O382" t="str">
+        <v/>
+      </c>
+      <c r="P382" t="str">
+        <v>s</v>
+      </c>
+      <c r="Q382" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="R382" t="str">
+        <v>a</v>
+      </c>
+      <c r="S382" t="str">
+        <v>April 13, 2026</v>
+      </c>
+      <c r="T382" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Test3</v>
+      </c>
+      <c r="B383" t="str">
+        <v>April 21, 2026</v>
+      </c>
+      <c r="C383" t="str">
+        <v>s</v>
+      </c>
+      <c r="D383" t="str">
+        <v>sdfsdfsdf</v>
+      </c>
+      <c r="E383" t="str">
+        <v>s</v>
+      </c>
+      <c r="F383" t="str">
+        <v>dfsdf</v>
+      </c>
+      <c r="G383" t="str">
+        <v/>
+      </c>
+      <c r="H383" t="str">
+        <v>April 14, 2026</v>
+      </c>
+      <c r="I383" t="str">
+        <v>ada</v>
+      </c>
+      <c r="J383" t="str">
+        <v/>
+      </c>
+      <c r="K383" t="str">
+        <v/>
+      </c>
+      <c r="L383" t="str">
+        <v/>
+      </c>
+      <c r="M383" t="str">
+        <v>dfgdfgdfg</v>
+      </c>
+      <c r="N383" t="str">
+        <v>sdf</v>
+      </c>
+      <c r="O383" t="str">
+        <v/>
+      </c>
+      <c r="P383" t="str">
+        <v>sdfsdfs</v>
+      </c>
+      <c r="Q383" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="R383" t="str">
+        <v>a</v>
+      </c>
+      <c r="S383" t="str">
+        <v>April 13, 2026</v>
+      </c>
+      <c r="T383" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T381"/>
+  <autoFilter ref="A1:T383"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T381"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T383"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T380</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T383"/>
+  <dimension ref="A1:T380"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -15805,7 +15805,7 @@
         <v>VII-14-INV 24B-45</v>
       </c>
       <c r="B249" t="str">
-        <v/>
+        <v>February 13, 2024</v>
       </c>
       <c r="C249" t="str">
         <v>TARIAO, ROSALINDA R.</v>
@@ -15867,7 +15867,7 @@
         <v>VII-14-INV 24B-45</v>
       </c>
       <c r="B250" t="str">
-        <v/>
+        <v>February 13, 2024</v>
       </c>
       <c r="C250" t="str">
         <v>TARIAO, ROSALINDA R.</v>
@@ -23984,196 +23984,10 @@
         <v>CUTAMORA, FLAVIA_0001.pdf</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="str">
-        <v>Test3</v>
-      </c>
-      <c r="B381" t="str">
-        <v>April 21, 2026</v>
-      </c>
-      <c r="C381" t="str">
-        <v>s</v>
-      </c>
-      <c r="D381" t="str">
-        <v>sdf</v>
-      </c>
-      <c r="E381" t="str">
-        <v>sdfs</v>
-      </c>
-      <c r="F381" t="str">
-        <v>dfsdf</v>
-      </c>
-      <c r="G381" t="str">
-        <v/>
-      </c>
-      <c r="H381" t="str">
-        <v>April 14, 2026</v>
-      </c>
-      <c r="I381" t="str">
-        <v>ada</v>
-      </c>
-      <c r="J381" t="str">
-        <v/>
-      </c>
-      <c r="K381" t="str">
-        <v/>
-      </c>
-      <c r="L381" t="str">
-        <v/>
-      </c>
-      <c r="M381" t="str">
-        <v>343dfd</v>
-      </c>
-      <c r="N381" t="str">
-        <v>gdfgdfgdf</v>
-      </c>
-      <c r="O381" t="str">
-        <v/>
-      </c>
-      <c r="P381" t="str">
-        <v>s</v>
-      </c>
-      <c r="Q381" t="str">
-        <v>Filed in Court</v>
-      </c>
-      <c r="R381" t="str">
-        <v>a</v>
-      </c>
-      <c r="S381" t="str">
-        <v>April 13, 2026</v>
-      </c>
-      <c r="T381" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="str">
-        <v>Test3</v>
-      </c>
-      <c r="B382" t="str">
-        <v>April 21, 2026</v>
-      </c>
-      <c r="C382" t="str">
-        <v>s</v>
-      </c>
-      <c r="D382" t="str">
-        <v>sdfsfds</v>
-      </c>
-      <c r="E382" t="str">
-        <v>s</v>
-      </c>
-      <c r="F382" t="str">
-        <v>dfsdf</v>
-      </c>
-      <c r="G382" t="str">
-        <v/>
-      </c>
-      <c r="H382" t="str">
-        <v>April 14, 2026</v>
-      </c>
-      <c r="I382" t="str">
-        <v>ada</v>
-      </c>
-      <c r="J382" t="str">
-        <v/>
-      </c>
-      <c r="K382" t="str">
-        <v/>
-      </c>
-      <c r="L382" t="str">
-        <v/>
-      </c>
-      <c r="M382" t="str">
-        <v>sdfsdf</v>
-      </c>
-      <c r="N382" t="str">
-        <v>dfgdfgdfg</v>
-      </c>
-      <c r="O382" t="str">
-        <v/>
-      </c>
-      <c r="P382" t="str">
-        <v>s</v>
-      </c>
-      <c r="Q382" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="R382" t="str">
-        <v>a</v>
-      </c>
-      <c r="S382" t="str">
-        <v>April 13, 2026</v>
-      </c>
-      <c r="T382" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="str">
-        <v>Test3</v>
-      </c>
-      <c r="B383" t="str">
-        <v>April 21, 2026</v>
-      </c>
-      <c r="C383" t="str">
-        <v>s</v>
-      </c>
-      <c r="D383" t="str">
-        <v>sdfsdfsdf</v>
-      </c>
-      <c r="E383" t="str">
-        <v>s</v>
-      </c>
-      <c r="F383" t="str">
-        <v>dfsdf</v>
-      </c>
-      <c r="G383" t="str">
-        <v/>
-      </c>
-      <c r="H383" t="str">
-        <v>April 14, 2026</v>
-      </c>
-      <c r="I383" t="str">
-        <v>ada</v>
-      </c>
-      <c r="J383" t="str">
-        <v/>
-      </c>
-      <c r="K383" t="str">
-        <v/>
-      </c>
-      <c r="L383" t="str">
-        <v/>
-      </c>
-      <c r="M383" t="str">
-        <v>dfgdfgdfg</v>
-      </c>
-      <c r="N383" t="str">
-        <v>sdf</v>
-      </c>
-      <c r="O383" t="str">
-        <v/>
-      </c>
-      <c r="P383" t="str">
-        <v>sdfsdfs</v>
-      </c>
-      <c r="Q383" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="R383" t="str">
-        <v>a</v>
-      </c>
-      <c r="S383" t="str">
-        <v>April 13, 2026</v>
-      </c>
-      <c r="T383" t="str">
-        <v>N/A</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T383"/>
+  <autoFilter ref="A1:T380"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T383"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T380"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/uploads/cases.xlsx
+++ b/uploads/cases.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Cases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T380</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Cases'!A1:T383</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T380"/>
+  <dimension ref="A1:T383"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -23984,10 +23984,196 @@
         <v>CUTAMORA, FLAVIA_0001.pdf</v>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>adas</v>
+      </c>
+      <c r="B381" t="str">
+        <v>April 22, 2026</v>
+      </c>
+      <c r="C381" t="str">
+        <v>asda</v>
+      </c>
+      <c r="D381" t="str">
+        <v>asdas</v>
+      </c>
+      <c r="E381" t="str">
+        <v>sdfs</v>
+      </c>
+      <c r="F381" t="str">
+        <v>odasd</v>
+      </c>
+      <c r="G381" t="str">
+        <v/>
+      </c>
+      <c r="H381" t="str">
+        <v/>
+      </c>
+      <c r="I381" t="str">
+        <v>asdasda</v>
+      </c>
+      <c r="J381" t="str">
+        <v/>
+      </c>
+      <c r="K381" t="str">
+        <v/>
+      </c>
+      <c r="L381" t="str">
+        <v/>
+      </c>
+      <c r="M381" t="str">
+        <v/>
+      </c>
+      <c r="N381" t="str">
+        <v/>
+      </c>
+      <c r="O381" t="str">
+        <v/>
+      </c>
+      <c r="P381" t="str">
+        <v/>
+      </c>
+      <c r="Q381" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="R381" t="str">
+        <v/>
+      </c>
+      <c r="S381" t="str">
+        <v/>
+      </c>
+      <c r="T381" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>adas</v>
+      </c>
+      <c r="B382" t="str">
+        <v>April 22, 2026</v>
+      </c>
+      <c r="C382" t="str">
+        <v>asda</v>
+      </c>
+      <c r="D382" t="str">
+        <v>dfgdfg</v>
+      </c>
+      <c r="E382" t="str">
+        <v>sfgdf</v>
+      </c>
+      <c r="F382" t="str">
+        <v>odasd</v>
+      </c>
+      <c r="G382" t="str">
+        <v/>
+      </c>
+      <c r="H382" t="str">
+        <v/>
+      </c>
+      <c r="I382" t="str">
+        <v>asdasda</v>
+      </c>
+      <c r="J382" t="str">
+        <v/>
+      </c>
+      <c r="K382" t="str">
+        <v/>
+      </c>
+      <c r="L382" t="str">
+        <v/>
+      </c>
+      <c r="M382" t="str">
+        <v/>
+      </c>
+      <c r="N382" t="str">
+        <v/>
+      </c>
+      <c r="O382" t="str">
+        <v/>
+      </c>
+      <c r="P382" t="str">
+        <v/>
+      </c>
+      <c r="Q382" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="R382" t="str">
+        <v/>
+      </c>
+      <c r="S382" t="str">
+        <v/>
+      </c>
+      <c r="T382" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>adas</v>
+      </c>
+      <c r="B383" t="str">
+        <v>April 22, 2026</v>
+      </c>
+      <c r="C383" t="str">
+        <v>asda</v>
+      </c>
+      <c r="D383" t="str">
+        <v>sdfs</v>
+      </c>
+      <c r="E383" t="str">
+        <v>dfgdfg</v>
+      </c>
+      <c r="F383" t="str">
+        <v>odasd</v>
+      </c>
+      <c r="G383" t="str">
+        <v/>
+      </c>
+      <c r="H383" t="str">
+        <v/>
+      </c>
+      <c r="I383" t="str">
+        <v>asdasda</v>
+      </c>
+      <c r="J383" t="str">
+        <v/>
+      </c>
+      <c r="K383" t="str">
+        <v/>
+      </c>
+      <c r="L383" t="str">
+        <v/>
+      </c>
+      <c r="M383" t="str">
+        <v/>
+      </c>
+      <c r="N383" t="str">
+        <v/>
+      </c>
+      <c r="O383" t="str">
+        <v/>
+      </c>
+      <c r="P383" t="str">
+        <v/>
+      </c>
+      <c r="Q383" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="R383" t="str">
+        <v/>
+      </c>
+      <c r="S383" t="str">
+        <v/>
+      </c>
+      <c r="T383" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T380"/>
+  <autoFilter ref="A1:T383"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T380"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T383"/>
   </ignoredErrors>
 </worksheet>
 </file>